--- a/assets/Items_for_Replenishment.xlsx
+++ b/assets/Items_for_Replenishment.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30430"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0E2F6EB-D6DC-4EE6-A855-97877241C869}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5A6BE45-BFFE-4A0A-93B2-57BC2105D58E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -108,7 +108,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -127,6 +127,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -432,7 +438,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B587"/>
+  <dimension ref="A1:B616"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.140625" style="6" customWidth="1"/>
@@ -452,7 +458,7 @@
         <v>46496</v>
       </c>
       <c r="B2" s="2">
-        <v>620</v>
+        <v>544</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -460,7 +466,7 @@
         <v>55847</v>
       </c>
       <c r="B3" s="2">
-        <v>984</v>
+        <v>936</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -468,7 +474,7 @@
         <v>68563</v>
       </c>
       <c r="B4" s="2">
-        <v>2480</v>
+        <v>2400</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -476,7 +482,7 @@
         <v>74532</v>
       </c>
       <c r="B5" s="2">
-        <v>86</v>
+        <v>22</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -484,7 +490,7 @@
         <v>76560</v>
       </c>
       <c r="B6" s="2">
-        <v>592</v>
+        <v>586</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -492,7 +498,7 @@
         <v>78699</v>
       </c>
       <c r="B7" s="2">
-        <v>1270</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -500,7 +506,7 @@
         <v>80815</v>
       </c>
       <c r="B8" s="2">
-        <v>2336</v>
+        <v>2296</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -508,7 +514,7 @@
         <v>82379</v>
       </c>
       <c r="B9" s="2">
-        <v>1020</v>
+        <v>958</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
@@ -516,7 +522,7 @@
         <v>82595</v>
       </c>
       <c r="B10" s="2">
-        <v>1050</v>
+        <v>940</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
@@ -524,7 +530,7 @@
         <v>84559</v>
       </c>
       <c r="B11" s="2">
-        <v>1544</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
@@ -532,127 +538,127 @@
         <v>84662</v>
       </c>
       <c r="B12" s="2">
-        <v>1000</v>
+        <v>890</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
-        <v>86979</v>
+        <v>87151</v>
       </c>
       <c r="B13" s="2">
-        <v>2</v>
+        <v>2260</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
-        <v>87151</v>
+        <v>87154</v>
       </c>
       <c r="B14" s="2">
-        <v>2370</v>
+        <v>1230</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
-        <v>87154</v>
+        <v>87813</v>
       </c>
       <c r="B15" s="2">
-        <v>1340</v>
+        <v>330</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
-        <v>87813</v>
+        <v>88245</v>
       </c>
       <c r="B16" s="2">
-        <v>354</v>
+        <v>610</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
-        <v>88245</v>
+        <v>88478</v>
       </c>
       <c r="B17" s="2">
-        <v>630</v>
+        <v>104</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
-        <v>88478</v>
+        <v>88481</v>
       </c>
       <c r="B18" s="2">
-        <v>120</v>
+        <v>505</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
-        <v>88481</v>
+        <v>88571</v>
       </c>
       <c r="B19" s="2">
-        <v>560</v>
+        <v>246</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
-        <v>88571</v>
+        <v>88609</v>
       </c>
       <c r="B20" s="2">
-        <v>280</v>
+        <v>384</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
-        <v>88609</v>
+        <v>88810</v>
       </c>
       <c r="B21" s="2">
-        <v>414</v>
+        <v>557</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
-        <v>88810</v>
+        <v>89952</v>
       </c>
       <c r="B22" s="2">
-        <v>589</v>
+        <v>642</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
-        <v>89952</v>
+        <v>90828</v>
       </c>
       <c r="B23" s="2">
-        <v>678</v>
+        <v>20</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
-        <v>90828</v>
+        <v>90829</v>
       </c>
       <c r="B24" s="2">
-        <v>20</v>
+        <v>420</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
-        <v>90829</v>
+        <v>90830</v>
       </c>
       <c r="B25" s="2">
-        <v>440</v>
+        <v>3660</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
-        <v>90830</v>
+        <v>90831</v>
       </c>
       <c r="B26" s="2">
-        <v>3660</v>
+        <v>700</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
-        <v>90831</v>
+        <v>91064</v>
       </c>
       <c r="B27" s="2">
-        <v>700</v>
+        <v>1623</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
@@ -660,268 +666,268 @@
         <v>91290</v>
       </c>
       <c r="B28" s="2">
-        <v>1190</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
-        <v>92425</v>
+        <v>91431</v>
       </c>
       <c r="B29" s="2">
-        <v>600</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
-        <v>92681</v>
+        <v>92425</v>
       </c>
       <c r="B30" s="2">
-        <v>1793</v>
+        <v>570</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
-        <v>92688</v>
+        <v>92681</v>
       </c>
       <c r="B31" s="2">
-        <v>1015</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
-        <v>92725</v>
+        <v>92688</v>
       </c>
       <c r="B32" s="2">
-        <v>1200</v>
+        <v>989</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
-        <v>92728</v>
+        <v>92725</v>
       </c>
       <c r="B33" s="2">
-        <v>320</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
-        <v>92730</v>
+        <v>92728</v>
       </c>
       <c r="B34" s="2">
-        <v>640</v>
+        <v>320</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
-        <v>92731</v>
+        <v>92730</v>
       </c>
       <c r="B35" s="2">
-        <v>1070</v>
+        <v>640</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" s="1">
-        <v>93307</v>
+        <v>92731</v>
       </c>
       <c r="B36" s="2">
-        <v>952</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" s="1">
-        <v>93311</v>
+        <v>93286</v>
       </c>
       <c r="B37" s="2">
-        <v>1356</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
-        <v>93329</v>
+        <v>93307</v>
       </c>
       <c r="B38" s="2">
-        <v>2303</v>
+        <v>618</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
-        <v>93333</v>
+        <v>93311</v>
       </c>
       <c r="B39" s="2">
-        <v>1732</v>
+        <v>974</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" s="1">
-        <v>94076</v>
+        <v>93329</v>
       </c>
       <c r="B40" s="2">
-        <v>3126</v>
+        <v>2233</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" s="1">
-        <v>94319</v>
+        <v>93333</v>
       </c>
       <c r="B41" s="2">
-        <v>150</v>
+        <v>1684</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" s="1">
-        <v>94320</v>
+        <v>94076</v>
       </c>
       <c r="B42" s="2">
-        <v>650</v>
+        <v>3096</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" s="1">
-        <v>94321</v>
+        <v>94319</v>
       </c>
       <c r="B43" s="2">
-        <v>60</v>
+        <v>150</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" s="1">
-        <v>94322</v>
+        <v>94320</v>
       </c>
       <c r="B44" s="2">
-        <v>970</v>
+        <v>650</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" s="1">
-        <v>94916</v>
+        <v>94321</v>
       </c>
       <c r="B45" s="2">
-        <v>2494</v>
+        <v>60</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" s="1">
-        <v>94917</v>
+        <v>94322</v>
       </c>
       <c r="B46" s="2">
-        <v>2252</v>
+        <v>940</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" s="1">
-        <v>95677</v>
+        <v>94425</v>
       </c>
       <c r="B47" s="2">
-        <v>1224</v>
+        <v>1458</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" s="1">
-        <v>95815</v>
+        <v>94916</v>
       </c>
       <c r="B48" s="2">
-        <v>1184</v>
+        <v>2278</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" s="1">
-        <v>95816</v>
+        <v>94917</v>
       </c>
       <c r="B49" s="2">
-        <v>2376</v>
+        <v>2100</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" s="1">
-        <v>95817</v>
+        <v>95677</v>
       </c>
       <c r="B50" s="2">
-        <v>2256</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" s="1">
-        <v>95947</v>
+        <v>95815</v>
       </c>
       <c r="B51" s="2">
-        <v>600</v>
+        <v>1166</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52" s="1">
-        <v>96559</v>
+        <v>95816</v>
       </c>
       <c r="B52" s="2">
-        <v>7600</v>
+        <v>1862</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A53" s="1">
-        <v>96893</v>
+        <v>95817</v>
       </c>
       <c r="B53" s="2">
-        <v>32</v>
+        <v>1834</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A54" s="1">
-        <v>97525</v>
+        <v>95947</v>
       </c>
       <c r="B54" s="2">
-        <v>104</v>
+        <v>396</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A55" s="1">
-        <v>97526</v>
+        <v>96557</v>
       </c>
       <c r="B55" s="2">
-        <v>96</v>
+        <v>1551</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A56" s="1">
-        <v>97527</v>
+        <v>96559</v>
       </c>
       <c r="B56" s="2">
-        <v>128</v>
+        <v>7580</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A57" s="1">
-        <v>97529</v>
+        <v>96893</v>
       </c>
       <c r="B57" s="2">
-        <v>2</v>
+        <v>12</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A58" s="1">
-        <v>97543</v>
+        <v>97525</v>
       </c>
       <c r="B58" s="2">
-        <v>64</v>
+        <v>98</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A59" s="1">
-        <v>97544</v>
+        <v>97526</v>
       </c>
       <c r="B59" s="2">
-        <v>2</v>
+        <v>20</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A60" s="1">
-        <v>97545</v>
+        <v>97527</v>
       </c>
       <c r="B60" s="2">
-        <v>14</v>
+        <v>40</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A61" s="1">
-        <v>97547</v>
+        <v>97543</v>
       </c>
       <c r="B61" s="2">
         <v>12</v>
@@ -929,34 +935,34 @@
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A62" s="1">
-        <v>97690</v>
+        <v>97545</v>
       </c>
       <c r="B62" s="2">
-        <v>204</v>
+        <v>6</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A63" s="1">
-        <v>97691</v>
+        <v>97547</v>
       </c>
       <c r="B63" s="2">
-        <v>206</v>
+        <v>4</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A64" s="1">
-        <v>97698</v>
+        <v>97690</v>
       </c>
       <c r="B64" s="2">
-        <v>4</v>
+        <v>180</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A65" s="1">
-        <v>97699</v>
+        <v>97691</v>
       </c>
       <c r="B65" s="2">
-        <v>22</v>
+        <v>194</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.25">
@@ -964,7 +970,7 @@
         <v>98423</v>
       </c>
       <c r="B66" s="2">
-        <v>55</v>
+        <v>25</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.25">
@@ -972,7 +978,7 @@
         <v>98424</v>
       </c>
       <c r="B67" s="2">
-        <v>56</v>
+        <v>38</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.25">
@@ -980,7 +986,7 @@
         <v>98600</v>
       </c>
       <c r="B68" s="2">
-        <v>280</v>
+        <v>250</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.25">
@@ -988,7 +994,7 @@
         <v>98601</v>
       </c>
       <c r="B69" s="2">
-        <v>270</v>
+        <v>180</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.25">
@@ -1012,7 +1018,7 @@
         <v>98658</v>
       </c>
       <c r="B72" s="2">
-        <v>700</v>
+        <v>680</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.25">
@@ -1020,7 +1026,7 @@
         <v>99392</v>
       </c>
       <c r="B73" s="2">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.25">
@@ -1028,1276 +1034,1276 @@
         <v>99393</v>
       </c>
       <c r="B74" s="2">
-        <v>27</v>
+        <v>12</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A75" s="1">
-        <v>99395</v>
+        <v>3764</v>
       </c>
       <c r="B75" s="2">
-        <v>9</v>
+        <v>972</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A76" s="1">
-        <v>3764</v>
+        <v>3775</v>
       </c>
       <c r="B76" s="2">
-        <v>198</v>
+        <v>3924</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A77" s="1">
-        <v>3775</v>
+        <v>3780</v>
       </c>
       <c r="B77" s="2">
-        <v>1332</v>
+        <v>2016</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A78" s="1">
-        <v>3809</v>
+        <v>3786</v>
       </c>
       <c r="B78" s="2">
-        <v>414</v>
+        <v>1728</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A79" s="1">
-        <v>3821</v>
+        <v>3798</v>
       </c>
       <c r="B79" s="2">
-        <v>432</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A80" s="1">
-        <v>3833</v>
+        <v>3809</v>
       </c>
       <c r="B80" s="2">
-        <v>756</v>
+        <v>954</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A81" s="1">
-        <v>36371</v>
+        <v>3817</v>
       </c>
       <c r="B81" s="2">
-        <v>1750</v>
+        <v>2304</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A82" s="1">
-        <v>54955</v>
+        <v>3821</v>
       </c>
       <c r="B82" s="2">
-        <v>6</v>
+        <v>918</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A83" s="1">
-        <v>59296</v>
+        <v>3827</v>
       </c>
       <c r="B83" s="2">
-        <v>92</v>
+        <v>1728</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A84" s="1">
-        <v>68947</v>
+        <v>3833</v>
       </c>
       <c r="B84" s="2">
-        <v>558</v>
+        <v>3636</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A85" s="1">
-        <v>68959</v>
+        <v>36371</v>
       </c>
       <c r="B85" s="2">
-        <v>6</v>
+        <v>1688</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A86" s="1">
-        <v>70451</v>
+        <v>59296</v>
       </c>
       <c r="B86" s="2">
-        <v>3066</v>
+        <v>44</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A87" s="1">
-        <v>73723</v>
+        <v>68947</v>
       </c>
       <c r="B87" s="2">
-        <v>903</v>
+        <v>498</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A88" s="1">
-        <v>74359</v>
+        <v>70451</v>
       </c>
       <c r="B88" s="2">
-        <v>702</v>
+        <v>2838</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A89" s="1">
-        <v>98427</v>
+        <v>70739</v>
       </c>
       <c r="B89" s="2">
-        <v>189</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A90" s="1">
-        <v>6881</v>
+        <v>73723</v>
       </c>
       <c r="B90" s="2">
-        <v>45</v>
+        <v>855</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A91" s="1">
-        <v>9859</v>
+        <v>74359</v>
       </c>
       <c r="B91" s="2">
-        <v>147</v>
+        <v>2736</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A92" s="1">
-        <v>9963</v>
+        <v>82580</v>
       </c>
       <c r="B92" s="2">
-        <v>152</v>
+        <v>3960</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A93" s="1">
-        <v>16075</v>
+        <v>82581</v>
       </c>
       <c r="B93" s="2">
-        <v>252</v>
+        <v>3960</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A94" s="1">
-        <v>68878</v>
+        <v>82582</v>
       </c>
       <c r="B94" s="2">
-        <v>115</v>
+        <v>4248</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A95" s="1">
-        <v>68879</v>
+        <v>82587</v>
       </c>
       <c r="B95" s="2">
-        <v>315</v>
+        <v>4248</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A96" s="1">
-        <v>68880</v>
+        <v>83192</v>
       </c>
       <c r="B96" s="2">
-        <v>235</v>
+        <v>864</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A97" s="1">
-        <v>84851</v>
+        <v>83687</v>
       </c>
       <c r="B97" s="2">
-        <v>305</v>
+        <v>4320</v>
       </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A98" s="1">
-        <v>84852</v>
+        <v>83689</v>
       </c>
       <c r="B98" s="2">
-        <v>279</v>
+        <v>4320</v>
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A99" s="1">
-        <v>84853</v>
+        <v>91047</v>
       </c>
       <c r="B99" s="2">
-        <v>110</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A100" s="1">
-        <v>84854</v>
+        <v>98427</v>
       </c>
       <c r="B100" s="2">
-        <v>253</v>
+        <v>57</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A101" s="1">
-        <v>84855</v>
+        <v>6881</v>
       </c>
       <c r="B101" s="2">
-        <v>215</v>
+        <v>22</v>
       </c>
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A102" s="1">
-        <v>85743</v>
+        <v>9859</v>
       </c>
       <c r="B102" s="2">
-        <v>290</v>
+        <v>107</v>
       </c>
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A103" s="1">
-        <v>86015</v>
+        <v>9963</v>
       </c>
       <c r="B103" s="2">
-        <v>188</v>
+        <v>70</v>
       </c>
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A104" s="1">
-        <v>86016</v>
+        <v>16075</v>
       </c>
       <c r="B104" s="2">
-        <v>58</v>
+        <v>228</v>
       </c>
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A105" s="1">
-        <v>86266</v>
+        <v>68878</v>
       </c>
       <c r="B105" s="2">
-        <v>224</v>
+        <v>85</v>
       </c>
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A106" s="1">
-        <v>86268</v>
+        <v>68879</v>
       </c>
       <c r="B106" s="2">
-        <v>363</v>
+        <v>287</v>
       </c>
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A107" s="1">
-        <v>86269</v>
+        <v>68880</v>
       </c>
       <c r="B107" s="2">
-        <v>119</v>
+        <v>221</v>
       </c>
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A108" s="1">
-        <v>86286</v>
+        <v>84851</v>
       </c>
       <c r="B108" s="2">
-        <v>558</v>
+        <v>271</v>
       </c>
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A109" s="1">
-        <v>86287</v>
+        <v>84852</v>
       </c>
       <c r="B109" s="2">
-        <v>508</v>
+        <v>237</v>
       </c>
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A110" s="1">
-        <v>86288</v>
+        <v>84853</v>
       </c>
       <c r="B110" s="2">
-        <v>483</v>
+        <v>70</v>
       </c>
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A111" s="1">
-        <v>86289</v>
+        <v>84854</v>
       </c>
       <c r="B111" s="2">
-        <v>209</v>
+        <v>223</v>
       </c>
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A112" s="1">
-        <v>87342</v>
+        <v>84855</v>
       </c>
       <c r="B112" s="2">
-        <v>380</v>
+        <v>193</v>
       </c>
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A113" s="1">
-        <v>87343</v>
+        <v>85743</v>
       </c>
       <c r="B113" s="2">
-        <v>311</v>
+        <v>270</v>
       </c>
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A114" s="1">
-        <v>87344</v>
+        <v>86015</v>
       </c>
       <c r="B114" s="2">
-        <v>216</v>
+        <v>177</v>
       </c>
     </row>
     <row r="115" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A115" s="1">
-        <v>87345</v>
+        <v>86016</v>
       </c>
       <c r="B115" s="2">
-        <v>174</v>
+        <v>48</v>
       </c>
     </row>
     <row r="116" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A116" s="1">
-        <v>87416</v>
+        <v>86266</v>
       </c>
       <c r="B116" s="2">
-        <v>286</v>
+        <v>158</v>
       </c>
     </row>
     <row r="117" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A117" s="1">
-        <v>87417</v>
+        <v>86268</v>
       </c>
       <c r="B117" s="2">
-        <v>150</v>
+        <v>340</v>
       </c>
     </row>
     <row r="118" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A118" s="1">
-        <v>87419</v>
+        <v>86269</v>
       </c>
       <c r="B118" s="2">
-        <v>19</v>
+        <v>100</v>
       </c>
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A119" s="1">
-        <v>87882</v>
+        <v>86286</v>
       </c>
       <c r="B119" s="2">
-        <v>704</v>
+        <v>518</v>
       </c>
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A120" s="1">
-        <v>87883</v>
+        <v>86287</v>
       </c>
       <c r="B120" s="2">
-        <v>473</v>
+        <v>483</v>
       </c>
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A121" s="1">
-        <v>87884</v>
+        <v>86288</v>
       </c>
       <c r="B121" s="2">
-        <v>110</v>
+        <v>462</v>
       </c>
     </row>
     <row r="122" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A122" s="1">
-        <v>87885</v>
+        <v>86289</v>
       </c>
       <c r="B122" s="2">
-        <v>164</v>
+        <v>191</v>
       </c>
     </row>
     <row r="123" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A123" s="1">
-        <v>87886</v>
+        <v>87342</v>
       </c>
       <c r="B123" s="2">
-        <v>183</v>
+        <v>112</v>
       </c>
     </row>
     <row r="124" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A124" s="1">
-        <v>87932</v>
+        <v>87343</v>
       </c>
       <c r="B124" s="2">
-        <v>679</v>
+        <v>94</v>
       </c>
     </row>
     <row r="125" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A125" s="1">
-        <v>87934</v>
+        <v>87344</v>
       </c>
       <c r="B125" s="2">
-        <v>468</v>
+        <v>59</v>
       </c>
     </row>
     <row r="126" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A126" s="1">
-        <v>87937</v>
+        <v>87345</v>
       </c>
       <c r="B126" s="2">
-        <v>471</v>
+        <v>46</v>
       </c>
     </row>
     <row r="127" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A127" s="1">
-        <v>87938</v>
+        <v>87416</v>
       </c>
       <c r="B127" s="2">
-        <v>678</v>
+        <v>258</v>
       </c>
     </row>
     <row r="128" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A128" s="1">
-        <v>87939</v>
+        <v>87417</v>
       </c>
       <c r="B128" s="2">
-        <v>439</v>
+        <v>121</v>
       </c>
     </row>
     <row r="129" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A129" s="1">
-        <v>87941</v>
+        <v>87882</v>
       </c>
       <c r="B129" s="2">
-        <v>36</v>
+        <v>689</v>
       </c>
     </row>
     <row r="130" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A130" s="1">
-        <v>88653</v>
+        <v>87883</v>
       </c>
       <c r="B130" s="2">
-        <v>408</v>
+        <v>462</v>
       </c>
     </row>
     <row r="131" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A131" s="1">
-        <v>88654</v>
+        <v>87884</v>
       </c>
       <c r="B131" s="2">
-        <v>459</v>
+        <v>100</v>
       </c>
     </row>
     <row r="132" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A132" s="1">
-        <v>88655</v>
+        <v>87885</v>
       </c>
       <c r="B132" s="2">
-        <v>563</v>
+        <v>151</v>
       </c>
     </row>
     <row r="133" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A133" s="1">
-        <v>88656</v>
+        <v>87886</v>
       </c>
       <c r="B133" s="2">
-        <v>165</v>
+        <v>175</v>
       </c>
     </row>
     <row r="134" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A134" s="1">
-        <v>88657</v>
+        <v>87932</v>
       </c>
       <c r="B134" s="2">
-        <v>91</v>
+        <v>654</v>
       </c>
     </row>
     <row r="135" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A135" s="1">
-        <v>89339</v>
+        <v>87934</v>
       </c>
       <c r="B135" s="2">
-        <v>132</v>
+        <v>438</v>
       </c>
     </row>
     <row r="136" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A136" s="1">
-        <v>89340</v>
+        <v>87937</v>
       </c>
       <c r="B136" s="2">
-        <v>229</v>
+        <v>435</v>
       </c>
     </row>
     <row r="137" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A137" s="1">
-        <v>89341</v>
+        <v>87938</v>
       </c>
       <c r="B137" s="2">
-        <v>117</v>
+        <v>657</v>
       </c>
     </row>
     <row r="138" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A138" s="1">
-        <v>90566</v>
+        <v>87939</v>
       </c>
       <c r="B138" s="2">
-        <v>490</v>
+        <v>420</v>
       </c>
     </row>
     <row r="139" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A139" s="1">
-        <v>90568</v>
+        <v>87941</v>
       </c>
       <c r="B139" s="2">
-        <v>356</v>
+        <v>26</v>
       </c>
     </row>
     <row r="140" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A140" s="1">
-        <v>90569</v>
+        <v>88653</v>
       </c>
       <c r="B140" s="2">
-        <v>234</v>
+        <v>393</v>
       </c>
     </row>
     <row r="141" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A141" s="1">
-        <v>90570</v>
+        <v>88654</v>
       </c>
       <c r="B141" s="2">
-        <v>199</v>
+        <v>444</v>
       </c>
     </row>
     <row r="142" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A142" s="1">
-        <v>90789</v>
+        <v>88655</v>
       </c>
       <c r="B142" s="2">
-        <v>321</v>
+        <v>550</v>
       </c>
     </row>
     <row r="143" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A143" s="1">
-        <v>90790</v>
+        <v>88656</v>
       </c>
       <c r="B143" s="2">
-        <v>395</v>
+        <v>160</v>
       </c>
     </row>
     <row r="144" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A144" s="1">
-        <v>90791</v>
+        <v>88657</v>
       </c>
       <c r="B144" s="2">
-        <v>296</v>
+        <v>83</v>
       </c>
     </row>
     <row r="145" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A145" s="1">
-        <v>90792</v>
+        <v>89339</v>
       </c>
       <c r="B145" s="2">
-        <v>140</v>
+        <v>168</v>
       </c>
     </row>
     <row r="146" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A146" s="1">
-        <v>90793</v>
+        <v>89340</v>
       </c>
       <c r="B146" s="2">
-        <v>97</v>
+        <v>229</v>
       </c>
     </row>
     <row r="147" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A147" s="1">
-        <v>90922</v>
+        <v>89341</v>
       </c>
       <c r="B147" s="2">
-        <v>689</v>
+        <v>67</v>
       </c>
     </row>
     <row r="148" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A148" s="1">
-        <v>90923</v>
+        <v>90566</v>
       </c>
       <c r="B148" s="2">
-        <v>634</v>
+        <v>458</v>
       </c>
     </row>
     <row r="149" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A149" s="1">
-        <v>90924</v>
+        <v>90568</v>
       </c>
       <c r="B149" s="2">
-        <v>239</v>
+        <v>341</v>
       </c>
     </row>
     <row r="150" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A150" s="1">
-        <v>90925</v>
+        <v>90569</v>
       </c>
       <c r="B150" s="2">
-        <v>144</v>
+        <v>224</v>
       </c>
     </row>
     <row r="151" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A151" s="1">
-        <v>90926</v>
+        <v>90570</v>
       </c>
       <c r="B151" s="2">
-        <v>143</v>
+        <v>191</v>
       </c>
     </row>
     <row r="152" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A152" s="1">
-        <v>91208</v>
+        <v>90789</v>
       </c>
       <c r="B152" s="2">
-        <v>11</v>
+        <v>112</v>
       </c>
     </row>
     <row r="153" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A153" s="1">
-        <v>91209</v>
+        <v>90790</v>
       </c>
       <c r="B153" s="2">
-        <v>25</v>
+        <v>156</v>
       </c>
     </row>
     <row r="154" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A154" s="1">
-        <v>91279</v>
+        <v>90791</v>
       </c>
       <c r="B154" s="2">
-        <v>525</v>
+        <v>119</v>
       </c>
     </row>
     <row r="155" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A155" s="1">
-        <v>91280</v>
+        <v>90792</v>
       </c>
       <c r="B155" s="2">
-        <v>637</v>
+        <v>45</v>
       </c>
     </row>
     <row r="156" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A156" s="1">
-        <v>91765</v>
+        <v>90793</v>
       </c>
       <c r="B156" s="2">
-        <v>309</v>
+        <v>21</v>
       </c>
     </row>
     <row r="157" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A157" s="1">
-        <v>91766</v>
+        <v>90922</v>
       </c>
       <c r="B157" s="2">
-        <v>111</v>
+        <v>656</v>
       </c>
     </row>
     <row r="158" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A158" s="1">
-        <v>91769</v>
+        <v>90923</v>
       </c>
       <c r="B158" s="2">
-        <v>57</v>
+        <v>600</v>
       </c>
     </row>
     <row r="159" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A159" s="1">
-        <v>91815</v>
+        <v>90924</v>
       </c>
       <c r="B159" s="2">
-        <v>272</v>
+        <v>214</v>
       </c>
     </row>
     <row r="160" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A160" s="1">
-        <v>91816</v>
+        <v>90925</v>
       </c>
       <c r="B160" s="2">
-        <v>906</v>
+        <v>124</v>
       </c>
     </row>
     <row r="161" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A161" s="1">
-        <v>91817</v>
+        <v>90926</v>
       </c>
       <c r="B161" s="2">
-        <v>286</v>
+        <v>120</v>
       </c>
     </row>
     <row r="162" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A162" s="1">
-        <v>92284</v>
+        <v>91208</v>
       </c>
       <c r="B162" s="2">
-        <v>44</v>
+        <v>1</v>
       </c>
     </row>
     <row r="163" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A163" s="1">
-        <v>92285</v>
+        <v>91209</v>
       </c>
       <c r="B163" s="2">
-        <v>92</v>
+        <v>5</v>
       </c>
     </row>
     <row r="164" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A164" s="1">
-        <v>92288</v>
+        <v>91279</v>
       </c>
       <c r="B164" s="2">
-        <v>1034</v>
+        <v>507</v>
       </c>
     </row>
     <row r="165" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A165" s="1">
-        <v>92289</v>
+        <v>91280</v>
       </c>
       <c r="B165" s="2">
-        <v>904</v>
+        <v>613</v>
       </c>
     </row>
     <row r="166" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A166" s="1">
-        <v>92290</v>
+        <v>91765</v>
       </c>
       <c r="B166" s="2">
-        <v>592</v>
+        <v>290</v>
       </c>
     </row>
     <row r="167" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A167" s="1">
-        <v>92291</v>
+        <v>91766</v>
       </c>
       <c r="B167" s="2">
-        <v>452</v>
+        <v>88</v>
       </c>
     </row>
     <row r="168" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A168" s="1">
-        <v>92292</v>
+        <v>91769</v>
       </c>
       <c r="B168" s="2">
-        <v>215</v>
+        <v>50</v>
       </c>
     </row>
     <row r="169" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A169" s="1">
-        <v>92409</v>
+        <v>91815</v>
       </c>
       <c r="B169" s="2">
-        <v>226</v>
+        <v>218</v>
       </c>
     </row>
     <row r="170" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A170" s="1">
-        <v>92410</v>
+        <v>91816</v>
       </c>
       <c r="B170" s="2">
-        <v>310</v>
+        <v>869</v>
       </c>
     </row>
     <row r="171" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A171" s="1">
-        <v>92411</v>
+        <v>91817</v>
       </c>
       <c r="B171" s="2">
-        <v>193</v>
+        <v>255</v>
       </c>
     </row>
     <row r="172" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A172" s="1">
-        <v>92412</v>
+        <v>92284</v>
       </c>
       <c r="B172" s="2">
-        <v>358</v>
+        <v>26</v>
       </c>
     </row>
     <row r="173" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A173" s="1">
-        <v>92413</v>
+        <v>92285</v>
       </c>
       <c r="B173" s="2">
-        <v>112</v>
+        <v>89</v>
       </c>
     </row>
     <row r="174" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A174" s="1">
-        <v>92542</v>
+        <v>92288</v>
       </c>
       <c r="B174" s="2">
-        <v>2</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="175" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A175" s="1">
-        <v>92543</v>
+        <v>92289</v>
       </c>
       <c r="B175" s="2">
-        <v>2</v>
+        <v>886</v>
       </c>
     </row>
     <row r="176" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A176" s="1">
-        <v>92589</v>
+        <v>92290</v>
       </c>
       <c r="B176" s="2">
-        <v>1009</v>
+        <v>581</v>
       </c>
     </row>
     <row r="177" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A177" s="1">
-        <v>92590</v>
+        <v>92291</v>
       </c>
       <c r="B177" s="2">
-        <v>914</v>
+        <v>443</v>
       </c>
     </row>
     <row r="178" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A178" s="1">
-        <v>92591</v>
+        <v>92292</v>
       </c>
       <c r="B178" s="2">
-        <v>446</v>
+        <v>212</v>
       </c>
     </row>
     <row r="179" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A179" s="1">
-        <v>92592</v>
+        <v>92409</v>
       </c>
       <c r="B179" s="2">
-        <v>517</v>
+        <v>185</v>
       </c>
     </row>
     <row r="180" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A180" s="1">
-        <v>92593</v>
+        <v>92410</v>
       </c>
       <c r="B180" s="2">
-        <v>210</v>
+        <v>268</v>
       </c>
     </row>
     <row r="181" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A181" s="1">
-        <v>93238</v>
+        <v>92411</v>
       </c>
       <c r="B181" s="2">
-        <v>1193</v>
+        <v>144</v>
       </c>
     </row>
     <row r="182" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A182" s="1">
-        <v>93239</v>
+        <v>92412</v>
       </c>
       <c r="B182" s="2">
-        <v>971</v>
+        <v>322</v>
       </c>
     </row>
     <row r="183" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A183" s="1">
-        <v>93240</v>
+        <v>92413</v>
       </c>
       <c r="B183" s="2">
-        <v>603</v>
+        <v>96</v>
       </c>
     </row>
     <row r="184" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A184" s="1">
-        <v>93241</v>
+        <v>92589</v>
       </c>
       <c r="B184" s="2">
-        <v>788</v>
+        <v>407</v>
       </c>
     </row>
     <row r="185" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A185" s="1">
-        <v>93242</v>
+        <v>92590</v>
       </c>
       <c r="B185" s="2">
-        <v>443</v>
+        <v>595</v>
       </c>
     </row>
     <row r="186" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A186" s="1">
-        <v>94139</v>
+        <v>92591</v>
       </c>
       <c r="B186" s="2">
-        <v>779</v>
+        <v>405</v>
       </c>
     </row>
     <row r="187" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A187" s="1">
-        <v>94140</v>
+        <v>92592</v>
       </c>
       <c r="B187" s="2">
-        <v>1103</v>
+        <v>255</v>
       </c>
     </row>
     <row r="188" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A188" s="1">
-        <v>94142</v>
+        <v>92593</v>
       </c>
       <c r="B188" s="2">
-        <v>362</v>
+        <v>185</v>
       </c>
     </row>
     <row r="189" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A189" s="1">
-        <v>94169</v>
+        <v>93238</v>
       </c>
       <c r="B189" s="2">
-        <v>1068</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="190" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A190" s="1">
-        <v>94170</v>
+        <v>93239</v>
       </c>
       <c r="B190" s="2">
-        <v>1068</v>
+        <v>939</v>
       </c>
     </row>
     <row r="191" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A191" s="1">
-        <v>94171</v>
+        <v>93240</v>
       </c>
       <c r="B191" s="2">
-        <v>794</v>
+        <v>577</v>
       </c>
     </row>
     <row r="192" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A192" s="1">
-        <v>94172</v>
+        <v>93241</v>
       </c>
       <c r="B192" s="2">
-        <v>620</v>
+        <v>762</v>
       </c>
     </row>
     <row r="193" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A193" s="1">
-        <v>94173</v>
+        <v>93242</v>
       </c>
       <c r="B193" s="2">
-        <v>445</v>
+        <v>428</v>
       </c>
     </row>
     <row r="194" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A194" s="1">
-        <v>94592</v>
+        <v>94139</v>
       </c>
       <c r="B194" s="2">
-        <v>824</v>
+        <v>616</v>
       </c>
     </row>
     <row r="195" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A195" s="1">
-        <v>94593</v>
+        <v>94140</v>
       </c>
       <c r="B195" s="2">
-        <v>753</v>
+        <v>983</v>
       </c>
     </row>
     <row r="196" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A196" s="1">
-        <v>94594</v>
+        <v>94142</v>
       </c>
       <c r="B196" s="2">
-        <v>636</v>
+        <v>302</v>
       </c>
     </row>
     <row r="197" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A197" s="1">
-        <v>94595</v>
+        <v>94169</v>
       </c>
       <c r="B197" s="2">
-        <v>437</v>
+        <v>737</v>
       </c>
     </row>
     <row r="198" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A198" s="1">
-        <v>94596</v>
+        <v>94170</v>
       </c>
       <c r="B198" s="2">
-        <v>205</v>
+        <v>737</v>
       </c>
     </row>
     <row r="199" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A199" s="1">
-        <v>95082</v>
+        <v>94171</v>
       </c>
       <c r="B199" s="2">
-        <v>139</v>
+        <v>571</v>
       </c>
     </row>
     <row r="200" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A200" s="1">
-        <v>95083</v>
+        <v>94172</v>
       </c>
       <c r="B200" s="2">
-        <v>112</v>
+        <v>489</v>
       </c>
     </row>
     <row r="201" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A201" s="1">
-        <v>95085</v>
+        <v>94173</v>
       </c>
       <c r="B201" s="2">
-        <v>21</v>
+        <v>351</v>
       </c>
     </row>
     <row r="202" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A202" s="1">
-        <v>95086</v>
+        <v>94592</v>
       </c>
       <c r="B202" s="2">
-        <v>17</v>
+        <v>753</v>
       </c>
     </row>
     <row r="203" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A203" s="1">
-        <v>95976</v>
+        <v>94593</v>
       </c>
       <c r="B203" s="2">
-        <v>19</v>
+        <v>691</v>
       </c>
     </row>
     <row r="204" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A204" s="1">
-        <v>96315</v>
+        <v>94594</v>
       </c>
       <c r="B204" s="2">
-        <v>635</v>
+        <v>580</v>
       </c>
     </row>
     <row r="205" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A205" s="1">
-        <v>96316</v>
+        <v>94595</v>
       </c>
       <c r="B205" s="2">
-        <v>638</v>
+        <v>409</v>
       </c>
     </row>
     <row r="206" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A206" s="1">
-        <v>96317</v>
+        <v>94596</v>
       </c>
       <c r="B206" s="2">
-        <v>444</v>
+        <v>181</v>
       </c>
     </row>
     <row r="207" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A207" s="1">
-        <v>96318</v>
+        <v>95082</v>
       </c>
       <c r="B207" s="2">
-        <v>282</v>
+        <v>110</v>
       </c>
     </row>
     <row r="208" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A208" s="1">
-        <v>96319</v>
+        <v>95083</v>
       </c>
       <c r="B208" s="2">
-        <v>213</v>
+        <v>86</v>
       </c>
     </row>
     <row r="209" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A209" s="1">
-        <v>97324</v>
+        <v>95085</v>
       </c>
       <c r="B209" s="2">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="210" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A210" s="1">
-        <v>97353</v>
+        <v>95086</v>
       </c>
       <c r="B210" s="2">
-        <v>16</v>
+        <v>9</v>
       </c>
     </row>
     <row r="211" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A211" s="1">
-        <v>97354</v>
+        <v>95976</v>
       </c>
       <c r="B211" s="2">
-        <v>7</v>
+        <v>13</v>
       </c>
     </row>
     <row r="212" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A212" s="1">
-        <v>97355</v>
+        <v>96315</v>
       </c>
       <c r="B212" s="2">
-        <v>23</v>
+        <v>226</v>
       </c>
     </row>
     <row r="213" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A213" s="1">
-        <v>97356</v>
+        <v>96316</v>
       </c>
       <c r="B213" s="2">
-        <v>21</v>
+        <v>223</v>
       </c>
     </row>
     <row r="214" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A214" s="1">
-        <v>97357</v>
+        <v>96317</v>
       </c>
       <c r="B214" s="2">
-        <v>3</v>
+        <v>158</v>
       </c>
     </row>
     <row r="215" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A215" s="1">
-        <v>97375</v>
+        <v>96318</v>
       </c>
       <c r="B215" s="2">
-        <v>1</v>
+        <v>91</v>
       </c>
     </row>
     <row r="216" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A216" s="1">
-        <v>97496</v>
+        <v>96319</v>
       </c>
       <c r="B216" s="2">
-        <v>45</v>
+        <v>65</v>
       </c>
     </row>
     <row r="217" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A217" s="1">
-        <v>97497</v>
+        <v>97324</v>
       </c>
       <c r="B217" s="2">
-        <v>64</v>
+        <v>1</v>
       </c>
     </row>
     <row r="218" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A218" s="1">
-        <v>97498</v>
+        <v>97353</v>
       </c>
       <c r="B218" s="2">
-        <v>20</v>
+        <v>7</v>
       </c>
     </row>
     <row r="219" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A219" s="1">
-        <v>97499</v>
+        <v>97354</v>
       </c>
       <c r="B219" s="2">
-        <v>17</v>
+        <v>2</v>
       </c>
     </row>
     <row r="220" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A220" s="1">
-        <v>97504</v>
+        <v>97355</v>
       </c>
       <c r="B220" s="2">
-        <v>13</v>
+        <v>18</v>
       </c>
     </row>
     <row r="221" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A221" s="1">
-        <v>97797</v>
+        <v>97356</v>
       </c>
       <c r="B221" s="2">
-        <v>55</v>
+        <v>18</v>
       </c>
     </row>
     <row r="222" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A222" s="1">
-        <v>97798</v>
+        <v>97357</v>
       </c>
       <c r="B222" s="2">
-        <v>52</v>
+        <v>1</v>
       </c>
     </row>
     <row r="223" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A223" s="1">
-        <v>97799</v>
+        <v>97496</v>
       </c>
       <c r="B223" s="2">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="224" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A224" s="1">
-        <v>97800</v>
+        <v>97497</v>
       </c>
       <c r="B224" s="2">
-        <v>15</v>
+        <v>45</v>
       </c>
     </row>
     <row r="225" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A225" s="1">
-        <v>97801</v>
+        <v>97498</v>
       </c>
       <c r="B225" s="2">
-        <v>26</v>
+        <v>6</v>
       </c>
     </row>
     <row r="226" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A226" s="1">
-        <v>97813</v>
+        <v>97499</v>
       </c>
       <c r="B226" s="2">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="227" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A227" s="1">
-        <v>97815</v>
+        <v>97504</v>
       </c>
       <c r="B227" s="2">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="228" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A228" s="1">
-        <v>97819</v>
+        <v>97797</v>
       </c>
       <c r="B228" s="2">
-        <v>2</v>
+        <v>39</v>
       </c>
     </row>
     <row r="229" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A229" s="1">
-        <v>97832</v>
+        <v>97798</v>
       </c>
       <c r="B229" s="2">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="230" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A230" s="1">
-        <v>97833</v>
+        <v>97799</v>
       </c>
       <c r="B230" s="2">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="231" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A231" s="1">
-        <v>97834</v>
+        <v>97800</v>
       </c>
       <c r="B231" s="2">
-        <v>4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="232" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A232" s="1">
-        <v>97836</v>
+        <v>97801</v>
       </c>
       <c r="B232" s="2">
-        <v>2</v>
+        <v>23</v>
       </c>
     </row>
     <row r="233" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A233" s="1">
-        <v>98279</v>
+        <v>97813</v>
       </c>
       <c r="B233" s="2">
         <v>1</v>
@@ -2305,58 +2311,58 @@
     </row>
     <row r="234" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A234" s="1">
-        <v>98288</v>
+        <v>97815</v>
       </c>
       <c r="B234" s="2">
-        <v>39</v>
+        <v>3</v>
       </c>
     </row>
     <row r="235" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A235" s="1">
-        <v>98289</v>
+        <v>97832</v>
       </c>
       <c r="B235" s="2">
-        <v>12</v>
+        <v>28</v>
       </c>
     </row>
     <row r="236" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A236" s="1">
-        <v>98290</v>
+        <v>97833</v>
       </c>
       <c r="B236" s="2">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="237" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A237" s="1">
-        <v>98307</v>
+        <v>98288</v>
       </c>
       <c r="B237" s="2">
-        <v>29</v>
+        <v>15</v>
       </c>
     </row>
     <row r="238" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A238" s="1">
-        <v>98308</v>
+        <v>98289</v>
       </c>
       <c r="B238" s="2">
-        <v>45</v>
+        <v>1</v>
       </c>
     </row>
     <row r="239" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A239" s="1">
-        <v>98309</v>
+        <v>98307</v>
       </c>
       <c r="B239" s="2">
-        <v>2</v>
+        <v>11</v>
       </c>
     </row>
     <row r="240" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A240" s="1">
-        <v>98310</v>
+        <v>98308</v>
       </c>
       <c r="B240" s="2">
-        <v>14</v>
+        <v>23</v>
       </c>
     </row>
     <row r="241" spans="1:2" x14ac:dyDescent="0.25">
@@ -2364,7 +2370,7 @@
         <v>98332</v>
       </c>
       <c r="B241" s="2">
-        <v>36</v>
+        <v>21</v>
       </c>
     </row>
     <row r="242" spans="1:2" x14ac:dyDescent="0.25">
@@ -2372,228 +2378,228 @@
         <v>98333</v>
       </c>
       <c r="B242" s="2">
-        <v>26</v>
+        <v>11</v>
       </c>
     </row>
     <row r="243" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A243" s="1">
-        <v>98334</v>
+        <v>98340</v>
       </c>
       <c r="B243" s="2">
-        <v>10</v>
+        <v>56</v>
       </c>
     </row>
     <row r="244" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A244" s="1">
-        <v>98340</v>
+        <v>98341</v>
       </c>
       <c r="B244" s="2">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="245" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A245" s="1">
-        <v>98341</v>
+        <v>98342</v>
       </c>
       <c r="B245" s="2">
-        <v>74</v>
+        <v>39</v>
       </c>
     </row>
     <row r="246" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A246" s="1">
-        <v>98342</v>
+        <v>98343</v>
       </c>
       <c r="B246" s="2">
-        <v>41</v>
+        <v>26</v>
       </c>
     </row>
     <row r="247" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A247" s="1">
-        <v>98343</v>
+        <v>98344</v>
       </c>
       <c r="B247" s="2">
-        <v>31</v>
+        <v>6</v>
       </c>
     </row>
     <row r="248" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A248" s="1">
-        <v>98344</v>
+        <v>98345</v>
       </c>
       <c r="B248" s="2">
-        <v>9</v>
+        <v>14</v>
       </c>
     </row>
     <row r="249" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A249" s="1">
-        <v>98345</v>
+        <v>98346</v>
       </c>
       <c r="B249" s="2">
-        <v>35</v>
+        <v>5</v>
       </c>
     </row>
     <row r="250" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A250" s="1">
-        <v>98346</v>
+        <v>98347</v>
       </c>
       <c r="B250" s="2">
-        <v>26</v>
+        <v>9</v>
       </c>
     </row>
     <row r="251" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A251" s="1">
-        <v>98347</v>
+        <v>98348</v>
       </c>
       <c r="B251" s="2">
-        <v>23</v>
+        <v>1</v>
       </c>
     </row>
     <row r="252" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A252" s="1">
-        <v>98348</v>
+        <v>98350</v>
       </c>
       <c r="B252" s="2">
-        <v>11</v>
+        <v>47</v>
       </c>
     </row>
     <row r="253" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A253" s="1">
-        <v>98349</v>
+        <v>98351</v>
       </c>
       <c r="B253" s="2">
-        <v>4</v>
+        <v>43</v>
       </c>
     </row>
     <row r="254" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A254" s="1">
-        <v>98350</v>
+        <v>98353</v>
       </c>
       <c r="B254" s="2">
-        <v>63</v>
+        <v>3</v>
       </c>
     </row>
     <row r="255" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A255" s="1">
-        <v>98351</v>
+        <v>98354</v>
       </c>
       <c r="B255" s="2">
-        <v>61</v>
+        <v>3</v>
       </c>
     </row>
     <row r="256" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A256" s="1">
-        <v>98352</v>
+        <v>98355</v>
       </c>
       <c r="B256" s="2">
-        <v>3</v>
+        <v>37</v>
       </c>
     </row>
     <row r="257" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A257" s="1">
-        <v>98353</v>
+        <v>98356</v>
       </c>
       <c r="B257" s="2">
-        <v>11</v>
+        <v>48</v>
       </c>
     </row>
     <row r="258" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A258" s="1">
-        <v>98354</v>
+        <v>98358</v>
       </c>
       <c r="B258" s="2">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="259" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A259" s="1">
-        <v>98355</v>
+        <v>98365</v>
       </c>
       <c r="B259" s="2">
-        <v>55</v>
+        <v>5</v>
       </c>
     </row>
     <row r="260" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A260" s="1">
-        <v>98356</v>
+        <v>98366</v>
       </c>
       <c r="B260" s="2">
-        <v>57</v>
+        <v>18</v>
       </c>
     </row>
     <row r="261" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A261" s="1">
-        <v>98358</v>
+        <v>98368</v>
       </c>
       <c r="B261" s="2">
-        <v>10</v>
+        <v>4</v>
       </c>
     </row>
     <row r="262" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A262" s="1">
-        <v>98361</v>
+        <v>98370</v>
       </c>
       <c r="B262" s="2">
-        <v>2</v>
+        <v>49</v>
       </c>
     </row>
     <row r="263" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A263" s="1">
-        <v>98365</v>
+        <v>98371</v>
       </c>
       <c r="B263" s="2">
-        <v>26</v>
+        <v>44</v>
       </c>
     </row>
     <row r="264" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A264" s="1">
-        <v>98366</v>
+        <v>98372</v>
       </c>
       <c r="B264" s="2">
-        <v>46</v>
+        <v>11</v>
       </c>
     </row>
     <row r="265" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A265" s="1">
-        <v>98367</v>
+        <v>98375</v>
       </c>
       <c r="B265" s="2">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="266" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A266" s="1">
-        <v>98368</v>
+        <v>98376</v>
       </c>
       <c r="B266" s="2">
-        <v>10</v>
+        <v>20</v>
       </c>
     </row>
     <row r="267" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A267" s="1">
-        <v>98370</v>
+        <v>98377</v>
       </c>
       <c r="B267" s="2">
-        <v>59</v>
+        <v>2</v>
       </c>
     </row>
     <row r="268" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A268" s="1">
-        <v>98371</v>
+        <v>98378</v>
       </c>
       <c r="B268" s="2">
-        <v>63</v>
+        <v>15</v>
       </c>
     </row>
     <row r="269" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A269" s="1">
-        <v>98372</v>
+        <v>98379</v>
       </c>
       <c r="B269" s="2">
-        <v>26</v>
+        <v>1</v>
       </c>
     </row>
     <row r="270" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A270" s="1">
-        <v>98374</v>
+        <v>98380</v>
       </c>
       <c r="B270" s="2">
         <v>4</v>
@@ -2601,727 +2607,727 @@
     </row>
     <row r="271" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A271" s="1">
-        <v>98375</v>
+        <v>98381</v>
       </c>
       <c r="B271" s="2">
-        <v>27</v>
+        <v>13</v>
       </c>
     </row>
     <row r="272" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A272" s="1">
-        <v>98376</v>
+        <v>98382</v>
       </c>
       <c r="B272" s="2">
-        <v>49</v>
+        <v>2</v>
       </c>
     </row>
     <row r="273" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A273" s="1">
-        <v>98377</v>
+        <v>98385</v>
       </c>
       <c r="B273" s="2">
-        <v>22</v>
+        <v>2</v>
       </c>
     </row>
     <row r="274" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A274" s="1">
-        <v>98378</v>
+        <v>98386</v>
       </c>
       <c r="B274" s="2">
-        <v>25</v>
+        <v>19</v>
       </c>
     </row>
     <row r="275" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A275" s="1">
-        <v>98379</v>
+        <v>98387</v>
       </c>
       <c r="B275" s="2">
-        <v>7</v>
+        <v>26</v>
       </c>
     </row>
     <row r="276" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A276" s="1">
-        <v>98380</v>
+        <v>98400</v>
       </c>
       <c r="B276" s="2">
-        <v>25</v>
+        <v>73</v>
       </c>
     </row>
     <row r="277" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A277" s="1">
-        <v>98381</v>
+        <v>98401</v>
       </c>
       <c r="B277" s="2">
-        <v>48</v>
+        <v>87</v>
       </c>
     </row>
     <row r="278" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A278" s="1">
-        <v>98382</v>
+        <v>98402</v>
       </c>
       <c r="B278" s="2">
-        <v>10</v>
+        <v>55</v>
       </c>
     </row>
     <row r="279" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A279" s="1">
-        <v>98385</v>
+        <v>98403</v>
       </c>
       <c r="B279" s="2">
-        <v>18</v>
+        <v>33</v>
       </c>
     </row>
     <row r="280" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A280" s="1">
-        <v>98386</v>
+        <v>98404</v>
       </c>
       <c r="B280" s="2">
-        <v>40</v>
+        <v>24</v>
       </c>
     </row>
     <row r="281" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A281" s="1">
-        <v>98387</v>
+        <v>98469</v>
       </c>
       <c r="B281" s="2">
-        <v>32</v>
+        <v>12</v>
       </c>
     </row>
     <row r="282" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A282" s="1">
-        <v>98396</v>
+        <v>98471</v>
       </c>
       <c r="B282" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="283" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A283" s="1">
-        <v>98451</v>
+        <v>98488</v>
       </c>
       <c r="B283" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="284" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A284" s="1">
-        <v>98464</v>
+        <v>98489</v>
       </c>
       <c r="B284" s="2">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="285" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A285" s="1">
-        <v>98465</v>
+        <v>98504</v>
       </c>
       <c r="B285" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="286" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A286" s="1">
-        <v>98469</v>
+        <v>98519</v>
       </c>
       <c r="B286" s="2">
-        <v>30</v>
+        <v>7</v>
       </c>
     </row>
     <row r="287" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A287" s="1">
-        <v>98471</v>
+        <v>98737</v>
       </c>
       <c r="B287" s="2">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="288" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A288" s="1">
-        <v>98488</v>
+        <v>98747</v>
       </c>
       <c r="B288" s="2">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="289" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A289" s="1">
-        <v>98489</v>
+        <v>98752</v>
       </c>
       <c r="B289" s="2">
-        <v>19</v>
+        <v>2</v>
       </c>
     </row>
     <row r="290" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A290" s="1">
-        <v>98503</v>
+        <v>20840</v>
       </c>
       <c r="B290" s="2">
-        <v>5</v>
+        <v>2436</v>
       </c>
     </row>
     <row r="291" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A291" s="1">
-        <v>98504</v>
+        <v>20841</v>
       </c>
       <c r="B291" s="2">
-        <v>10</v>
+        <v>587</v>
       </c>
     </row>
     <row r="292" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A292" s="1">
-        <v>98519</v>
+        <v>20846</v>
       </c>
       <c r="B292" s="2">
-        <v>28</v>
+        <v>156</v>
       </c>
     </row>
     <row r="293" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A293" s="1">
-        <v>98737</v>
+        <v>20847</v>
       </c>
       <c r="B293" s="2">
-        <v>1</v>
+        <v>136</v>
       </c>
     </row>
     <row r="294" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A294" s="1">
-        <v>98747</v>
+        <v>34299</v>
       </c>
       <c r="B294" s="2">
-        <v>1</v>
+        <v>608</v>
       </c>
     </row>
     <row r="295" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A295" s="1">
-        <v>98752</v>
+        <v>44701</v>
       </c>
       <c r="B295" s="2">
-        <v>2</v>
+        <v>212</v>
       </c>
     </row>
     <row r="296" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A296" s="1">
-        <v>20840</v>
+        <v>49926</v>
       </c>
       <c r="B296" s="2">
-        <v>2454</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="297" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A297" s="1">
-        <v>20841</v>
+        <v>53406</v>
       </c>
       <c r="B297" s="2">
-        <v>651</v>
+        <v>1728</v>
       </c>
     </row>
     <row r="298" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A298" s="1">
-        <v>20846</v>
+        <v>53407</v>
       </c>
       <c r="B298" s="2">
-        <v>162</v>
+        <v>3888</v>
       </c>
     </row>
     <row r="299" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A299" s="1">
-        <v>20847</v>
+        <v>53408</v>
       </c>
       <c r="B299" s="2">
-        <v>188</v>
+        <v>2592</v>
       </c>
     </row>
     <row r="300" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A300" s="1">
-        <v>34299</v>
+        <v>53410</v>
       </c>
       <c r="B300" s="2">
-        <v>636</v>
+        <v>1512</v>
       </c>
     </row>
     <row r="301" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A301" s="1">
-        <v>44701</v>
+        <v>58609</v>
       </c>
       <c r="B301" s="2">
-        <v>244</v>
+        <v>1728</v>
       </c>
     </row>
     <row r="302" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A302" s="1">
-        <v>69369</v>
+        <v>60971</v>
       </c>
       <c r="B302" s="2">
-        <v>48</v>
+        <v>1296</v>
       </c>
     </row>
     <row r="303" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A303" s="1">
-        <v>69372</v>
+        <v>64252</v>
       </c>
       <c r="B303" s="2">
-        <v>1500</v>
+        <v>3024</v>
       </c>
     </row>
     <row r="304" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A304" s="1">
-        <v>69373</v>
+        <v>65819</v>
       </c>
       <c r="B304" s="2">
-        <v>1860</v>
+        <v>1728</v>
       </c>
     </row>
     <row r="305" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A305" s="1">
-        <v>69380</v>
+        <v>68651</v>
       </c>
       <c r="B305" s="2">
-        <v>900</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="306" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A306" s="1">
-        <v>69382</v>
+        <v>69369</v>
       </c>
       <c r="B306" s="2">
-        <v>408</v>
+        <v>48</v>
       </c>
     </row>
     <row r="307" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A307" s="1">
-        <v>69389</v>
+        <v>69372</v>
       </c>
       <c r="B307" s="2">
-        <v>1524</v>
+        <v>1236</v>
       </c>
     </row>
     <row r="308" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A308" s="1">
-        <v>69948</v>
+        <v>69373</v>
       </c>
       <c r="B308" s="2">
-        <v>252</v>
+        <v>1644</v>
       </c>
     </row>
     <row r="309" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A309" s="1">
-        <v>69949</v>
+        <v>69380</v>
       </c>
       <c r="B309" s="2">
-        <v>60</v>
+        <v>588</v>
       </c>
     </row>
     <row r="310" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A310" s="1">
-        <v>74158</v>
+        <v>69382</v>
       </c>
       <c r="B310" s="2">
-        <v>516</v>
+        <v>120</v>
       </c>
     </row>
     <row r="311" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A311" s="1">
-        <v>83233</v>
+        <v>69389</v>
       </c>
       <c r="B311" s="2">
-        <v>352</v>
+        <v>1308</v>
       </c>
     </row>
     <row r="312" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A312" s="1">
-        <v>87534</v>
+        <v>69948</v>
       </c>
       <c r="B312" s="2">
-        <v>556</v>
+        <v>36</v>
       </c>
     </row>
     <row r="313" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A313" s="1">
-        <v>91732</v>
+        <v>69949</v>
       </c>
       <c r="B313" s="2">
-        <v>300</v>
+        <v>60</v>
       </c>
     </row>
     <row r="314" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A314" s="1">
-        <v>92742</v>
+        <v>74158</v>
       </c>
       <c r="B314" s="2">
-        <v>102</v>
+        <v>216</v>
       </c>
     </row>
     <row r="315" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A315" s="1">
-        <v>92767</v>
+        <v>74166</v>
       </c>
       <c r="B315" s="2">
-        <v>1788</v>
+        <v>1728</v>
       </c>
     </row>
     <row r="316" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A316" s="1">
-        <v>93027</v>
+        <v>74167</v>
       </c>
       <c r="B316" s="2">
-        <v>642</v>
+        <v>2160</v>
       </c>
     </row>
     <row r="317" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A317" s="1">
-        <v>93036</v>
+        <v>76530</v>
       </c>
       <c r="B317" s="2">
-        <v>156</v>
+        <v>200</v>
       </c>
     </row>
     <row r="318" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A318" s="1">
-        <v>93051</v>
+        <v>83232</v>
       </c>
       <c r="B318" s="2">
-        <v>548</v>
+        <v>2600</v>
       </c>
     </row>
     <row r="319" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A319" s="1">
-        <v>94355</v>
+        <v>83233</v>
       </c>
       <c r="B319" s="2">
-        <v>1700</v>
+        <v>136</v>
       </c>
     </row>
     <row r="320" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A320" s="1">
-        <v>94356</v>
+        <v>83234</v>
       </c>
       <c r="B320" s="2">
-        <v>2258</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="321" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A321" s="1">
-        <v>94357</v>
+        <v>83664</v>
       </c>
       <c r="B321" s="2">
-        <v>2668</v>
+        <v>960</v>
       </c>
     </row>
     <row r="322" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A322" s="1">
-        <v>94358</v>
+        <v>85652</v>
       </c>
       <c r="B322" s="2">
-        <v>2596</v>
+        <v>800</v>
       </c>
     </row>
     <row r="323" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A323" s="1">
-        <v>94404</v>
+        <v>86000</v>
       </c>
       <c r="B323" s="2">
-        <v>572</v>
+        <v>780</v>
       </c>
     </row>
     <row r="324" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A324" s="1">
-        <v>95667</v>
+        <v>87534</v>
       </c>
       <c r="B324" s="2">
-        <v>32</v>
+        <v>536</v>
       </c>
     </row>
     <row r="325" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A325" s="1">
-        <v>96519</v>
+        <v>88269</v>
       </c>
       <c r="B325" s="2">
-        <v>388</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="326" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A326" s="1">
-        <v>97126</v>
+        <v>88270</v>
       </c>
       <c r="B326" s="2">
-        <v>36</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="327" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A327" s="1">
-        <v>97127</v>
+        <v>88271</v>
       </c>
       <c r="B327" s="2">
-        <v>137</v>
+        <v>504</v>
       </c>
     </row>
     <row r="328" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A328" s="1">
-        <v>97129</v>
+        <v>88866</v>
       </c>
       <c r="B328" s="2">
-        <v>128</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="329" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A329" s="1">
-        <v>97131</v>
+        <v>89302</v>
       </c>
       <c r="B329" s="2">
-        <v>92</v>
+        <v>400</v>
       </c>
     </row>
     <row r="330" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A330" s="1">
-        <v>97133</v>
+        <v>89304</v>
       </c>
       <c r="B330" s="2">
-        <v>24</v>
+        <v>660</v>
       </c>
     </row>
     <row r="331" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A331" s="1">
-        <v>97552</v>
+        <v>91732</v>
       </c>
       <c r="B331" s="2">
-        <v>32</v>
+        <v>272</v>
       </c>
     </row>
     <row r="332" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A332" s="1">
-        <v>97553</v>
+        <v>92742</v>
       </c>
       <c r="B332" s="2">
-        <v>14</v>
+        <v>48</v>
       </c>
     </row>
     <row r="333" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A333" s="1">
-        <v>97554</v>
+        <v>92747</v>
       </c>
       <c r="B333" s="2">
-        <v>212</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="334" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A334" s="1">
-        <v>97559</v>
+        <v>92767</v>
       </c>
       <c r="B334" s="2">
-        <v>12</v>
+        <v>1776</v>
       </c>
     </row>
     <row r="335" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A335" s="1">
-        <v>97560</v>
+        <v>93027</v>
       </c>
       <c r="B335" s="2">
-        <v>32</v>
+        <v>627</v>
       </c>
     </row>
     <row r="336" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A336" s="1">
-        <v>97561</v>
+        <v>93036</v>
       </c>
       <c r="B336" s="2">
-        <v>44</v>
+        <v>136</v>
       </c>
     </row>
     <row r="337" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A337" s="1">
-        <v>97564</v>
+        <v>93051</v>
       </c>
       <c r="B337" s="2">
-        <v>27</v>
+        <v>524</v>
       </c>
     </row>
     <row r="338" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A338" s="1">
-        <v>97565</v>
+        <v>93057</v>
       </c>
       <c r="B338" s="2">
-        <v>12</v>
+        <v>1680</v>
       </c>
     </row>
     <row r="339" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A339" s="1">
-        <v>97566</v>
+        <v>94355</v>
       </c>
       <c r="B339" s="2">
-        <v>79</v>
+        <v>1688</v>
       </c>
     </row>
     <row r="340" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A340" s="1">
-        <v>97571</v>
+        <v>94356</v>
       </c>
       <c r="B340" s="2">
-        <v>48</v>
+        <v>2246</v>
       </c>
     </row>
     <row r="341" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A341" s="1">
-        <v>97573</v>
+        <v>94357</v>
       </c>
       <c r="B341" s="2">
-        <v>112</v>
+        <v>2612</v>
       </c>
     </row>
     <row r="342" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A342" s="1">
-        <v>97579</v>
+        <v>94358</v>
       </c>
       <c r="B342" s="2">
-        <v>8</v>
+        <v>2552</v>
       </c>
     </row>
     <row r="343" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A343" s="1">
-        <v>97580</v>
+        <v>94394</v>
       </c>
       <c r="B343" s="2">
-        <v>68</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="344" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A344" s="1">
-        <v>97581</v>
+        <v>94400</v>
       </c>
       <c r="B344" s="2">
-        <v>84</v>
+        <v>2520</v>
       </c>
     </row>
     <row r="345" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A345" s="1">
-        <v>97582</v>
+        <v>94402</v>
       </c>
       <c r="B345" s="2">
-        <v>120</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="346" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A346" s="1">
-        <v>97583</v>
+        <v>94404</v>
       </c>
       <c r="B346" s="2">
-        <v>152</v>
+        <v>508</v>
       </c>
     </row>
     <row r="347" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A347" s="1">
-        <v>97584</v>
+        <v>95590</v>
       </c>
       <c r="B347" s="2">
-        <v>92</v>
+        <v>1312</v>
       </c>
     </row>
     <row r="348" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A348" s="1">
-        <v>97585</v>
+        <v>95591</v>
       </c>
       <c r="B348" s="2">
-        <v>132</v>
+        <v>896</v>
       </c>
     </row>
     <row r="349" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A349" s="1">
-        <v>97586</v>
+        <v>95592</v>
       </c>
       <c r="B349" s="2">
-        <v>124</v>
+        <v>3600</v>
       </c>
     </row>
     <row r="350" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A350" s="1">
-        <v>97588</v>
+        <v>95667</v>
       </c>
       <c r="B350" s="2">
-        <v>28</v>
+        <v>12</v>
       </c>
     </row>
     <row r="351" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A351" s="1">
-        <v>97596</v>
+        <v>96435</v>
       </c>
       <c r="B351" s="2">
-        <v>252</v>
+        <v>588</v>
       </c>
     </row>
     <row r="352" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A352" s="1">
-        <v>97598</v>
+        <v>96436</v>
       </c>
       <c r="B352" s="2">
-        <v>30</v>
+        <v>624</v>
       </c>
     </row>
     <row r="353" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A353" s="1">
-        <v>97599</v>
+        <v>96439</v>
       </c>
       <c r="B353" s="2">
-        <v>3</v>
+        <v>240</v>
       </c>
     </row>
     <row r="354" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A354" s="1">
-        <v>97600</v>
+        <v>96440</v>
       </c>
       <c r="B354" s="2">
-        <v>90</v>
+        <v>240</v>
       </c>
     </row>
     <row r="355" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A355" s="1">
-        <v>97624</v>
+        <v>96441</v>
       </c>
       <c r="B355" s="2">
-        <v>143</v>
+        <v>192</v>
       </c>
     </row>
     <row r="356" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A356" s="1">
-        <v>97625</v>
+        <v>96519</v>
       </c>
       <c r="B356" s="2">
-        <v>40</v>
+        <v>360</v>
       </c>
     </row>
     <row r="357" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A357" s="1">
-        <v>97626</v>
+        <v>97126</v>
       </c>
       <c r="B357" s="2">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="358" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A358" s="1">
-        <v>97627</v>
+        <v>97127</v>
       </c>
       <c r="B358" s="2">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="359" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A359" s="1">
-        <v>97628</v>
+        <v>97129</v>
       </c>
       <c r="B359" s="2">
-        <v>8</v>
+        <v>56</v>
       </c>
     </row>
     <row r="360" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A360" s="1">
-        <v>97653</v>
+        <v>97131</v>
       </c>
       <c r="B360" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="361" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A361" s="1">
-        <v>97654</v>
+        <v>97133</v>
       </c>
       <c r="B361" s="2">
         <v>4</v>
@@ -3329,1663 +3335,1663 @@
     </row>
     <row r="362" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A362" s="1">
-        <v>97881</v>
+        <v>97552</v>
       </c>
       <c r="B362" s="2">
-        <v>360</v>
+        <v>20</v>
       </c>
     </row>
     <row r="363" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A363" s="1">
-        <v>97882</v>
+        <v>97553</v>
       </c>
       <c r="B363" s="2">
-        <v>324</v>
+        <v>4</v>
       </c>
     </row>
     <row r="364" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A364" s="1">
-        <v>98217</v>
+        <v>97554</v>
       </c>
       <c r="B364" s="2">
-        <v>160</v>
+        <v>180</v>
       </c>
     </row>
     <row r="365" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A365" s="1">
-        <v>98218</v>
+        <v>97559</v>
       </c>
       <c r="B365" s="2">
-        <v>84</v>
+        <v>12</v>
       </c>
     </row>
     <row r="366" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A366" s="1">
-        <v>98219</v>
+        <v>97560</v>
       </c>
       <c r="B366" s="2">
-        <v>88</v>
+        <v>24</v>
       </c>
     </row>
     <row r="367" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A367" s="1">
-        <v>98222</v>
+        <v>97561</v>
       </c>
       <c r="B367" s="2">
-        <v>32</v>
+        <v>44</v>
       </c>
     </row>
     <row r="368" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A368" s="1">
-        <v>98225</v>
+        <v>97564</v>
       </c>
       <c r="B368" s="2">
-        <v>4</v>
+        <v>15</v>
       </c>
     </row>
     <row r="369" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A369" s="1">
-        <v>98227</v>
+        <v>97565</v>
       </c>
       <c r="B369" s="2">
-        <v>104</v>
+        <v>12</v>
       </c>
     </row>
     <row r="370" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A370" s="1">
-        <v>98229</v>
+        <v>97566</v>
       </c>
       <c r="B370" s="2">
-        <v>8</v>
+        <v>40</v>
       </c>
     </row>
     <row r="371" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A371" s="1">
-        <v>98233</v>
+        <v>97571</v>
       </c>
       <c r="B371" s="2">
-        <v>96</v>
+        <v>14</v>
       </c>
     </row>
     <row r="372" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A372" s="1">
-        <v>98538</v>
+        <v>97573</v>
       </c>
       <c r="B372" s="2">
-        <v>42</v>
+        <v>68</v>
       </c>
     </row>
     <row r="373" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A373" s="1">
-        <v>98581</v>
+        <v>97580</v>
       </c>
       <c r="B373" s="2">
-        <v>64</v>
+        <v>36</v>
       </c>
     </row>
     <row r="374" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A374" s="1">
-        <v>98582</v>
+        <v>97581</v>
       </c>
       <c r="B374" s="2">
-        <v>44</v>
+        <v>60</v>
       </c>
     </row>
     <row r="375" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A375" s="1">
-        <v>98583</v>
+        <v>97582</v>
       </c>
       <c r="B375" s="2">
-        <v>60</v>
+        <v>96</v>
       </c>
     </row>
     <row r="376" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A376" s="1">
-        <v>98584</v>
+        <v>97583</v>
       </c>
       <c r="B376" s="2">
-        <v>60</v>
+        <v>140</v>
       </c>
     </row>
     <row r="377" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A377" s="1">
-        <v>98585</v>
+        <v>97584</v>
       </c>
       <c r="B377" s="2">
-        <v>56</v>
+        <v>76</v>
       </c>
     </row>
     <row r="378" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A378" s="1">
-        <v>98587</v>
+        <v>97585</v>
       </c>
       <c r="B378" s="2">
-        <v>72</v>
+        <v>116</v>
       </c>
     </row>
     <row r="379" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A379" s="1">
-        <v>98626</v>
+        <v>97586</v>
       </c>
       <c r="B379" s="2">
-        <v>90</v>
+        <v>84</v>
       </c>
     </row>
     <row r="380" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A380" s="1">
-        <v>98627</v>
+        <v>97588</v>
       </c>
       <c r="B380" s="2">
-        <v>72</v>
+        <v>14</v>
       </c>
     </row>
     <row r="381" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A381" s="1">
-        <v>98628</v>
+        <v>97596</v>
       </c>
       <c r="B381" s="2">
-        <v>72</v>
+        <v>60</v>
       </c>
     </row>
     <row r="382" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A382" s="1">
-        <v>98629</v>
+        <v>97598</v>
       </c>
       <c r="B382" s="2">
-        <v>111</v>
+        <v>12</v>
       </c>
     </row>
     <row r="383" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A383" s="1">
-        <v>98630</v>
+        <v>97600</v>
       </c>
       <c r="B383" s="2">
-        <v>15</v>
+        <v>69</v>
       </c>
     </row>
     <row r="384" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A384" s="1">
-        <v>98631</v>
+        <v>97624</v>
       </c>
       <c r="B384" s="2">
-        <v>75</v>
+        <v>131</v>
       </c>
     </row>
     <row r="385" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A385" s="1">
-        <v>98632</v>
+        <v>97625</v>
       </c>
       <c r="B385" s="2">
-        <v>60</v>
+        <v>39</v>
       </c>
     </row>
     <row r="386" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A386" s="1">
-        <v>98634</v>
+        <v>97626</v>
       </c>
       <c r="B386" s="2">
-        <v>28</v>
+        <v>9</v>
       </c>
     </row>
     <row r="387" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A387" s="1">
-        <v>7722</v>
+        <v>97627</v>
       </c>
       <c r="B387" s="2">
-        <v>828</v>
+        <v>40</v>
       </c>
     </row>
     <row r="388" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A388" s="1">
-        <v>33427</v>
+        <v>97628</v>
       </c>
       <c r="B388" s="2">
-        <v>268</v>
+        <v>6</v>
       </c>
     </row>
     <row r="389" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A389" s="1">
-        <v>59285</v>
+        <v>97653</v>
       </c>
       <c r="B389" s="2">
-        <v>34</v>
+        <v>78</v>
       </c>
     </row>
     <row r="390" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A390" s="1">
-        <v>78372</v>
+        <v>97654</v>
       </c>
       <c r="B390" s="2">
-        <v>700</v>
+        <v>4</v>
       </c>
     </row>
     <row r="391" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A391" s="1">
-        <v>84540</v>
+        <v>97881</v>
       </c>
       <c r="B391" s="2">
-        <v>3799</v>
+        <v>340</v>
       </c>
     </row>
     <row r="392" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A392" s="1">
-        <v>89097</v>
+        <v>97882</v>
       </c>
       <c r="B392" s="2">
-        <v>467</v>
+        <v>304</v>
       </c>
     </row>
     <row r="393" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A393" s="1">
-        <v>92811</v>
+        <v>98217</v>
       </c>
       <c r="B393" s="2">
-        <v>1526</v>
+        <v>104</v>
       </c>
     </row>
     <row r="394" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A394" s="1">
-        <v>94746</v>
+        <v>98218</v>
       </c>
       <c r="B394" s="2">
-        <v>438</v>
+        <v>36</v>
       </c>
     </row>
     <row r="395" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A395" s="1">
-        <v>95346</v>
+        <v>98219</v>
       </c>
       <c r="B395" s="2">
-        <v>666</v>
+        <v>12</v>
       </c>
     </row>
     <row r="396" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A396" s="1">
-        <v>95588</v>
+        <v>98222</v>
       </c>
       <c r="B396" s="2">
-        <v>3480</v>
+        <v>12</v>
       </c>
     </row>
     <row r="397" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A397" s="1">
-        <v>95795</v>
+        <v>98227</v>
       </c>
       <c r="B397" s="2">
-        <v>214</v>
+        <v>52</v>
       </c>
     </row>
     <row r="398" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A398" s="1">
-        <v>96984</v>
+        <v>98233</v>
       </c>
       <c r="B398" s="2">
-        <v>2240</v>
+        <v>24</v>
       </c>
     </row>
     <row r="399" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A399" s="1">
-        <v>96985</v>
+        <v>98581</v>
       </c>
       <c r="B399" s="2">
-        <v>2144</v>
+        <v>20</v>
       </c>
     </row>
     <row r="400" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A400" s="1">
-        <v>96986</v>
+        <v>98582</v>
       </c>
       <c r="B400" s="2">
-        <v>1728</v>
+        <v>8</v>
       </c>
     </row>
     <row r="401" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A401" s="1">
-        <v>96989</v>
+        <v>98583</v>
       </c>
       <c r="B401" s="2">
-        <v>784</v>
+        <v>20</v>
       </c>
     </row>
     <row r="402" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A402" s="1">
-        <v>97662</v>
+        <v>98584</v>
       </c>
       <c r="B402" s="2">
-        <v>390</v>
+        <v>12</v>
       </c>
     </row>
     <row r="403" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A403" s="1">
-        <v>97663</v>
+        <v>98585</v>
       </c>
       <c r="B403" s="2">
-        <v>460</v>
+        <v>24</v>
       </c>
     </row>
     <row r="404" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A404" s="1">
-        <v>97664</v>
+        <v>98587</v>
       </c>
       <c r="B404" s="2">
-        <v>420</v>
+        <v>28</v>
       </c>
     </row>
     <row r="405" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A405" s="1">
-        <v>97665</v>
+        <v>98626</v>
       </c>
       <c r="B405" s="2">
-        <v>3350</v>
+        <v>33</v>
       </c>
     </row>
     <row r="406" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A406" s="1">
-        <v>98437</v>
+        <v>98627</v>
       </c>
       <c r="B406" s="2">
-        <v>80</v>
+        <v>27</v>
       </c>
     </row>
     <row r="407" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A407" s="1">
-        <v>98441</v>
+        <v>98628</v>
       </c>
       <c r="B407" s="2">
-        <v>8</v>
+        <v>18</v>
       </c>
     </row>
     <row r="408" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A408" s="1">
-        <v>98443</v>
+        <v>98629</v>
       </c>
       <c r="B408" s="2">
-        <v>12</v>
+        <v>81</v>
       </c>
     </row>
     <row r="409" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A409" s="1">
-        <v>98445</v>
+        <v>98631</v>
       </c>
       <c r="B409" s="2">
-        <v>8</v>
+        <v>51</v>
       </c>
     </row>
     <row r="410" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A410" s="1">
-        <v>98540</v>
+        <v>98632</v>
       </c>
       <c r="B410" s="2">
-        <v>90</v>
+        <v>28</v>
       </c>
     </row>
     <row r="411" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A411" s="1">
-        <v>98541</v>
+        <v>98634</v>
       </c>
       <c r="B411" s="2">
-        <v>70</v>
+        <v>28</v>
       </c>
     </row>
     <row r="412" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A412" s="1">
-        <v>99273</v>
+        <v>7722</v>
       </c>
       <c r="B412" s="2">
-        <v>1024</v>
+        <v>780</v>
       </c>
     </row>
     <row r="413" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A413" s="1">
-        <v>99275</v>
+        <v>33427</v>
       </c>
       <c r="B413" s="2">
-        <v>1696</v>
+        <v>148</v>
       </c>
     </row>
     <row r="414" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A414" s="1">
-        <v>9646</v>
+        <v>59285</v>
       </c>
       <c r="B414" s="2">
-        <v>612</v>
+        <v>20</v>
       </c>
     </row>
     <row r="415" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A415" s="1">
-        <v>24874</v>
+        <v>78372</v>
       </c>
       <c r="B415" s="2">
-        <v>1601</v>
+        <v>580</v>
       </c>
     </row>
     <row r="416" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A416" s="1">
-        <v>34094</v>
+        <v>78641</v>
       </c>
       <c r="B416" s="2">
-        <v>4048</v>
+        <v>888</v>
       </c>
     </row>
     <row r="417" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A417" s="1">
-        <v>53546</v>
+        <v>84540</v>
       </c>
       <c r="B417" s="2">
-        <v>1118</v>
+        <v>3459</v>
       </c>
     </row>
     <row r="418" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A418" s="1">
-        <v>59014</v>
+        <v>89097</v>
       </c>
       <c r="B418" s="2">
-        <v>488</v>
+        <v>431</v>
       </c>
     </row>
     <row r="419" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A419" s="1">
-        <v>66663</v>
+        <v>92811</v>
       </c>
       <c r="B419" s="2">
-        <v>470</v>
+        <v>1480</v>
       </c>
     </row>
     <row r="420" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A420" s="1">
-        <v>70620</v>
+        <v>94746</v>
       </c>
       <c r="B420" s="2">
-        <v>522</v>
+        <v>162</v>
       </c>
     </row>
     <row r="421" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A421" s="1">
-        <v>70653</v>
+        <v>95346</v>
       </c>
       <c r="B421" s="2">
-        <v>2250</v>
+        <v>492</v>
       </c>
     </row>
     <row r="422" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A422" s="1">
-        <v>74779</v>
+        <v>95588</v>
       </c>
       <c r="B422" s="2">
-        <v>724</v>
+        <v>2730</v>
       </c>
     </row>
     <row r="423" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A423" s="1">
-        <v>75922</v>
+        <v>95795</v>
       </c>
       <c r="B423" s="2">
-        <v>60</v>
+        <v>94</v>
       </c>
     </row>
     <row r="424" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A424" s="1">
-        <v>75923</v>
+        <v>96377</v>
       </c>
       <c r="B424" s="2">
-        <v>210</v>
+        <v>308</v>
       </c>
     </row>
     <row r="425" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A425" s="1">
-        <v>75924</v>
+        <v>96984</v>
       </c>
       <c r="B425" s="2">
-        <v>288</v>
+        <v>1596</v>
       </c>
     </row>
     <row r="426" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A426" s="1">
-        <v>76063</v>
+        <v>96985</v>
       </c>
       <c r="B426" s="2">
-        <v>76</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="427" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A427" s="1">
-        <v>76064</v>
+        <v>96986</v>
       </c>
       <c r="B427" s="2">
-        <v>74</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="428" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A428" s="1">
-        <v>76065</v>
+        <v>96989</v>
       </c>
       <c r="B428" s="2">
-        <v>568</v>
+        <v>720</v>
       </c>
     </row>
     <row r="429" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A429" s="1">
-        <v>76066</v>
+        <v>97662</v>
       </c>
       <c r="B429" s="2">
-        <v>610</v>
+        <v>130</v>
       </c>
     </row>
     <row r="430" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A430" s="1">
-        <v>76067</v>
+        <v>97663</v>
       </c>
       <c r="B430" s="2">
-        <v>412</v>
+        <v>330</v>
       </c>
     </row>
     <row r="431" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A431" s="1">
-        <v>77697</v>
+        <v>97664</v>
       </c>
       <c r="B431" s="2">
-        <v>254</v>
+        <v>310</v>
       </c>
     </row>
     <row r="432" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A432" s="1">
-        <v>78625</v>
+        <v>97665</v>
       </c>
       <c r="B432" s="2">
-        <v>44</v>
+        <v>3050</v>
       </c>
     </row>
     <row r="433" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A433" s="1">
-        <v>81763</v>
+        <v>98437</v>
       </c>
       <c r="B433" s="2">
-        <v>582</v>
+        <v>28</v>
       </c>
     </row>
     <row r="434" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A434" s="1">
-        <v>81764</v>
+        <v>98445</v>
       </c>
       <c r="B434" s="2">
-        <v>430</v>
+        <v>4</v>
       </c>
     </row>
     <row r="435" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A435" s="1">
-        <v>81765</v>
+        <v>98540</v>
       </c>
       <c r="B435" s="2">
-        <v>1112</v>
+        <v>30</v>
       </c>
     </row>
     <row r="436" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A436" s="1">
-        <v>83163</v>
+        <v>98541</v>
       </c>
       <c r="B436" s="2">
-        <v>1422</v>
+        <v>20</v>
       </c>
     </row>
     <row r="437" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A437" s="1">
-        <v>84801</v>
+        <v>99273</v>
       </c>
       <c r="B437" s="2">
-        <v>36</v>
+        <v>424</v>
       </c>
     </row>
     <row r="438" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A438" s="1">
-        <v>84802</v>
+        <v>99275</v>
       </c>
       <c r="B438" s="2">
-        <v>152</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="439" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A439" s="1">
-        <v>87263</v>
+        <v>9646</v>
       </c>
       <c r="B439" s="2">
-        <v>150</v>
+        <v>2448</v>
       </c>
     </row>
     <row r="440" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A440" s="1">
-        <v>87325</v>
+        <v>24874</v>
       </c>
       <c r="B440" s="2">
-        <v>426</v>
+        <v>1413</v>
       </c>
     </row>
     <row r="441" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A441" s="1">
-        <v>87326</v>
+        <v>34094</v>
       </c>
       <c r="B441" s="2">
-        <v>432</v>
+        <v>3558</v>
       </c>
     </row>
     <row r="442" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A442" s="1">
-        <v>87635</v>
+        <v>53546</v>
       </c>
       <c r="B442" s="2">
-        <v>756</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="443" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A443" s="1">
-        <v>87901</v>
+        <v>59014</v>
       </c>
       <c r="B443" s="2">
-        <v>1305</v>
+        <v>334</v>
       </c>
     </row>
     <row r="444" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A444" s="1">
-        <v>87903</v>
+        <v>66663</v>
       </c>
       <c r="B444" s="2">
-        <v>146</v>
+        <v>344</v>
       </c>
     </row>
     <row r="445" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A445" s="1">
-        <v>88350</v>
+        <v>68463</v>
       </c>
       <c r="B445" s="2">
-        <v>584</v>
+        <v>928</v>
       </c>
     </row>
     <row r="446" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A446" s="1">
-        <v>88360</v>
+        <v>70620</v>
       </c>
       <c r="B446" s="2">
-        <v>566</v>
+        <v>380</v>
       </c>
     </row>
     <row r="447" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A447" s="1">
-        <v>88400</v>
+        <v>70653</v>
       </c>
       <c r="B447" s="2">
-        <v>948</v>
+        <v>2234</v>
       </c>
     </row>
     <row r="448" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A448" s="1">
-        <v>90109</v>
+        <v>74779</v>
       </c>
       <c r="B448" s="2">
-        <v>719</v>
+        <v>594</v>
       </c>
     </row>
     <row r="449" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A449" s="1">
-        <v>90497</v>
+        <v>75922</v>
       </c>
       <c r="B449" s="2">
-        <v>112</v>
+        <v>544</v>
       </c>
     </row>
     <row r="450" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A450" s="1">
-        <v>91653</v>
+        <v>75923</v>
       </c>
       <c r="B450" s="2">
-        <v>488</v>
+        <v>168</v>
       </c>
     </row>
     <row r="451" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A451" s="1">
-        <v>91678</v>
+        <v>75924</v>
       </c>
       <c r="B451" s="2">
-        <v>256</v>
+        <v>230</v>
       </c>
     </row>
     <row r="452" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A452" s="1">
-        <v>92172</v>
+        <v>76063</v>
       </c>
       <c r="B452" s="2">
-        <v>922</v>
+        <v>12</v>
       </c>
     </row>
     <row r="453" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A453" s="1">
-        <v>92176</v>
+        <v>76064</v>
       </c>
       <c r="B453" s="2">
-        <v>1224</v>
+        <v>16</v>
       </c>
     </row>
     <row r="454" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A454" s="1">
-        <v>92815</v>
+        <v>76065</v>
       </c>
       <c r="B454" s="2">
-        <v>186</v>
+        <v>430</v>
       </c>
     </row>
     <row r="455" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A455" s="1">
-        <v>92822</v>
+        <v>76066</v>
       </c>
       <c r="B455" s="2">
-        <v>200</v>
+        <v>460</v>
       </c>
     </row>
     <row r="456" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A456" s="1">
-        <v>92823</v>
+        <v>76067</v>
       </c>
       <c r="B456" s="2">
-        <v>170</v>
+        <v>300</v>
       </c>
     </row>
     <row r="457" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A457" s="1">
-        <v>92836</v>
+        <v>77697</v>
       </c>
       <c r="B457" s="2">
-        <v>104</v>
+        <v>86</v>
       </c>
     </row>
     <row r="458" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A458" s="1">
-        <v>92984</v>
+        <v>78624</v>
       </c>
       <c r="B458" s="2">
-        <v>18</v>
+        <v>552</v>
       </c>
     </row>
     <row r="459" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A459" s="1">
-        <v>93067</v>
+        <v>78625</v>
       </c>
       <c r="B459" s="2">
-        <v>760</v>
+        <v>558</v>
       </c>
     </row>
     <row r="460" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A460" s="1">
-        <v>93073</v>
+        <v>78626</v>
       </c>
       <c r="B460" s="2">
-        <v>893</v>
+        <v>552</v>
       </c>
     </row>
     <row r="461" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A461" s="1">
-        <v>94233</v>
+        <v>78627</v>
       </c>
       <c r="B461" s="2">
-        <v>500</v>
+        <v>596</v>
       </c>
     </row>
     <row r="462" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A462" s="1">
-        <v>94314</v>
+        <v>78628</v>
       </c>
       <c r="B462" s="2">
-        <v>558</v>
+        <v>552</v>
       </c>
     </row>
     <row r="463" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A463" s="1">
-        <v>94317</v>
+        <v>78629</v>
       </c>
       <c r="B463" s="2">
-        <v>1318</v>
+        <v>552</v>
       </c>
     </row>
     <row r="464" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A464" s="1">
-        <v>94821</v>
+        <v>78630</v>
       </c>
       <c r="B464" s="2">
-        <v>772</v>
+        <v>552</v>
       </c>
     </row>
     <row r="465" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A465" s="1">
-        <v>94830</v>
+        <v>78631</v>
       </c>
       <c r="B465" s="2">
-        <v>306</v>
+        <v>552</v>
       </c>
     </row>
     <row r="466" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A466" s="1">
-        <v>95020</v>
+        <v>78633</v>
       </c>
       <c r="B466" s="2">
-        <v>958</v>
+        <v>564</v>
       </c>
     </row>
     <row r="467" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A467" s="1">
-        <v>95021</v>
+        <v>78634</v>
       </c>
       <c r="B467" s="2">
-        <v>778</v>
+        <v>552</v>
       </c>
     </row>
     <row r="468" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A468" s="1">
-        <v>95202</v>
+        <v>78635</v>
       </c>
       <c r="B468" s="2">
-        <v>136</v>
+        <v>552</v>
       </c>
     </row>
     <row r="469" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A469" s="1">
-        <v>95211</v>
+        <v>81763</v>
       </c>
       <c r="B469" s="2">
-        <v>202</v>
+        <v>482</v>
       </c>
     </row>
     <row r="470" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A470" s="1">
-        <v>95536</v>
+        <v>81764</v>
       </c>
       <c r="B470" s="2">
-        <v>828</v>
+        <v>370</v>
       </c>
     </row>
     <row r="471" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A471" s="1">
-        <v>95538</v>
+        <v>81765</v>
       </c>
       <c r="B471" s="2">
-        <v>996</v>
+        <v>976</v>
       </c>
     </row>
     <row r="472" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A472" s="1">
-        <v>95715</v>
+        <v>83163</v>
       </c>
       <c r="B472" s="2">
-        <v>978</v>
+        <v>1338</v>
       </c>
     </row>
     <row r="473" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A473" s="1">
-        <v>95731</v>
+        <v>83184</v>
       </c>
       <c r="B473" s="2">
-        <v>222</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="474" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A474" s="1">
-        <v>95732</v>
+        <v>84801</v>
       </c>
       <c r="B474" s="2">
-        <v>272</v>
+        <v>10</v>
       </c>
     </row>
     <row r="475" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A475" s="1">
-        <v>95765</v>
+        <v>84802</v>
       </c>
       <c r="B475" s="2">
-        <v>426</v>
+        <v>772</v>
       </c>
     </row>
     <row r="476" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A476" s="1">
-        <v>95768</v>
+        <v>87263</v>
       </c>
       <c r="B476" s="2">
-        <v>216</v>
+        <v>92</v>
       </c>
     </row>
     <row r="477" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A477" s="1">
-        <v>95769</v>
+        <v>87325</v>
       </c>
       <c r="B477" s="2">
-        <v>696</v>
+        <v>318</v>
       </c>
     </row>
     <row r="478" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A478" s="1">
-        <v>95770</v>
+        <v>87326</v>
       </c>
       <c r="B478" s="2">
-        <v>222</v>
+        <v>292</v>
       </c>
     </row>
     <row r="479" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A479" s="1">
-        <v>95772</v>
+        <v>87635</v>
       </c>
       <c r="B479" s="2">
-        <v>320</v>
+        <v>468</v>
       </c>
     </row>
     <row r="480" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A480" s="1">
-        <v>95774</v>
+        <v>87901</v>
       </c>
       <c r="B480" s="2">
-        <v>292</v>
+        <v>1175</v>
       </c>
     </row>
     <row r="481" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A481" s="1">
-        <v>95781</v>
+        <v>87903</v>
       </c>
       <c r="B481" s="2">
-        <v>362</v>
+        <v>124</v>
       </c>
     </row>
     <row r="482" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A482" s="1">
-        <v>95911</v>
+        <v>88350</v>
       </c>
       <c r="B482" s="2">
-        <v>85</v>
+        <v>528</v>
       </c>
     </row>
     <row r="483" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A483" s="1">
-        <v>96507</v>
+        <v>88360</v>
       </c>
       <c r="B483" s="2">
-        <v>136</v>
+        <v>430</v>
       </c>
     </row>
     <row r="484" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A484" s="1">
-        <v>96508</v>
+        <v>88400</v>
       </c>
       <c r="B484" s="2">
-        <v>518</v>
+        <v>840</v>
       </c>
     </row>
     <row r="485" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A485" s="1">
-        <v>96510</v>
+        <v>90109</v>
       </c>
       <c r="B485" s="2">
-        <v>166</v>
+        <v>599</v>
       </c>
     </row>
     <row r="486" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A486" s="1">
-        <v>96517</v>
+        <v>90497</v>
       </c>
       <c r="B486" s="2">
-        <v>74</v>
+        <v>60</v>
       </c>
     </row>
     <row r="487" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A487" s="1">
-        <v>96539</v>
+        <v>91653</v>
       </c>
       <c r="B487" s="2">
-        <v>132</v>
+        <v>406</v>
       </c>
     </row>
     <row r="488" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A488" s="1">
-        <v>97066</v>
+        <v>91665</v>
       </c>
       <c r="B488" s="2">
-        <v>280</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="489" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A489" s="1">
-        <v>97067</v>
+        <v>91678</v>
       </c>
       <c r="B489" s="2">
-        <v>400</v>
+        <v>144</v>
       </c>
     </row>
     <row r="490" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A490" s="1">
-        <v>97245</v>
+        <v>92172</v>
       </c>
       <c r="B490" s="2">
-        <v>1868</v>
+        <v>724</v>
       </c>
     </row>
     <row r="491" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A491" s="1">
-        <v>97701</v>
+        <v>92176</v>
       </c>
       <c r="B491" s="2">
-        <v>40</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="492" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A492" s="1">
-        <v>97702</v>
+        <v>92636</v>
       </c>
       <c r="B492" s="2">
-        <v>20</v>
+        <v>914</v>
       </c>
     </row>
     <row r="493" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A493" s="1">
-        <v>97703</v>
+        <v>92815</v>
       </c>
       <c r="B493" s="2">
-        <v>130</v>
+        <v>64</v>
       </c>
     </row>
     <row r="494" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A494" s="1">
-        <v>97711</v>
+        <v>92822</v>
       </c>
       <c r="B494" s="2">
-        <v>28</v>
+        <v>190</v>
       </c>
     </row>
     <row r="495" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A495" s="1">
-        <v>97712</v>
+        <v>92823</v>
       </c>
       <c r="B495" s="2">
-        <v>4</v>
+        <v>148</v>
       </c>
     </row>
     <row r="496" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A496" s="1">
-        <v>97715</v>
+        <v>92836</v>
       </c>
       <c r="B496" s="2">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row r="497" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A497" s="1">
-        <v>97717</v>
+        <v>92999</v>
       </c>
       <c r="B497" s="2">
-        <v>110</v>
+        <v>1818</v>
       </c>
     </row>
     <row r="498" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A498" s="1">
-        <v>97720</v>
+        <v>93067</v>
       </c>
       <c r="B498" s="2">
-        <v>62</v>
+        <v>664</v>
       </c>
     </row>
     <row r="499" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A499" s="1">
-        <v>97723</v>
+        <v>93073</v>
       </c>
       <c r="B499" s="2">
-        <v>28</v>
+        <v>762</v>
       </c>
     </row>
     <row r="500" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A500" s="1">
-        <v>97725</v>
+        <v>94233</v>
       </c>
       <c r="B500" s="2">
-        <v>30</v>
+        <v>498</v>
       </c>
     </row>
     <row r="501" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A501" s="1">
-        <v>97727</v>
+        <v>94314</v>
       </c>
       <c r="B501" s="2">
-        <v>22</v>
+        <v>466</v>
       </c>
     </row>
     <row r="502" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A502" s="1">
-        <v>97735</v>
+        <v>94317</v>
       </c>
       <c r="B502" s="2">
-        <v>8</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="503" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A503" s="1">
-        <v>97744</v>
+        <v>94821</v>
       </c>
       <c r="B503" s="2">
-        <v>56</v>
+        <v>712</v>
       </c>
     </row>
     <row r="504" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A504" s="1">
-        <v>97750</v>
+        <v>94830</v>
       </c>
       <c r="B504" s="2">
-        <v>22</v>
+        <v>182</v>
       </c>
     </row>
     <row r="505" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A505" s="1">
-        <v>97756</v>
+        <v>95020</v>
       </c>
       <c r="B505" s="2">
-        <v>128</v>
+        <v>762</v>
       </c>
     </row>
     <row r="506" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A506" s="1">
-        <v>97768</v>
+        <v>95021</v>
       </c>
       <c r="B506" s="2">
-        <v>84</v>
+        <v>458</v>
       </c>
     </row>
     <row r="507" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A507" s="1">
-        <v>97784</v>
+        <v>95202</v>
       </c>
       <c r="B507" s="2">
-        <v>26</v>
+        <v>94</v>
       </c>
     </row>
     <row r="508" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A508" s="1">
-        <v>97785</v>
+        <v>95211</v>
       </c>
       <c r="B508" s="2">
-        <v>66</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="509" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A509" s="1">
-        <v>97788</v>
+        <v>95536</v>
       </c>
       <c r="B509" s="2">
-        <v>102</v>
+        <v>754</v>
       </c>
     </row>
     <row r="510" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A510" s="1">
-        <v>97790</v>
+        <v>95538</v>
       </c>
       <c r="B510" s="2">
-        <v>56</v>
+        <v>938</v>
       </c>
     </row>
     <row r="511" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A511" s="1">
-        <v>97791</v>
+        <v>95715</v>
       </c>
       <c r="B511" s="2">
-        <v>38</v>
+        <v>894</v>
       </c>
     </row>
     <row r="512" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A512" s="1">
-        <v>97792</v>
+        <v>95731</v>
       </c>
       <c r="B512" s="2">
-        <v>14</v>
+        <v>148</v>
       </c>
     </row>
     <row r="513" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A513" s="1">
-        <v>97793</v>
+        <v>95732</v>
       </c>
       <c r="B513" s="2">
-        <v>54</v>
+        <v>132</v>
       </c>
     </row>
     <row r="514" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A514" s="1">
-        <v>98131</v>
+        <v>95735</v>
       </c>
       <c r="B514" s="2">
-        <v>42</v>
+        <v>1594</v>
       </c>
     </row>
     <row r="515" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A515" s="1">
-        <v>98132</v>
+        <v>95765</v>
       </c>
       <c r="B515" s="2">
-        <v>58</v>
+        <v>366</v>
       </c>
     </row>
     <row r="516" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A516" s="1">
-        <v>98133</v>
+        <v>95768</v>
       </c>
       <c r="B516" s="2">
-        <v>98</v>
+        <v>142</v>
       </c>
     </row>
     <row r="517" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A517" s="1">
-        <v>98134</v>
+        <v>95769</v>
       </c>
       <c r="B517" s="2">
-        <v>24</v>
+        <v>610</v>
       </c>
     </row>
     <row r="518" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A518" s="1">
-        <v>98135</v>
+        <v>95770</v>
       </c>
       <c r="B518" s="2">
-        <v>68</v>
+        <v>184</v>
       </c>
     </row>
     <row r="519" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A519" s="1">
-        <v>98136</v>
+        <v>95772</v>
       </c>
       <c r="B519" s="2">
-        <v>44</v>
+        <v>246</v>
       </c>
     </row>
     <row r="520" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A520" s="1">
-        <v>98137</v>
+        <v>95774</v>
       </c>
       <c r="B520" s="2">
-        <v>8</v>
+        <v>240</v>
       </c>
     </row>
     <row r="521" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A521" s="1">
-        <v>98138</v>
+        <v>95781</v>
       </c>
       <c r="B521" s="2">
-        <v>36</v>
+        <v>266</v>
       </c>
     </row>
     <row r="522" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A522" s="1">
-        <v>98140</v>
+        <v>95907</v>
       </c>
       <c r="B522" s="2">
-        <v>96</v>
+        <v>1746</v>
       </c>
     </row>
     <row r="523" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A523" s="1">
-        <v>98141</v>
+        <v>95911</v>
       </c>
       <c r="B523" s="2">
-        <v>58</v>
+        <v>24</v>
       </c>
     </row>
     <row r="524" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A524" s="1">
-        <v>98142</v>
+        <v>96507</v>
       </c>
       <c r="B524" s="2">
-        <v>56</v>
+        <v>40</v>
       </c>
     </row>
     <row r="525" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A525" s="1">
-        <v>98143</v>
+        <v>96508</v>
       </c>
       <c r="B525" s="2">
-        <v>34</v>
+        <v>394</v>
       </c>
     </row>
     <row r="526" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A526" s="1">
-        <v>98144</v>
+        <v>96509</v>
       </c>
       <c r="B526" s="2">
-        <v>80</v>
+        <v>1874</v>
       </c>
     </row>
     <row r="527" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A527" s="1">
-        <v>98147</v>
+        <v>96510</v>
       </c>
       <c r="B527" s="2">
-        <v>104</v>
+        <v>86</v>
       </c>
     </row>
     <row r="528" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A528" s="1">
-        <v>98148</v>
+        <v>96517</v>
       </c>
       <c r="B528" s="2">
-        <v>46</v>
+        <v>22</v>
       </c>
     </row>
     <row r="529" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A529" s="1">
-        <v>98149</v>
+        <v>96539</v>
       </c>
       <c r="B529" s="2">
-        <v>54</v>
+        <v>92</v>
       </c>
     </row>
     <row r="530" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A530" s="1">
-        <v>98150</v>
+        <v>96588</v>
       </c>
       <c r="B530" s="2">
-        <v>24</v>
+        <v>1496</v>
       </c>
     </row>
     <row r="531" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A531" s="1">
-        <v>98151</v>
+        <v>97066</v>
       </c>
       <c r="B531" s="2">
-        <v>24</v>
+        <v>222</v>
       </c>
     </row>
     <row r="532" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A532" s="1">
-        <v>98154</v>
+        <v>97067</v>
       </c>
       <c r="B532" s="2">
-        <v>52</v>
+        <v>302</v>
       </c>
     </row>
     <row r="533" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A533" s="1">
-        <v>98159</v>
+        <v>97116</v>
       </c>
       <c r="B533" s="2">
-        <v>42</v>
+        <v>2104</v>
       </c>
     </row>
     <row r="534" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A534" s="1">
-        <v>98162</v>
+        <v>97118</v>
       </c>
       <c r="B534" s="2">
-        <v>4</v>
+        <v>2104</v>
       </c>
     </row>
     <row r="535" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A535" s="1">
-        <v>98166</v>
+        <v>97186</v>
       </c>
       <c r="B535" s="2">
-        <v>98</v>
+        <v>1422</v>
       </c>
     </row>
     <row r="536" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A536" s="1">
-        <v>98171</v>
+        <v>97245</v>
       </c>
       <c r="B536" s="2">
-        <v>48</v>
+        <v>1354</v>
       </c>
     </row>
     <row r="537" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A537" s="1">
-        <v>98172</v>
+        <v>97703</v>
       </c>
       <c r="B537" s="2">
-        <v>92</v>
+        <v>54</v>
       </c>
     </row>
     <row r="538" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A538" s="1">
-        <v>98173</v>
+        <v>97717</v>
       </c>
       <c r="B538" s="2">
-        <v>68</v>
+        <v>92</v>
       </c>
     </row>
     <row r="539" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A539" s="1">
-        <v>98174</v>
+        <v>97720</v>
       </c>
       <c r="B539" s="2">
-        <v>10</v>
+        <v>28</v>
       </c>
     </row>
     <row r="540" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A540" s="1">
-        <v>98175</v>
+        <v>97723</v>
       </c>
       <c r="B540" s="2">
-        <v>4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="541" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A541" s="1">
-        <v>98178</v>
+        <v>97725</v>
       </c>
       <c r="B541" s="2">
-        <v>54</v>
+        <v>6</v>
       </c>
     </row>
     <row r="542" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A542" s="1">
-        <v>98179</v>
+        <v>97744</v>
       </c>
       <c r="B542" s="2">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="543" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A543" s="1">
-        <v>98257</v>
+        <v>97756</v>
       </c>
       <c r="B543" s="2">
-        <v>18</v>
+        <v>84</v>
       </c>
     </row>
     <row r="544" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A544" s="1">
-        <v>98258</v>
+        <v>97768</v>
       </c>
       <c r="B544" s="2">
-        <v>6</v>
+        <v>44</v>
       </c>
     </row>
     <row r="545" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A545" s="1">
-        <v>98260</v>
+        <v>97784</v>
       </c>
       <c r="B545" s="2">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="546" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A546" s="1">
-        <v>98263</v>
+        <v>97785</v>
       </c>
       <c r="B546" s="2">
-        <v>40</v>
+        <v>34</v>
       </c>
     </row>
     <row r="547" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A547" s="1">
-        <v>98264</v>
+        <v>97788</v>
       </c>
       <c r="B547" s="2">
-        <v>82</v>
+        <v>72</v>
       </c>
     </row>
     <row r="548" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A548" s="1">
-        <v>98268</v>
+        <v>97790</v>
       </c>
       <c r="B548" s="2">
-        <v>46</v>
+        <v>16</v>
       </c>
     </row>
     <row r="549" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A549" s="1">
-        <v>98269</v>
+        <v>97791</v>
       </c>
       <c r="B549" s="2">
-        <v>12</v>
+        <v>18</v>
       </c>
     </row>
     <row r="550" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A550" s="1">
-        <v>98270</v>
+        <v>97792</v>
       </c>
       <c r="B550" s="2">
-        <v>96</v>
+        <v>2</v>
       </c>
     </row>
     <row r="551" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A551" s="1">
-        <v>98271</v>
+        <v>97793</v>
       </c>
       <c r="B551" s="2">
-        <v>8</v>
+        <v>30</v>
       </c>
     </row>
     <row r="552" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A552" s="1">
-        <v>98545</v>
+        <v>98131</v>
       </c>
       <c r="B552" s="2">
-        <v>84</v>
+        <v>14</v>
       </c>
     </row>
     <row r="553" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A553" s="1">
-        <v>98546</v>
+        <v>98132</v>
       </c>
       <c r="B553" s="2">
-        <v>89</v>
+        <v>36</v>
       </c>
     </row>
     <row r="554" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A554" s="1">
-        <v>98547</v>
+        <v>98133</v>
       </c>
       <c r="B554" s="2">
-        <v>42</v>
+        <v>56</v>
       </c>
     </row>
     <row r="555" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A555" s="1">
-        <v>98548</v>
+        <v>98134</v>
       </c>
       <c r="B555" s="2">
-        <v>87</v>
+        <v>6</v>
       </c>
     </row>
     <row r="556" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A556" s="1">
-        <v>98549</v>
+        <v>98135</v>
       </c>
       <c r="B556" s="2">
-        <v>62</v>
+        <v>44</v>
       </c>
     </row>
     <row r="557" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A557" s="1">
-        <v>98550</v>
+        <v>98136</v>
       </c>
       <c r="B557" s="2">
-        <v>26</v>
+        <v>18</v>
       </c>
     </row>
     <row r="558" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A558" s="1">
-        <v>98551</v>
+        <v>98138</v>
       </c>
       <c r="B558" s="2">
-        <v>48</v>
+        <v>12</v>
       </c>
     </row>
     <row r="559" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A559" s="1">
-        <v>98552</v>
+        <v>98140</v>
       </c>
       <c r="B559" s="2">
-        <v>20</v>
+        <v>74</v>
       </c>
     </row>
     <row r="560" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A560" s="1">
-        <v>98553</v>
+        <v>98141</v>
       </c>
       <c r="B560" s="2">
-        <v>96</v>
+        <v>44</v>
       </c>
     </row>
     <row r="561" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A561" s="1">
-        <v>98555</v>
+        <v>98142</v>
       </c>
       <c r="B561" s="2">
-        <v>22</v>
+        <v>28</v>
       </c>
     </row>
     <row r="562" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A562" s="1">
-        <v>98556</v>
+        <v>98143</v>
       </c>
       <c r="B562" s="2">
-        <v>126</v>
+        <v>8</v>
       </c>
     </row>
     <row r="563" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A563" s="1">
-        <v>98557</v>
+        <v>98144</v>
       </c>
       <c r="B563" s="2">
-        <v>64</v>
+        <v>46</v>
       </c>
     </row>
     <row r="564" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A564" s="1">
-        <v>98559</v>
+        <v>98147</v>
       </c>
       <c r="B564" s="2">
-        <v>48</v>
+        <v>88</v>
       </c>
     </row>
     <row r="565" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A565" s="1">
-        <v>98560</v>
+        <v>98148</v>
       </c>
       <c r="B565" s="2">
-        <v>80</v>
+        <v>32</v>
       </c>
     </row>
     <row r="566" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A566" s="1">
-        <v>98561</v>
+        <v>98149</v>
       </c>
       <c r="B566" s="2">
-        <v>80</v>
+        <v>10</v>
       </c>
     </row>
     <row r="567" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A567" s="1">
-        <v>98562</v>
+        <v>98150</v>
       </c>
       <c r="B567" s="2">
-        <v>118</v>
+        <v>2</v>
       </c>
     </row>
     <row r="568" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A568" s="1">
-        <v>98563</v>
+        <v>98151</v>
       </c>
       <c r="B568" s="2">
-        <v>86</v>
+        <v>10</v>
       </c>
     </row>
     <row r="569" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A569" s="1">
-        <v>98564</v>
+        <v>98154</v>
       </c>
       <c r="B569" s="2">
         <v>10</v>
@@ -4993,146 +4999,378 @@
     </row>
     <row r="570" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A570" s="1">
-        <v>98566</v>
+        <v>98159</v>
       </c>
       <c r="B570" s="2">
-        <v>62</v>
+        <v>26</v>
       </c>
     </row>
     <row r="571" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A571" s="1">
-        <v>98567</v>
+        <v>98162</v>
       </c>
       <c r="B571" s="2">
-        <v>50</v>
+        <v>2</v>
       </c>
     </row>
     <row r="572" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A572" s="1">
-        <v>98568</v>
+        <v>98166</v>
       </c>
       <c r="B572" s="2">
-        <v>100</v>
+        <v>76</v>
       </c>
     </row>
     <row r="573" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A573" s="1">
-        <v>98569</v>
+        <v>98171</v>
       </c>
       <c r="B573" s="2">
-        <v>122</v>
+        <v>42</v>
       </c>
     </row>
     <row r="574" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A574" s="1">
-        <v>98571</v>
+        <v>98172</v>
       </c>
       <c r="B574" s="2">
-        <v>104</v>
+        <v>54</v>
       </c>
     </row>
     <row r="575" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A575" s="1">
-        <v>98572</v>
+        <v>98173</v>
       </c>
       <c r="B575" s="2">
-        <v>86</v>
+        <v>64</v>
       </c>
     </row>
     <row r="576" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A576" s="1">
-        <v>98573</v>
+        <v>98178</v>
       </c>
       <c r="B576" s="2">
-        <v>110</v>
+        <v>14</v>
       </c>
     </row>
     <row r="577" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A577" s="1">
-        <v>98575</v>
+        <v>98263</v>
       </c>
       <c r="B577" s="2">
-        <v>354</v>
+        <v>18</v>
       </c>
     </row>
     <row r="578" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A578" s="1">
-        <v>98577</v>
+        <v>98264</v>
       </c>
       <c r="B578" s="2">
-        <v>1</v>
+        <v>36</v>
       </c>
     </row>
     <row r="579" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A579" s="1">
-        <v>98579</v>
+        <v>98268</v>
       </c>
       <c r="B579" s="2">
-        <v>80</v>
+        <v>22</v>
       </c>
     </row>
     <row r="580" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A580" s="1">
-        <v>98580</v>
+        <v>98269</v>
       </c>
       <c r="B580" s="2">
-        <v>50</v>
+        <v>2</v>
       </c>
     </row>
     <row r="581" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A581" s="1">
-        <v>98593</v>
+        <v>98270</v>
       </c>
       <c r="B581" s="2">
-        <v>64</v>
+        <v>56</v>
       </c>
     </row>
     <row r="582" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A582" s="1">
-        <v>98594</v>
+        <v>98545</v>
       </c>
       <c r="B582" s="2">
-        <v>36</v>
+        <v>54</v>
       </c>
     </row>
     <row r="583" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A583" s="1">
-        <v>98595</v>
+        <v>98546</v>
       </c>
       <c r="B583" s="2">
-        <v>92</v>
+        <v>75</v>
       </c>
     </row>
     <row r="584" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A584" s="1">
-        <v>98596</v>
+        <v>98547</v>
       </c>
       <c r="B584" s="2">
-        <v>74</v>
+        <v>16</v>
       </c>
     </row>
     <row r="585" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A585" s="1">
-        <v>98597</v>
+        <v>98548</v>
       </c>
       <c r="B585" s="2">
-        <v>108</v>
+        <v>77</v>
       </c>
     </row>
     <row r="586" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A586" s="1">
-        <v>98598</v>
+        <v>98549</v>
       </c>
       <c r="B586" s="2">
-        <v>124</v>
+        <v>36</v>
       </c>
     </row>
     <row r="587" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A587" s="1">
+        <v>98550</v>
+      </c>
+      <c r="B587" s="2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="588" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A588" s="7">
+        <v>98551</v>
+      </c>
+      <c r="B588" s="8">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="589" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A589" s="7">
+        <v>98552</v>
+      </c>
+      <c r="B589" s="8">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="590" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A590" s="7">
+        <v>98553</v>
+      </c>
+      <c r="B590" s="8">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="591" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A591" s="7">
+        <v>98555</v>
+      </c>
+      <c r="B591" s="8">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="592" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A592" s="7">
+        <v>98556</v>
+      </c>
+      <c r="B592" s="8">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="593" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A593" s="7">
+        <v>98557</v>
+      </c>
+      <c r="B593" s="8">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="594" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A594" s="7">
+        <v>98559</v>
+      </c>
+      <c r="B594" s="8">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="595" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A595" s="7">
+        <v>98560</v>
+      </c>
+      <c r="B595" s="8">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="596" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A596" s="7">
+        <v>98561</v>
+      </c>
+      <c r="B596" s="8">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="597" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A597" s="7">
+        <v>98562</v>
+      </c>
+      <c r="B597" s="8">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="598" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A598" s="7">
+        <v>98563</v>
+      </c>
+      <c r="B598" s="8">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="599" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A599" s="7">
+        <v>98564</v>
+      </c>
+      <c r="B599" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="600" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A600" s="7">
+        <v>98566</v>
+      </c>
+      <c r="B600" s="8">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="601" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A601" s="7">
+        <v>98567</v>
+      </c>
+      <c r="B601" s="8">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="602" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A602" s="7">
+        <v>98568</v>
+      </c>
+      <c r="B602" s="8">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="603" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A603" s="7">
+        <v>98569</v>
+      </c>
+      <c r="B603" s="8">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="604" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A604" s="7">
+        <v>98571</v>
+      </c>
+      <c r="B604" s="8">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="605" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A605" s="7">
+        <v>98572</v>
+      </c>
+      <c r="B605" s="8">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="606" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A606" s="7">
+        <v>98573</v>
+      </c>
+      <c r="B606" s="8">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="607" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A607" s="7">
+        <v>98575</v>
+      </c>
+      <c r="B607" s="8">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="608" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A608" s="7">
+        <v>98579</v>
+      </c>
+      <c r="B608" s="8">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="609" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A609" s="7">
+        <v>98580</v>
+      </c>
+      <c r="B609" s="8">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="610" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A610" s="7">
+        <v>98593</v>
+      </c>
+      <c r="B610" s="8">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="611" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A611" s="7">
+        <v>98594</v>
+      </c>
+      <c r="B611" s="8">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="612" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A612" s="7">
+        <v>98595</v>
+      </c>
+      <c r="B612" s="8">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="613" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A613" s="7">
+        <v>98596</v>
+      </c>
+      <c r="B613" s="8">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="614" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A614" s="7">
+        <v>98597</v>
+      </c>
+      <c r="B614" s="8">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="615" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A615" s="7">
+        <v>98598</v>
+      </c>
+      <c r="B615" s="8">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="616" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A616" s="7">
         <v>98599</v>
       </c>
-      <c r="B587" s="2">
-        <v>108</v>
+      <c r="B616" s="8">
+        <v>86</v>
       </c>
     </row>
   </sheetData>

--- a/assets/Items_for_Replenishment.xlsx
+++ b/assets/Items_for_Replenishment.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30430"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5A6BE45-BFFE-4A0A-93B2-57BC2105D58E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07A434A9-12DE-4BF6-BAB2-344AEFCEA71F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -108,7 +108,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -127,12 +127,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -438,7 +432,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B616"/>
+  <dimension ref="A1:B534"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.140625" style="6" customWidth="1"/>
@@ -458,7 +452,7 @@
         <v>46496</v>
       </c>
       <c r="B2" s="2">
-        <v>544</v>
+        <v>314</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -466,7 +460,7 @@
         <v>55847</v>
       </c>
       <c r="B3" s="2">
-        <v>936</v>
+        <v>738</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -474,7 +468,7 @@
         <v>68563</v>
       </c>
       <c r="B4" s="2">
-        <v>2400</v>
+        <v>1380</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -482,7 +476,7 @@
         <v>74532</v>
       </c>
       <c r="B5" s="2">
-        <v>22</v>
+        <v>1347</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -490,7 +484,7 @@
         <v>76560</v>
       </c>
       <c r="B6" s="2">
-        <v>586</v>
+        <v>560</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -498,7 +492,7 @@
         <v>78699</v>
       </c>
       <c r="B7" s="2">
-        <v>1200</v>
+        <v>50</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -506,303 +500,303 @@
         <v>80815</v>
       </c>
       <c r="B8" s="2">
-        <v>2296</v>
+        <v>1988</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
-        <v>82379</v>
+        <v>81181</v>
       </c>
       <c r="B9" s="2">
-        <v>958</v>
+        <v>312</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
-        <v>82595</v>
+        <v>82379</v>
       </c>
       <c r="B10" s="2">
-        <v>940</v>
+        <v>744</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
-        <v>84559</v>
+        <v>82595</v>
       </c>
       <c r="B11" s="2">
-        <v>1476</v>
+        <v>100</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
-        <v>84662</v>
+        <v>84559</v>
       </c>
       <c r="B12" s="2">
-        <v>890</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
-        <v>87151</v>
+        <v>84662</v>
       </c>
       <c r="B13" s="2">
-        <v>2260</v>
+        <v>50</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
-        <v>87154</v>
+        <v>86979</v>
       </c>
       <c r="B14" s="2">
-        <v>1230</v>
+        <v>1528</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
-        <v>87813</v>
+        <v>87151</v>
       </c>
       <c r="B15" s="2">
-        <v>330</v>
+        <v>1560</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
-        <v>88245</v>
+        <v>87154</v>
       </c>
       <c r="B16" s="2">
-        <v>610</v>
+        <v>40</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
-        <v>88478</v>
+        <v>87813</v>
       </c>
       <c r="B17" s="2">
-        <v>104</v>
+        <v>276</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
-        <v>88481</v>
+        <v>88245</v>
       </c>
       <c r="B18" s="2">
-        <v>505</v>
+        <v>484</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
-        <v>88571</v>
+        <v>88478</v>
       </c>
       <c r="B19" s="2">
-        <v>246</v>
+        <v>60</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
-        <v>88609</v>
+        <v>88481</v>
       </c>
       <c r="B20" s="2">
-        <v>384</v>
+        <v>426</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
-        <v>88810</v>
+        <v>88571</v>
       </c>
       <c r="B21" s="2">
-        <v>557</v>
+        <v>170</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
-        <v>89952</v>
+        <v>88609</v>
       </c>
       <c r="B22" s="2">
-        <v>642</v>
+        <v>262</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
-        <v>90828</v>
+        <v>88810</v>
       </c>
       <c r="B23" s="2">
-        <v>20</v>
+        <v>474</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
-        <v>90829</v>
+        <v>89952</v>
       </c>
       <c r="B24" s="2">
-        <v>420</v>
+        <v>520</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
-        <v>90830</v>
+        <v>90829</v>
       </c>
       <c r="B25" s="2">
-        <v>3660</v>
+        <v>420</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
-        <v>90831</v>
+        <v>90830</v>
       </c>
       <c r="B26" s="2">
-        <v>700</v>
+        <v>3660</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
-        <v>91064</v>
+        <v>90831</v>
       </c>
       <c r="B27" s="2">
-        <v>1623</v>
+        <v>700</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
-        <v>91290</v>
+        <v>91064</v>
       </c>
       <c r="B28" s="2">
-        <v>1120</v>
+        <v>1123</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
-        <v>91431</v>
+        <v>91290</v>
       </c>
       <c r="B29" s="2">
-        <v>1440</v>
+        <v>60</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
-        <v>92425</v>
+        <v>91431</v>
       </c>
       <c r="B30" s="2">
-        <v>570</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
-        <v>92681</v>
+        <v>92425</v>
       </c>
       <c r="B31" s="2">
-        <v>1441</v>
+        <v>492</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
-        <v>92688</v>
+        <v>92681</v>
       </c>
       <c r="B32" s="2">
-        <v>989</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
-        <v>92725</v>
+        <v>92688</v>
       </c>
       <c r="B33" s="2">
-        <v>1060</v>
+        <v>933</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
-        <v>92728</v>
+        <v>92725</v>
       </c>
       <c r="B34" s="2">
-        <v>320</v>
+        <v>80</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
-        <v>92730</v>
+        <v>92728</v>
       </c>
       <c r="B35" s="2">
-        <v>640</v>
+        <v>320</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" s="1">
-        <v>92731</v>
+        <v>92730</v>
       </c>
       <c r="B36" s="2">
-        <v>1070</v>
+        <v>640</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" s="1">
-        <v>93286</v>
+        <v>92731</v>
       </c>
       <c r="B37" s="2">
-        <v>1100</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
-        <v>93307</v>
+        <v>93286</v>
       </c>
       <c r="B38" s="2">
-        <v>618</v>
+        <v>762</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
-        <v>93311</v>
+        <v>93307</v>
       </c>
       <c r="B39" s="2">
-        <v>974</v>
+        <v>362</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" s="1">
-        <v>93329</v>
+        <v>93311</v>
       </c>
       <c r="B40" s="2">
-        <v>2233</v>
+        <v>512</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" s="1">
-        <v>93333</v>
+        <v>93329</v>
       </c>
       <c r="B41" s="2">
-        <v>1684</v>
+        <v>2101</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" s="1">
-        <v>94076</v>
+        <v>93333</v>
       </c>
       <c r="B42" s="2">
-        <v>3096</v>
+        <v>1598</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" s="1">
-        <v>94319</v>
+        <v>94076</v>
       </c>
       <c r="B43" s="2">
-        <v>150</v>
+        <v>3020</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" s="1">
-        <v>94320</v>
+        <v>94319</v>
       </c>
       <c r="B44" s="2">
-        <v>650</v>
+        <v>140</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" s="1">
-        <v>94321</v>
+        <v>94320</v>
       </c>
       <c r="B45" s="2">
-        <v>60</v>
+        <v>650</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.25">
@@ -810,7 +804,7 @@
         <v>94322</v>
       </c>
       <c r="B46" s="2">
-        <v>940</v>
+        <v>830</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
@@ -818,7 +812,7 @@
         <v>94425</v>
       </c>
       <c r="B47" s="2">
-        <v>1458</v>
+        <v>924</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
@@ -826,7 +820,7 @@
         <v>94916</v>
       </c>
       <c r="B48" s="2">
-        <v>2278</v>
+        <v>1776</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
@@ -834,7 +828,7 @@
         <v>94917</v>
       </c>
       <c r="B49" s="2">
-        <v>2100</v>
+        <v>1752</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
@@ -842,7 +836,7 @@
         <v>95677</v>
       </c>
       <c r="B50" s="2">
-        <v>1220</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
@@ -850,7 +844,7 @@
         <v>95815</v>
       </c>
       <c r="B51" s="2">
-        <v>1166</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
@@ -858,7 +852,7 @@
         <v>95816</v>
       </c>
       <c r="B52" s="2">
-        <v>1862</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.25">
@@ -866,7 +860,7 @@
         <v>95817</v>
       </c>
       <c r="B53" s="2">
-        <v>1834</v>
+        <v>1536</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.25">
@@ -874,7 +868,7 @@
         <v>95947</v>
       </c>
       <c r="B54" s="2">
-        <v>396</v>
+        <v>48</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.25">
@@ -882,7 +876,7 @@
         <v>96557</v>
       </c>
       <c r="B55" s="2">
-        <v>1551</v>
+        <v>579</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.25">
@@ -890,1596 +884,1596 @@
         <v>96559</v>
       </c>
       <c r="B56" s="2">
-        <v>7580</v>
+        <v>6920</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A57" s="1">
-        <v>96893</v>
+        <v>97525</v>
       </c>
       <c r="B57" s="2">
-        <v>12</v>
+        <v>88</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A58" s="1">
-        <v>97525</v>
+        <v>97529</v>
       </c>
       <c r="B58" s="2">
-        <v>98</v>
+        <v>8</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A59" s="1">
-        <v>97526</v>
+        <v>97690</v>
       </c>
       <c r="B59" s="2">
-        <v>20</v>
+        <v>162</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A60" s="1">
-        <v>97527</v>
+        <v>97691</v>
       </c>
       <c r="B60" s="2">
-        <v>40</v>
+        <v>160</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A61" s="1">
-        <v>97543</v>
+        <v>98600</v>
       </c>
       <c r="B61" s="2">
-        <v>12</v>
+        <v>180</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A62" s="1">
-        <v>97545</v>
+        <v>98601</v>
       </c>
       <c r="B62" s="2">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A63" s="1">
-        <v>97547</v>
+        <v>98602</v>
       </c>
       <c r="B63" s="2">
-        <v>4</v>
+        <v>490</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A64" s="1">
-        <v>97690</v>
+        <v>98657</v>
       </c>
       <c r="B64" s="2">
-        <v>180</v>
+        <v>410</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A65" s="1">
-        <v>97691</v>
+        <v>98658</v>
       </c>
       <c r="B65" s="2">
-        <v>194</v>
+        <v>590</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A66" s="1">
-        <v>98423</v>
+        <v>99392</v>
       </c>
       <c r="B66" s="2">
-        <v>25</v>
+        <v>3</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A67" s="1">
-        <v>98424</v>
+        <v>3764</v>
       </c>
       <c r="B67" s="2">
-        <v>38</v>
+        <v>648</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A68" s="1">
-        <v>98600</v>
+        <v>3775</v>
       </c>
       <c r="B68" s="2">
-        <v>250</v>
+        <v>3492</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A69" s="1">
-        <v>98601</v>
+        <v>3780</v>
       </c>
       <c r="B69" s="2">
-        <v>180</v>
+        <v>846</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A70" s="1">
-        <v>98602</v>
+        <v>3786</v>
       </c>
       <c r="B70" s="2">
-        <v>490</v>
+        <v>882</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A71" s="1">
-        <v>98657</v>
+        <v>3798</v>
       </c>
       <c r="B71" s="2">
-        <v>510</v>
+        <v>756</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A72" s="1">
-        <v>98658</v>
+        <v>3809</v>
       </c>
       <c r="B72" s="2">
-        <v>680</v>
+        <v>558</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A73" s="1">
-        <v>99392</v>
+        <v>3817</v>
       </c>
       <c r="B73" s="2">
-        <v>3</v>
+        <v>1494</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A74" s="1">
-        <v>99393</v>
+        <v>3821</v>
       </c>
       <c r="B74" s="2">
-        <v>12</v>
+        <v>540</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A75" s="1">
-        <v>3764</v>
+        <v>3827</v>
       </c>
       <c r="B75" s="2">
-        <v>972</v>
+        <v>900</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A76" s="1">
-        <v>3775</v>
+        <v>3833</v>
       </c>
       <c r="B76" s="2">
-        <v>3924</v>
+        <v>2880</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A77" s="1">
-        <v>3780</v>
+        <v>7652</v>
       </c>
       <c r="B77" s="2">
-        <v>2016</v>
+        <v>7200</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A78" s="1">
-        <v>3786</v>
+        <v>36371</v>
       </c>
       <c r="B78" s="2">
-        <v>1728</v>
+        <v>1506</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A79" s="1">
-        <v>3798</v>
+        <v>68947</v>
       </c>
       <c r="B79" s="2">
-        <v>1440</v>
+        <v>252</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A80" s="1">
-        <v>3809</v>
+        <v>70451</v>
       </c>
       <c r="B80" s="2">
-        <v>954</v>
+        <v>2358</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A81" s="1">
-        <v>3817</v>
+        <v>70739</v>
       </c>
       <c r="B81" s="2">
-        <v>2304</v>
+        <v>416</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A82" s="1">
-        <v>3821</v>
+        <v>73723</v>
       </c>
       <c r="B82" s="2">
-        <v>918</v>
+        <v>705</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A83" s="1">
-        <v>3827</v>
+        <v>74359</v>
       </c>
       <c r="B83" s="2">
-        <v>1728</v>
+        <v>2376</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A84" s="1">
-        <v>3833</v>
+        <v>82580</v>
       </c>
       <c r="B84" s="2">
-        <v>3636</v>
+        <v>2064</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A85" s="1">
-        <v>36371</v>
+        <v>82581</v>
       </c>
       <c r="B85" s="2">
-        <v>1688</v>
+        <v>1728</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A86" s="1">
-        <v>59296</v>
+        <v>82582</v>
       </c>
       <c r="B86" s="2">
-        <v>44</v>
+        <v>2400</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A87" s="1">
-        <v>68947</v>
+        <v>82587</v>
       </c>
       <c r="B87" s="2">
-        <v>498</v>
+        <v>2280</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A88" s="1">
-        <v>70451</v>
+        <v>83192</v>
       </c>
       <c r="B88" s="2">
-        <v>2838</v>
+        <v>306</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A89" s="1">
-        <v>70739</v>
+        <v>83687</v>
       </c>
       <c r="B89" s="2">
-        <v>1000</v>
+        <v>2040</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A90" s="1">
-        <v>73723</v>
+        <v>83689</v>
       </c>
       <c r="B90" s="2">
-        <v>855</v>
+        <v>1872</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A91" s="1">
-        <v>74359</v>
+        <v>91047</v>
       </c>
       <c r="B91" s="2">
-        <v>2736</v>
+        <v>234</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A92" s="1">
-        <v>82580</v>
+        <v>98427</v>
       </c>
       <c r="B92" s="2">
-        <v>3960</v>
+        <v>15</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A93" s="1">
-        <v>82581</v>
+        <v>6881</v>
       </c>
       <c r="B93" s="2">
-        <v>3960</v>
+        <v>920</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A94" s="1">
-        <v>82582</v>
+        <v>9859</v>
       </c>
       <c r="B94" s="2">
-        <v>4248</v>
+        <v>2</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A95" s="1">
-        <v>82587</v>
+        <v>9961</v>
       </c>
       <c r="B95" s="2">
-        <v>4248</v>
+        <v>720</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A96" s="1">
-        <v>83192</v>
+        <v>9962</v>
       </c>
       <c r="B96" s="2">
-        <v>864</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A97" s="1">
-        <v>83687</v>
+        <v>9963</v>
       </c>
       <c r="B97" s="2">
-        <v>4320</v>
+        <v>962</v>
       </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A98" s="1">
-        <v>83689</v>
+        <v>16075</v>
       </c>
       <c r="B98" s="2">
-        <v>4320</v>
+        <v>201</v>
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A99" s="1">
-        <v>91047</v>
+        <v>66615</v>
       </c>
       <c r="B99" s="2">
-        <v>1002</v>
+        <v>266</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A100" s="1">
-        <v>98427</v>
+        <v>66617</v>
       </c>
       <c r="B100" s="2">
-        <v>57</v>
+        <v>145</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A101" s="1">
-        <v>6881</v>
+        <v>68878</v>
       </c>
       <c r="B101" s="2">
-        <v>22</v>
+        <v>5</v>
       </c>
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A102" s="1">
-        <v>9859</v>
+        <v>68879</v>
       </c>
       <c r="B102" s="2">
-        <v>107</v>
+        <v>199</v>
       </c>
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A103" s="1">
-        <v>9963</v>
+        <v>68880</v>
       </c>
       <c r="B103" s="2">
-        <v>70</v>
+        <v>173</v>
       </c>
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A104" s="1">
-        <v>16075</v>
+        <v>81351</v>
       </c>
       <c r="B104" s="2">
-        <v>228</v>
+        <v>924</v>
       </c>
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A105" s="1">
-        <v>68878</v>
+        <v>81352</v>
       </c>
       <c r="B105" s="2">
-        <v>85</v>
+        <v>781</v>
       </c>
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A106" s="1">
-        <v>68879</v>
+        <v>84851</v>
       </c>
       <c r="B106" s="2">
-        <v>287</v>
+        <v>322</v>
       </c>
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A107" s="1">
-        <v>68880</v>
+        <v>84852</v>
       </c>
       <c r="B107" s="2">
-        <v>221</v>
+        <v>400</v>
       </c>
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A108" s="1">
-        <v>84851</v>
+        <v>84853</v>
       </c>
       <c r="B108" s="2">
-        <v>271</v>
+        <v>376</v>
       </c>
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A109" s="1">
-        <v>84852</v>
+        <v>84854</v>
       </c>
       <c r="B109" s="2">
-        <v>237</v>
+        <v>306</v>
       </c>
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A110" s="1">
-        <v>84853</v>
+        <v>84855</v>
       </c>
       <c r="B110" s="2">
-        <v>70</v>
+        <v>212</v>
       </c>
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A111" s="1">
-        <v>84854</v>
+        <v>85743</v>
       </c>
       <c r="B111" s="2">
-        <v>223</v>
+        <v>228</v>
       </c>
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A112" s="1">
-        <v>84855</v>
+        <v>86015</v>
       </c>
       <c r="B112" s="2">
-        <v>193</v>
+        <v>143</v>
       </c>
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A113" s="1">
-        <v>85743</v>
+        <v>86016</v>
       </c>
       <c r="B113" s="2">
-        <v>270</v>
+        <v>30</v>
       </c>
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A114" s="1">
-        <v>86015</v>
+        <v>86266</v>
       </c>
       <c r="B114" s="2">
-        <v>177</v>
+        <v>8</v>
       </c>
     </row>
     <row r="115" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A115" s="1">
-        <v>86016</v>
+        <v>86268</v>
       </c>
       <c r="B115" s="2">
-        <v>48</v>
+        <v>267</v>
       </c>
     </row>
     <row r="116" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A116" s="1">
-        <v>86266</v>
+        <v>86269</v>
       </c>
       <c r="B116" s="2">
-        <v>158</v>
+        <v>51</v>
       </c>
     </row>
     <row r="117" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A117" s="1">
-        <v>86268</v>
+        <v>86286</v>
       </c>
       <c r="B117" s="2">
-        <v>340</v>
+        <v>424</v>
       </c>
     </row>
     <row r="118" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A118" s="1">
-        <v>86269</v>
+        <v>86287</v>
       </c>
       <c r="B118" s="2">
-        <v>100</v>
+        <v>420</v>
       </c>
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A119" s="1">
-        <v>86286</v>
+        <v>86288</v>
       </c>
       <c r="B119" s="2">
-        <v>518</v>
+        <v>407</v>
       </c>
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A120" s="1">
-        <v>86287</v>
+        <v>86289</v>
       </c>
       <c r="B120" s="2">
-        <v>483</v>
+        <v>155</v>
       </c>
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A121" s="1">
-        <v>86288</v>
+        <v>87342</v>
       </c>
       <c r="B121" s="2">
-        <v>462</v>
+        <v>5</v>
       </c>
     </row>
     <row r="122" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A122" s="1">
-        <v>86289</v>
+        <v>87343</v>
       </c>
       <c r="B122" s="2">
-        <v>191</v>
+        <v>5</v>
       </c>
     </row>
     <row r="123" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A123" s="1">
-        <v>87342</v>
+        <v>87344</v>
       </c>
       <c r="B123" s="2">
-        <v>112</v>
+        <v>3</v>
       </c>
     </row>
     <row r="124" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A124" s="1">
-        <v>87343</v>
+        <v>87345</v>
       </c>
       <c r="B124" s="2">
-        <v>94</v>
+        <v>1</v>
       </c>
     </row>
     <row r="125" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A125" s="1">
-        <v>87344</v>
+        <v>87416</v>
       </c>
       <c r="B125" s="2">
-        <v>59</v>
+        <v>167</v>
       </c>
     </row>
     <row r="126" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A126" s="1">
-        <v>87345</v>
+        <v>87417</v>
       </c>
       <c r="B126" s="2">
-        <v>46</v>
+        <v>33</v>
       </c>
     </row>
     <row r="127" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A127" s="1">
-        <v>87416</v>
+        <v>87882</v>
       </c>
       <c r="B127" s="2">
-        <v>258</v>
+        <v>675</v>
       </c>
     </row>
     <row r="128" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A128" s="1">
-        <v>87417</v>
+        <v>87883</v>
       </c>
       <c r="B128" s="2">
-        <v>121</v>
+        <v>439</v>
       </c>
     </row>
     <row r="129" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A129" s="1">
-        <v>87882</v>
+        <v>87884</v>
       </c>
       <c r="B129" s="2">
-        <v>689</v>
+        <v>80</v>
       </c>
     </row>
     <row r="130" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A130" s="1">
-        <v>87883</v>
+        <v>87885</v>
       </c>
       <c r="B130" s="2">
-        <v>462</v>
+        <v>137</v>
       </c>
     </row>
     <row r="131" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A131" s="1">
-        <v>87884</v>
+        <v>87886</v>
       </c>
       <c r="B131" s="2">
-        <v>100</v>
+        <v>151</v>
       </c>
     </row>
     <row r="132" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A132" s="1">
-        <v>87885</v>
+        <v>87932</v>
       </c>
       <c r="B132" s="2">
-        <v>151</v>
+        <v>607</v>
       </c>
     </row>
     <row r="133" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A133" s="1">
-        <v>87886</v>
+        <v>87934</v>
       </c>
       <c r="B133" s="2">
-        <v>175</v>
+        <v>382</v>
       </c>
     </row>
     <row r="134" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A134" s="1">
-        <v>87932</v>
+        <v>87937</v>
       </c>
       <c r="B134" s="2">
-        <v>654</v>
+        <v>367</v>
       </c>
     </row>
     <row r="135" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A135" s="1">
-        <v>87934</v>
+        <v>87938</v>
       </c>
       <c r="B135" s="2">
-        <v>438</v>
+        <v>608</v>
       </c>
     </row>
     <row r="136" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A136" s="1">
-        <v>87937</v>
+        <v>87939</v>
       </c>
       <c r="B136" s="2">
-        <v>435</v>
+        <v>347</v>
       </c>
     </row>
     <row r="137" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A137" s="1">
-        <v>87938</v>
+        <v>87941</v>
       </c>
       <c r="B137" s="2">
-        <v>657</v>
+        <v>1</v>
       </c>
     </row>
     <row r="138" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A138" s="1">
-        <v>87939</v>
+        <v>88653</v>
       </c>
       <c r="B138" s="2">
-        <v>420</v>
+        <v>364</v>
       </c>
     </row>
     <row r="139" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A139" s="1">
-        <v>87941</v>
+        <v>88654</v>
       </c>
       <c r="B139" s="2">
-        <v>26</v>
+        <v>406</v>
       </c>
     </row>
     <row r="140" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A140" s="1">
-        <v>88653</v>
+        <v>88655</v>
       </c>
       <c r="B140" s="2">
-        <v>393</v>
+        <v>524</v>
       </c>
     </row>
     <row r="141" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A141" s="1">
-        <v>88654</v>
+        <v>88656</v>
       </c>
       <c r="B141" s="2">
-        <v>444</v>
+        <v>140</v>
       </c>
     </row>
     <row r="142" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A142" s="1">
-        <v>88655</v>
+        <v>88657</v>
       </c>
       <c r="B142" s="2">
-        <v>550</v>
+        <v>65</v>
       </c>
     </row>
     <row r="143" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A143" s="1">
-        <v>88656</v>
+        <v>89337</v>
       </c>
       <c r="B143" s="2">
-        <v>160</v>
+        <v>243</v>
       </c>
     </row>
     <row r="144" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A144" s="1">
-        <v>88657</v>
+        <v>89340</v>
       </c>
       <c r="B144" s="2">
-        <v>83</v>
+        <v>229</v>
       </c>
     </row>
     <row r="145" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A145" s="1">
-        <v>89339</v>
+        <v>89341</v>
       </c>
       <c r="B145" s="2">
-        <v>168</v>
+        <v>93</v>
       </c>
     </row>
     <row r="146" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A146" s="1">
-        <v>89340</v>
+        <v>90566</v>
       </c>
       <c r="B146" s="2">
-        <v>229</v>
+        <v>396</v>
       </c>
     </row>
     <row r="147" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A147" s="1">
-        <v>89341</v>
+        <v>90568</v>
       </c>
       <c r="B147" s="2">
-        <v>67</v>
+        <v>278</v>
       </c>
     </row>
     <row r="148" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A148" s="1">
-        <v>90566</v>
+        <v>90569</v>
       </c>
       <c r="B148" s="2">
-        <v>458</v>
+        <v>195</v>
       </c>
     </row>
     <row r="149" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A149" s="1">
-        <v>90568</v>
+        <v>90570</v>
       </c>
       <c r="B149" s="2">
-        <v>341</v>
+        <v>164</v>
       </c>
     </row>
     <row r="150" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A150" s="1">
-        <v>90569</v>
+        <v>90789</v>
       </c>
       <c r="B150" s="2">
-        <v>224</v>
+        <v>3</v>
       </c>
     </row>
     <row r="151" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A151" s="1">
-        <v>90570</v>
+        <v>90790</v>
       </c>
       <c r="B151" s="2">
-        <v>191</v>
+        <v>4</v>
       </c>
     </row>
     <row r="152" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A152" s="1">
-        <v>90789</v>
+        <v>90791</v>
       </c>
       <c r="B152" s="2">
-        <v>112</v>
+        <v>2</v>
       </c>
     </row>
     <row r="153" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A153" s="1">
-        <v>90790</v>
+        <v>90792</v>
       </c>
       <c r="B153" s="2">
-        <v>156</v>
+        <v>3</v>
       </c>
     </row>
     <row r="154" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A154" s="1">
-        <v>90791</v>
+        <v>90922</v>
       </c>
       <c r="B154" s="2">
-        <v>119</v>
+        <v>589</v>
       </c>
     </row>
     <row r="155" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A155" s="1">
-        <v>90792</v>
+        <v>90923</v>
       </c>
       <c r="B155" s="2">
-        <v>45</v>
+        <v>544</v>
       </c>
     </row>
     <row r="156" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A156" s="1">
-        <v>90793</v>
+        <v>90924</v>
       </c>
       <c r="B156" s="2">
-        <v>21</v>
+        <v>158</v>
       </c>
     </row>
     <row r="157" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A157" s="1">
-        <v>90922</v>
+        <v>90925</v>
       </c>
       <c r="B157" s="2">
-        <v>656</v>
+        <v>58</v>
       </c>
     </row>
     <row r="158" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A158" s="1">
-        <v>90923</v>
+        <v>90926</v>
       </c>
       <c r="B158" s="2">
-        <v>600</v>
+        <v>73</v>
       </c>
     </row>
     <row r="159" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A159" s="1">
-        <v>90924</v>
+        <v>91279</v>
       </c>
       <c r="B159" s="2">
-        <v>214</v>
+        <v>482</v>
       </c>
     </row>
     <row r="160" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A160" s="1">
-        <v>90925</v>
+        <v>91280</v>
       </c>
       <c r="B160" s="2">
-        <v>124</v>
+        <v>556</v>
       </c>
     </row>
     <row r="161" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A161" s="1">
-        <v>90926</v>
+        <v>91765</v>
       </c>
       <c r="B161" s="2">
-        <v>120</v>
+        <v>237</v>
       </c>
     </row>
     <row r="162" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A162" s="1">
-        <v>91208</v>
+        <v>91766</v>
       </c>
       <c r="B162" s="2">
-        <v>1</v>
+        <v>53</v>
       </c>
     </row>
     <row r="163" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A163" s="1">
-        <v>91209</v>
+        <v>91769</v>
       </c>
       <c r="B163" s="2">
-        <v>5</v>
+        <v>34</v>
       </c>
     </row>
     <row r="164" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A164" s="1">
-        <v>91279</v>
+        <v>91815</v>
       </c>
       <c r="B164" s="2">
-        <v>507</v>
+        <v>85</v>
       </c>
     </row>
     <row r="165" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A165" s="1">
-        <v>91280</v>
+        <v>91816</v>
       </c>
       <c r="B165" s="2">
-        <v>613</v>
+        <v>769</v>
       </c>
     </row>
     <row r="166" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A166" s="1">
-        <v>91765</v>
+        <v>91817</v>
       </c>
       <c r="B166" s="2">
-        <v>290</v>
+        <v>175</v>
       </c>
     </row>
     <row r="167" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A167" s="1">
-        <v>91766</v>
+        <v>92227</v>
       </c>
       <c r="B167" s="2">
-        <v>88</v>
+        <v>800</v>
       </c>
     </row>
     <row r="168" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A168" s="1">
-        <v>91769</v>
+        <v>92228</v>
       </c>
       <c r="B168" s="2">
-        <v>50</v>
+        <v>800</v>
       </c>
     </row>
     <row r="169" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A169" s="1">
-        <v>91815</v>
+        <v>92229</v>
       </c>
       <c r="B169" s="2">
-        <v>218</v>
+        <v>480</v>
       </c>
     </row>
     <row r="170" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A170" s="1">
-        <v>91816</v>
+        <v>92230</v>
       </c>
       <c r="B170" s="2">
-        <v>869</v>
+        <v>400</v>
       </c>
     </row>
     <row r="171" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A171" s="1">
-        <v>91817</v>
+        <v>92231</v>
       </c>
       <c r="B171" s="2">
-        <v>255</v>
+        <v>320</v>
       </c>
     </row>
     <row r="172" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A172" s="1">
-        <v>92284</v>
+        <v>92285</v>
       </c>
       <c r="B172" s="2">
-        <v>26</v>
+        <v>51</v>
       </c>
     </row>
     <row r="173" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A173" s="1">
-        <v>92285</v>
+        <v>92288</v>
       </c>
       <c r="B173" s="2">
-        <v>89</v>
+        <v>983</v>
       </c>
     </row>
     <row r="174" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A174" s="1">
-        <v>92288</v>
+        <v>92289</v>
       </c>
       <c r="B174" s="2">
-        <v>1017</v>
+        <v>850</v>
       </c>
     </row>
     <row r="175" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A175" s="1">
-        <v>92289</v>
+        <v>92290</v>
       </c>
       <c r="B175" s="2">
-        <v>886</v>
+        <v>551</v>
       </c>
     </row>
     <row r="176" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A176" s="1">
-        <v>92290</v>
+        <v>92291</v>
       </c>
       <c r="B176" s="2">
-        <v>581</v>
+        <v>423</v>
       </c>
     </row>
     <row r="177" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A177" s="1">
-        <v>92291</v>
+        <v>92292</v>
       </c>
       <c r="B177" s="2">
-        <v>443</v>
+        <v>200</v>
       </c>
     </row>
     <row r="178" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A178" s="1">
-        <v>92292</v>
+        <v>92409</v>
       </c>
       <c r="B178" s="2">
-        <v>212</v>
+        <v>94</v>
       </c>
     </row>
     <row r="179" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A179" s="1">
-        <v>92409</v>
+        <v>92410</v>
       </c>
       <c r="B179" s="2">
-        <v>185</v>
+        <v>182</v>
       </c>
     </row>
     <row r="180" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A180" s="1">
-        <v>92410</v>
+        <v>92411</v>
       </c>
       <c r="B180" s="2">
-        <v>268</v>
+        <v>60</v>
       </c>
     </row>
     <row r="181" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A181" s="1">
-        <v>92411</v>
+        <v>92412</v>
       </c>
       <c r="B181" s="2">
-        <v>144</v>
+        <v>264</v>
       </c>
     </row>
     <row r="182" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A182" s="1">
-        <v>92412</v>
+        <v>92413</v>
       </c>
       <c r="B182" s="2">
-        <v>322</v>
+        <v>45</v>
       </c>
     </row>
     <row r="183" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A183" s="1">
-        <v>92413</v>
+        <v>92543</v>
       </c>
       <c r="B183" s="2">
-        <v>96</v>
+        <v>617</v>
       </c>
     </row>
     <row r="184" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A184" s="1">
-        <v>92589</v>
+        <v>92544</v>
       </c>
       <c r="B184" s="2">
-        <v>407</v>
+        <v>476</v>
       </c>
     </row>
     <row r="185" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A185" s="1">
-        <v>92590</v>
+        <v>92545</v>
       </c>
       <c r="B185" s="2">
-        <v>595</v>
+        <v>350</v>
       </c>
     </row>
     <row r="186" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A186" s="1">
-        <v>92591</v>
+        <v>92546</v>
       </c>
       <c r="B186" s="2">
-        <v>405</v>
+        <v>224</v>
       </c>
     </row>
     <row r="187" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A187" s="1">
-        <v>92592</v>
+        <v>92589</v>
       </c>
       <c r="B187" s="2">
-        <v>255</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="188" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A188" s="1">
-        <v>92593</v>
+        <v>92590</v>
       </c>
       <c r="B188" s="2">
-        <v>185</v>
+        <v>1314</v>
       </c>
     </row>
     <row r="189" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A189" s="1">
-        <v>93238</v>
+        <v>92591</v>
       </c>
       <c r="B189" s="2">
-        <v>1150</v>
+        <v>692</v>
       </c>
     </row>
     <row r="190" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A190" s="1">
-        <v>93239</v>
+        <v>92592</v>
       </c>
       <c r="B190" s="2">
-        <v>939</v>
+        <v>624</v>
       </c>
     </row>
     <row r="191" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A191" s="1">
-        <v>93240</v>
+        <v>92593</v>
       </c>
       <c r="B191" s="2">
-        <v>577</v>
+        <v>302</v>
       </c>
     </row>
     <row r="192" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A192" s="1">
-        <v>93241</v>
+        <v>93228</v>
       </c>
       <c r="B192" s="2">
-        <v>762</v>
+        <v>1</v>
       </c>
     </row>
     <row r="193" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A193" s="1">
-        <v>93242</v>
+        <v>93238</v>
       </c>
       <c r="B193" s="2">
-        <v>428</v>
+        <v>883</v>
       </c>
     </row>
     <row r="194" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A194" s="1">
-        <v>94139</v>
+        <v>93239</v>
       </c>
       <c r="B194" s="2">
-        <v>616</v>
+        <v>667</v>
       </c>
     </row>
     <row r="195" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A195" s="1">
-        <v>94140</v>
+        <v>93240</v>
       </c>
       <c r="B195" s="2">
-        <v>983</v>
+        <v>292</v>
       </c>
     </row>
     <row r="196" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A196" s="1">
-        <v>94142</v>
+        <v>93241</v>
       </c>
       <c r="B196" s="2">
-        <v>302</v>
+        <v>590</v>
       </c>
     </row>
     <row r="197" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A197" s="1">
-        <v>94169</v>
+        <v>93242</v>
       </c>
       <c r="B197" s="2">
-        <v>737</v>
+        <v>342</v>
       </c>
     </row>
     <row r="198" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A198" s="1">
-        <v>94170</v>
+        <v>94139</v>
       </c>
       <c r="B198" s="2">
-        <v>737</v>
+        <v>193</v>
       </c>
     </row>
     <row r="199" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A199" s="1">
-        <v>94171</v>
+        <v>94140</v>
       </c>
       <c r="B199" s="2">
-        <v>571</v>
+        <v>693</v>
       </c>
     </row>
     <row r="200" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A200" s="1">
-        <v>94172</v>
+        <v>94142</v>
       </c>
       <c r="B200" s="2">
-        <v>489</v>
+        <v>130</v>
       </c>
     </row>
     <row r="201" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A201" s="1">
-        <v>94173</v>
+        <v>94169</v>
       </c>
       <c r="B201" s="2">
-        <v>351</v>
+        <v>479</v>
       </c>
     </row>
     <row r="202" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A202" s="1">
-        <v>94592</v>
+        <v>94170</v>
       </c>
       <c r="B202" s="2">
-        <v>753</v>
+        <v>483</v>
       </c>
     </row>
     <row r="203" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A203" s="1">
-        <v>94593</v>
+        <v>94171</v>
       </c>
       <c r="B203" s="2">
-        <v>691</v>
+        <v>399</v>
       </c>
     </row>
     <row r="204" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A204" s="1">
-        <v>94594</v>
+        <v>94172</v>
       </c>
       <c r="B204" s="2">
-        <v>580</v>
+        <v>387</v>
       </c>
     </row>
     <row r="205" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A205" s="1">
-        <v>94595</v>
+        <v>94173</v>
       </c>
       <c r="B205" s="2">
-        <v>409</v>
+        <v>254</v>
       </c>
     </row>
     <row r="206" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A206" s="1">
-        <v>94596</v>
+        <v>94592</v>
       </c>
       <c r="B206" s="2">
-        <v>181</v>
+        <v>400</v>
       </c>
     </row>
     <row r="207" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A207" s="1">
-        <v>95082</v>
+        <v>94593</v>
       </c>
       <c r="B207" s="2">
-        <v>110</v>
+        <v>341</v>
       </c>
     </row>
     <row r="208" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A208" s="1">
-        <v>95083</v>
+        <v>94594</v>
       </c>
       <c r="B208" s="2">
-        <v>86</v>
+        <v>229</v>
       </c>
     </row>
     <row r="209" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A209" s="1">
-        <v>95085</v>
+        <v>94595</v>
       </c>
       <c r="B209" s="2">
-        <v>7</v>
+        <v>217</v>
       </c>
     </row>
     <row r="210" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A210" s="1">
-        <v>95086</v>
+        <v>94596</v>
       </c>
       <c r="B210" s="2">
-        <v>9</v>
+        <v>65</v>
       </c>
     </row>
     <row r="211" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A211" s="1">
-        <v>95976</v>
+        <v>95082</v>
       </c>
       <c r="B211" s="2">
-        <v>13</v>
+        <v>36</v>
       </c>
     </row>
     <row r="212" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A212" s="1">
-        <v>96315</v>
+        <v>95083</v>
       </c>
       <c r="B212" s="2">
-        <v>226</v>
+        <v>9</v>
       </c>
     </row>
     <row r="213" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A213" s="1">
-        <v>96316</v>
+        <v>95976</v>
       </c>
       <c r="B213" s="2">
-        <v>223</v>
+        <v>5</v>
       </c>
     </row>
     <row r="214" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A214" s="1">
-        <v>96317</v>
+        <v>96315</v>
       </c>
       <c r="B214" s="2">
-        <v>158</v>
+        <v>11</v>
       </c>
     </row>
     <row r="215" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A215" s="1">
-        <v>96318</v>
+        <v>96316</v>
       </c>
       <c r="B215" s="2">
-        <v>91</v>
+        <v>3</v>
       </c>
     </row>
     <row r="216" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A216" s="1">
-        <v>96319</v>
+        <v>96317</v>
       </c>
       <c r="B216" s="2">
-        <v>65</v>
+        <v>9</v>
       </c>
     </row>
     <row r="217" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A217" s="1">
-        <v>97324</v>
+        <v>96318</v>
       </c>
       <c r="B217" s="2">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="218" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A218" s="1">
-        <v>97353</v>
+        <v>97324</v>
       </c>
       <c r="B218" s="2">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="219" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A219" s="1">
-        <v>97354</v>
+        <v>97355</v>
       </c>
       <c r="B219" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="220" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A220" s="1">
-        <v>97355</v>
+        <v>97356</v>
       </c>
       <c r="B220" s="2">
-        <v>18</v>
+        <v>11</v>
       </c>
     </row>
     <row r="221" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A221" s="1">
-        <v>97356</v>
+        <v>97496</v>
       </c>
       <c r="B221" s="2">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="222" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A222" s="1">
-        <v>97357</v>
+        <v>97497</v>
       </c>
       <c r="B222" s="2">
-        <v>1</v>
+        <v>14</v>
       </c>
     </row>
     <row r="223" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A223" s="1">
-        <v>97496</v>
+        <v>97498</v>
       </c>
       <c r="B223" s="2">
-        <v>35</v>
+        <v>1</v>
       </c>
     </row>
     <row r="224" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A224" s="1">
-        <v>97497</v>
+        <v>97797</v>
       </c>
       <c r="B224" s="2">
-        <v>45</v>
+        <v>31</v>
       </c>
     </row>
     <row r="225" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A225" s="1">
-        <v>97498</v>
+        <v>97798</v>
       </c>
       <c r="B225" s="2">
-        <v>6</v>
+        <v>34</v>
       </c>
     </row>
     <row r="226" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A226" s="1">
-        <v>97499</v>
+        <v>97799</v>
       </c>
       <c r="B226" s="2">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="227" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A227" s="1">
-        <v>97504</v>
+        <v>97801</v>
       </c>
       <c r="B227" s="2">
-        <v>3</v>
+        <v>15</v>
       </c>
     </row>
     <row r="228" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A228" s="1">
-        <v>97797</v>
+        <v>97832</v>
       </c>
       <c r="B228" s="2">
-        <v>39</v>
+        <v>1</v>
       </c>
     </row>
     <row r="229" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A229" s="1">
-        <v>97798</v>
+        <v>97833</v>
       </c>
       <c r="B229" s="2">
-        <v>48</v>
+        <v>1</v>
       </c>
     </row>
     <row r="230" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A230" s="1">
-        <v>97799</v>
+        <v>97856</v>
       </c>
       <c r="B230" s="2">
-        <v>33</v>
+        <v>103</v>
       </c>
     </row>
     <row r="231" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A231" s="1">
-        <v>97800</v>
+        <v>97857</v>
       </c>
       <c r="B231" s="2">
-        <v>10</v>
+        <v>148</v>
       </c>
     </row>
     <row r="232" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A232" s="1">
-        <v>97801</v>
+        <v>97858</v>
       </c>
       <c r="B232" s="2">
-        <v>23</v>
+        <v>86</v>
       </c>
     </row>
     <row r="233" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A233" s="1">
-        <v>97813</v>
+        <v>97859</v>
       </c>
       <c r="B233" s="2">
-        <v>1</v>
+        <v>70</v>
       </c>
     </row>
     <row r="234" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A234" s="1">
-        <v>97815</v>
+        <v>97860</v>
       </c>
       <c r="B234" s="2">
-        <v>3</v>
+        <v>38</v>
       </c>
     </row>
     <row r="235" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A235" s="1">
-        <v>97832</v>
+        <v>97861</v>
       </c>
       <c r="B235" s="2">
-        <v>28</v>
+        <v>137</v>
       </c>
     </row>
     <row r="236" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A236" s="1">
-        <v>97833</v>
+        <v>97862</v>
       </c>
       <c r="B236" s="2">
-        <v>11</v>
+        <v>349</v>
       </c>
     </row>
     <row r="237" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A237" s="1">
-        <v>98288</v>
+        <v>97871</v>
       </c>
       <c r="B237" s="2">
-        <v>15</v>
+        <v>120</v>
       </c>
     </row>
     <row r="238" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A238" s="1">
-        <v>98289</v>
+        <v>97872</v>
       </c>
       <c r="B238" s="2">
-        <v>1</v>
+        <v>152</v>
       </c>
     </row>
     <row r="239" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A239" s="1">
-        <v>98307</v>
+        <v>97873</v>
       </c>
       <c r="B239" s="2">
-        <v>11</v>
+        <v>53</v>
       </c>
     </row>
     <row r="240" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A240" s="1">
-        <v>98308</v>
+        <v>97874</v>
       </c>
       <c r="B240" s="2">
-        <v>23</v>
+        <v>31</v>
       </c>
     </row>
     <row r="241" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A241" s="1">
-        <v>98332</v>
+        <v>97875</v>
       </c>
       <c r="B241" s="2">
-        <v>21</v>
+        <v>7</v>
       </c>
     </row>
     <row r="242" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A242" s="1">
-        <v>98333</v>
+        <v>97876</v>
       </c>
       <c r="B242" s="2">
-        <v>11</v>
+        <v>147</v>
       </c>
     </row>
     <row r="243" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A243" s="1">
-        <v>98340</v>
+        <v>97877</v>
       </c>
       <c r="B243" s="2">
-        <v>56</v>
+        <v>326</v>
       </c>
     </row>
     <row r="244" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A244" s="1">
-        <v>98341</v>
+        <v>97878</v>
       </c>
       <c r="B244" s="2">
-        <v>67</v>
+        <v>11</v>
       </c>
     </row>
     <row r="245" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A245" s="1">
-        <v>98342</v>
+        <v>97879</v>
       </c>
       <c r="B245" s="2">
-        <v>39</v>
+        <v>12</v>
       </c>
     </row>
     <row r="246" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A246" s="1">
-        <v>98343</v>
+        <v>98288</v>
       </c>
       <c r="B246" s="2">
-        <v>26</v>
+        <v>1</v>
       </c>
     </row>
     <row r="247" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A247" s="1">
-        <v>98344</v>
+        <v>98307</v>
       </c>
       <c r="B247" s="2">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="248" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A248" s="1">
-        <v>98345</v>
+        <v>98308</v>
       </c>
       <c r="B248" s="2">
-        <v>14</v>
+        <v>1</v>
       </c>
     </row>
     <row r="249" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A249" s="1">
-        <v>98346</v>
+        <v>98333</v>
       </c>
       <c r="B249" s="2">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="250" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A250" s="1">
-        <v>98347</v>
+        <v>98340</v>
       </c>
       <c r="B250" s="2">
-        <v>9</v>
+        <v>34</v>
       </c>
     </row>
     <row r="251" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A251" s="1">
-        <v>98348</v>
+        <v>98341</v>
       </c>
       <c r="B251" s="2">
-        <v>1</v>
+        <v>54</v>
       </c>
     </row>
     <row r="252" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A252" s="1">
-        <v>98350</v>
+        <v>98342</v>
       </c>
       <c r="B252" s="2">
-        <v>47</v>
+        <v>20</v>
       </c>
     </row>
     <row r="253" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A253" s="1">
-        <v>98351</v>
+        <v>98343</v>
       </c>
       <c r="B253" s="2">
-        <v>43</v>
+        <v>11</v>
       </c>
     </row>
     <row r="254" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A254" s="1">
-        <v>98353</v>
+        <v>98350</v>
       </c>
       <c r="B254" s="2">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="255" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A255" s="1">
-        <v>98354</v>
+        <v>98351</v>
       </c>
       <c r="B255" s="2">
         <v>3</v>
@@ -2490,7 +2484,7 @@
         <v>98355</v>
       </c>
       <c r="B256" s="2">
-        <v>37</v>
+        <v>9</v>
       </c>
     </row>
     <row r="257" spans="1:2" x14ac:dyDescent="0.25">
@@ -2498,100 +2492,100 @@
         <v>98356</v>
       </c>
       <c r="B257" s="2">
-        <v>48</v>
+        <v>8</v>
       </c>
     </row>
     <row r="258" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A258" s="1">
-        <v>98358</v>
+        <v>98370</v>
       </c>
       <c r="B258" s="2">
-        <v>2</v>
+        <v>13</v>
       </c>
     </row>
     <row r="259" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A259" s="1">
-        <v>98365</v>
+        <v>98371</v>
       </c>
       <c r="B259" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="260" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A260" s="1">
-        <v>98366</v>
+        <v>98387</v>
       </c>
       <c r="B260" s="2">
-        <v>18</v>
+        <v>1</v>
       </c>
     </row>
     <row r="261" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A261" s="1">
-        <v>98368</v>
+        <v>98400</v>
       </c>
       <c r="B261" s="2">
-        <v>4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="262" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A262" s="1">
-        <v>98370</v>
+        <v>98401</v>
       </c>
       <c r="B262" s="2">
-        <v>49</v>
+        <v>23</v>
       </c>
     </row>
     <row r="263" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A263" s="1">
-        <v>98371</v>
+        <v>98402</v>
       </c>
       <c r="B263" s="2">
-        <v>44</v>
+        <v>12</v>
       </c>
     </row>
     <row r="264" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A264" s="1">
-        <v>98372</v>
+        <v>98403</v>
       </c>
       <c r="B264" s="2">
-        <v>11</v>
+        <v>5</v>
       </c>
     </row>
     <row r="265" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A265" s="1">
-        <v>98375</v>
+        <v>98404</v>
       </c>
       <c r="B265" s="2">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="266" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A266" s="1">
-        <v>98376</v>
+        <v>98450</v>
       </c>
       <c r="B266" s="2">
-        <v>20</v>
+        <v>1</v>
       </c>
     </row>
     <row r="267" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A267" s="1">
-        <v>98377</v>
+        <v>98471</v>
       </c>
       <c r="B267" s="2">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="268" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A268" s="1">
-        <v>98378</v>
+        <v>98737</v>
       </c>
       <c r="B268" s="2">
-        <v>15</v>
+        <v>1</v>
       </c>
     </row>
     <row r="269" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A269" s="1">
-        <v>98379</v>
+        <v>98747</v>
       </c>
       <c r="B269" s="2">
         <v>1</v>
@@ -2599,703 +2593,703 @@
     </row>
     <row r="270" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A270" s="1">
-        <v>98380</v>
+        <v>98752</v>
       </c>
       <c r="B270" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="271" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A271" s="1">
-        <v>98381</v>
+        <v>20402</v>
       </c>
       <c r="B271" s="2">
-        <v>13</v>
+        <v>4320</v>
       </c>
     </row>
     <row r="272" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A272" s="1">
-        <v>98382</v>
+        <v>20839</v>
       </c>
       <c r="B272" s="2">
-        <v>2</v>
+        <v>1656</v>
       </c>
     </row>
     <row r="273" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A273" s="1">
-        <v>98385</v>
+        <v>20840</v>
       </c>
       <c r="B273" s="2">
-        <v>2</v>
+        <v>2418</v>
       </c>
     </row>
     <row r="274" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A274" s="1">
-        <v>98386</v>
+        <v>20841</v>
       </c>
       <c r="B274" s="2">
-        <v>19</v>
+        <v>311</v>
       </c>
     </row>
     <row r="275" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A275" s="1">
-        <v>98387</v>
+        <v>20845</v>
       </c>
       <c r="B275" s="2">
-        <v>26</v>
+        <v>756</v>
       </c>
     </row>
     <row r="276" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A276" s="1">
-        <v>98400</v>
+        <v>20846</v>
       </c>
       <c r="B276" s="2">
-        <v>73</v>
+        <v>138</v>
       </c>
     </row>
     <row r="277" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A277" s="1">
-        <v>98401</v>
+        <v>20847</v>
       </c>
       <c r="B277" s="2">
-        <v>87</v>
+        <v>114</v>
       </c>
     </row>
     <row r="278" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A278" s="1">
-        <v>98402</v>
+        <v>34299</v>
       </c>
       <c r="B278" s="2">
-        <v>55</v>
+        <v>556</v>
       </c>
     </row>
     <row r="279" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A279" s="1">
-        <v>98403</v>
+        <v>44701</v>
       </c>
       <c r="B279" s="2">
-        <v>33</v>
+        <v>632</v>
       </c>
     </row>
     <row r="280" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A280" s="1">
-        <v>98404</v>
+        <v>49926</v>
       </c>
       <c r="B280" s="2">
-        <v>24</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="281" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A281" s="1">
-        <v>98469</v>
+        <v>53086</v>
       </c>
       <c r="B281" s="2">
-        <v>12</v>
+        <v>1728</v>
       </c>
     </row>
     <row r="282" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A282" s="1">
-        <v>98471</v>
+        <v>53406</v>
       </c>
       <c r="B282" s="2">
-        <v>5</v>
+        <v>36</v>
       </c>
     </row>
     <row r="283" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A283" s="1">
-        <v>98488</v>
+        <v>53407</v>
       </c>
       <c r="B283" s="2">
-        <v>1</v>
+        <v>2064</v>
       </c>
     </row>
     <row r="284" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A284" s="1">
-        <v>98489</v>
+        <v>53408</v>
       </c>
       <c r="B284" s="2">
-        <v>7</v>
+        <v>756</v>
       </c>
     </row>
     <row r="285" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A285" s="1">
-        <v>98504</v>
+        <v>53410</v>
       </c>
       <c r="B285" s="2">
-        <v>2</v>
+        <v>12</v>
       </c>
     </row>
     <row r="286" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A286" s="1">
-        <v>98519</v>
+        <v>57140</v>
       </c>
       <c r="B286" s="2">
-        <v>7</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="287" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A287" s="1">
-        <v>98737</v>
+        <v>58609</v>
       </c>
       <c r="B287" s="2">
-        <v>1</v>
+        <v>24</v>
       </c>
     </row>
     <row r="288" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A288" s="1">
-        <v>98747</v>
+        <v>60971</v>
       </c>
       <c r="B288" s="2">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="289" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A289" s="1">
-        <v>98752</v>
+        <v>64252</v>
       </c>
       <c r="B289" s="2">
-        <v>2</v>
+        <v>1320</v>
       </c>
     </row>
     <row r="290" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A290" s="1">
-        <v>20840</v>
+        <v>65819</v>
       </c>
       <c r="B290" s="2">
-        <v>2436</v>
+        <v>36</v>
       </c>
     </row>
     <row r="291" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A291" s="1">
-        <v>20841</v>
+        <v>68293</v>
       </c>
       <c r="B291" s="2">
-        <v>587</v>
+        <v>336</v>
       </c>
     </row>
     <row r="292" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A292" s="1">
-        <v>20846</v>
+        <v>68480</v>
       </c>
       <c r="B292" s="2">
-        <v>156</v>
+        <v>400</v>
       </c>
     </row>
     <row r="293" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A293" s="1">
-        <v>20847</v>
+        <v>68651</v>
       </c>
       <c r="B293" s="2">
-        <v>136</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="294" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A294" s="1">
-        <v>34299</v>
+        <v>69372</v>
       </c>
       <c r="B294" s="2">
-        <v>608</v>
+        <v>384</v>
       </c>
     </row>
     <row r="295" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A295" s="1">
-        <v>44701</v>
+        <v>69373</v>
       </c>
       <c r="B295" s="2">
-        <v>212</v>
+        <v>972</v>
       </c>
     </row>
     <row r="296" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A296" s="1">
-        <v>49926</v>
+        <v>69380</v>
       </c>
       <c r="B296" s="2">
-        <v>4000</v>
+        <v>12</v>
       </c>
     </row>
     <row r="297" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A297" s="1">
-        <v>53406</v>
+        <v>69382</v>
       </c>
       <c r="B297" s="2">
-        <v>1728</v>
+        <v>12</v>
       </c>
     </row>
     <row r="298" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A298" s="1">
-        <v>53407</v>
+        <v>69389</v>
       </c>
       <c r="B298" s="2">
-        <v>3888</v>
+        <v>828</v>
       </c>
     </row>
     <row r="299" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A299" s="1">
-        <v>53408</v>
+        <v>69949</v>
       </c>
       <c r="B299" s="2">
-        <v>2592</v>
+        <v>24</v>
       </c>
     </row>
     <row r="300" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A300" s="1">
-        <v>53410</v>
+        <v>74166</v>
       </c>
       <c r="B300" s="2">
-        <v>1512</v>
+        <v>120</v>
       </c>
     </row>
     <row r="301" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A301" s="1">
-        <v>58609</v>
+        <v>74167</v>
       </c>
       <c r="B301" s="2">
-        <v>1728</v>
+        <v>396</v>
       </c>
     </row>
     <row r="302" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A302" s="1">
-        <v>60971</v>
+        <v>74427</v>
       </c>
       <c r="B302" s="2">
-        <v>1296</v>
+        <v>468</v>
       </c>
     </row>
     <row r="303" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A303" s="1">
-        <v>64252</v>
+        <v>74520</v>
       </c>
       <c r="B303" s="2">
-        <v>3024</v>
+        <v>348</v>
       </c>
     </row>
     <row r="304" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A304" s="1">
-        <v>65819</v>
+        <v>82918</v>
       </c>
       <c r="B304" s="2">
-        <v>1728</v>
+        <v>600</v>
       </c>
     </row>
     <row r="305" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A305" s="1">
-        <v>68651</v>
+        <v>83232</v>
       </c>
       <c r="B305" s="2">
-        <v>1440</v>
+        <v>1496</v>
       </c>
     </row>
     <row r="306" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A306" s="1">
-        <v>69369</v>
+        <v>83233</v>
       </c>
       <c r="B306" s="2">
-        <v>48</v>
+        <v>8</v>
       </c>
     </row>
     <row r="307" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A307" s="1">
-        <v>69372</v>
+        <v>83234</v>
       </c>
       <c r="B307" s="2">
-        <v>1236</v>
+        <v>472</v>
       </c>
     </row>
     <row r="308" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A308" s="1">
-        <v>69373</v>
+        <v>83664</v>
       </c>
       <c r="B308" s="2">
-        <v>1644</v>
+        <v>192</v>
       </c>
     </row>
     <row r="309" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A309" s="1">
-        <v>69380</v>
+        <v>86000</v>
       </c>
       <c r="B309" s="2">
-        <v>588</v>
+        <v>242</v>
       </c>
     </row>
     <row r="310" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A310" s="1">
-        <v>69382</v>
+        <v>87534</v>
       </c>
       <c r="B310" s="2">
-        <v>120</v>
+        <v>180</v>
       </c>
     </row>
     <row r="311" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A311" s="1">
-        <v>69389</v>
+        <v>88269</v>
       </c>
       <c r="B311" s="2">
-        <v>1308</v>
+        <v>124</v>
       </c>
     </row>
     <row r="312" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A312" s="1">
-        <v>69948</v>
+        <v>88270</v>
       </c>
       <c r="B312" s="2">
-        <v>36</v>
+        <v>332</v>
       </c>
     </row>
     <row r="313" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A313" s="1">
-        <v>69949</v>
+        <v>88271</v>
       </c>
       <c r="B313" s="2">
-        <v>60</v>
+        <v>8</v>
       </c>
     </row>
     <row r="314" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A314" s="1">
-        <v>74158</v>
+        <v>89302</v>
       </c>
       <c r="B314" s="2">
-        <v>216</v>
+        <v>86</v>
       </c>
     </row>
     <row r="315" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A315" s="1">
-        <v>74166</v>
+        <v>89304</v>
       </c>
       <c r="B315" s="2">
-        <v>1728</v>
+        <v>202</v>
       </c>
     </row>
     <row r="316" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A316" s="1">
-        <v>74167</v>
+        <v>91732</v>
       </c>
       <c r="B316" s="2">
-        <v>2160</v>
+        <v>224</v>
       </c>
     </row>
     <row r="317" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A317" s="1">
-        <v>76530</v>
+        <v>92742</v>
       </c>
       <c r="B317" s="2">
-        <v>200</v>
+        <v>6</v>
       </c>
     </row>
     <row r="318" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A318" s="1">
-        <v>83232</v>
+        <v>92747</v>
       </c>
       <c r="B318" s="2">
-        <v>2600</v>
+        <v>352</v>
       </c>
     </row>
     <row r="319" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A319" s="1">
-        <v>83233</v>
+        <v>92767</v>
       </c>
       <c r="B319" s="2">
-        <v>136</v>
+        <v>1722</v>
       </c>
     </row>
     <row r="320" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A320" s="1">
-        <v>83234</v>
+        <v>93027</v>
       </c>
       <c r="B320" s="2">
-        <v>1600</v>
+        <v>537</v>
       </c>
     </row>
     <row r="321" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A321" s="1">
-        <v>83664</v>
+        <v>93036</v>
       </c>
       <c r="B321" s="2">
-        <v>960</v>
+        <v>44</v>
       </c>
     </row>
     <row r="322" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A322" s="1">
-        <v>85652</v>
+        <v>93042</v>
       </c>
       <c r="B322" s="2">
-        <v>800</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="323" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A323" s="1">
-        <v>86000</v>
+        <v>93051</v>
       </c>
       <c r="B323" s="2">
-        <v>780</v>
+        <v>324</v>
       </c>
     </row>
     <row r="324" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A324" s="1">
-        <v>87534</v>
+        <v>93057</v>
       </c>
       <c r="B324" s="2">
-        <v>536</v>
+        <v>684</v>
       </c>
     </row>
     <row r="325" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A325" s="1">
-        <v>88269</v>
+        <v>94355</v>
       </c>
       <c r="B325" s="2">
-        <v>1260</v>
+        <v>1604</v>
       </c>
     </row>
     <row r="326" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A326" s="1">
-        <v>88270</v>
+        <v>94356</v>
       </c>
       <c r="B326" s="2">
-        <v>1152</v>
+        <v>2178</v>
       </c>
     </row>
     <row r="327" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A327" s="1">
-        <v>88271</v>
+        <v>94357</v>
       </c>
       <c r="B327" s="2">
-        <v>504</v>
+        <v>2484</v>
       </c>
     </row>
     <row r="328" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A328" s="1">
-        <v>88866</v>
+        <v>94358</v>
       </c>
       <c r="B328" s="2">
-        <v>1200</v>
+        <v>2432</v>
       </c>
     </row>
     <row r="329" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A329" s="1">
-        <v>89302</v>
+        <v>94394</v>
       </c>
       <c r="B329" s="2">
-        <v>400</v>
+        <v>624</v>
       </c>
     </row>
     <row r="330" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A330" s="1">
-        <v>89304</v>
+        <v>94404</v>
       </c>
       <c r="B330" s="2">
-        <v>660</v>
+        <v>4096</v>
       </c>
     </row>
     <row r="331" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A331" s="1">
-        <v>91732</v>
+        <v>95038</v>
       </c>
       <c r="B331" s="2">
-        <v>272</v>
+        <v>510</v>
       </c>
     </row>
     <row r="332" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A332" s="1">
-        <v>92742</v>
+        <v>95590</v>
       </c>
       <c r="B332" s="2">
-        <v>48</v>
+        <v>692</v>
       </c>
     </row>
     <row r="333" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A333" s="1">
-        <v>92747</v>
+        <v>95591</v>
       </c>
       <c r="B333" s="2">
-        <v>1140</v>
+        <v>280</v>
       </c>
     </row>
     <row r="334" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A334" s="1">
-        <v>92767</v>
+        <v>95592</v>
       </c>
       <c r="B334" s="2">
-        <v>1776</v>
+        <v>1944</v>
       </c>
     </row>
     <row r="335" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A335" s="1">
-        <v>93027</v>
+        <v>96435</v>
       </c>
       <c r="B335" s="2">
-        <v>627</v>
+        <v>234</v>
       </c>
     </row>
     <row r="336" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A336" s="1">
-        <v>93036</v>
+        <v>96436</v>
       </c>
       <c r="B336" s="2">
-        <v>136</v>
+        <v>300</v>
       </c>
     </row>
     <row r="337" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A337" s="1">
-        <v>93051</v>
+        <v>96439</v>
       </c>
       <c r="B337" s="2">
-        <v>524</v>
+        <v>60</v>
       </c>
     </row>
     <row r="338" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A338" s="1">
-        <v>93057</v>
+        <v>96440</v>
       </c>
       <c r="B338" s="2">
-        <v>1680</v>
+        <v>66</v>
       </c>
     </row>
     <row r="339" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A339" s="1">
-        <v>94355</v>
+        <v>96441</v>
       </c>
       <c r="B339" s="2">
-        <v>1688</v>
+        <v>30</v>
       </c>
     </row>
     <row r="340" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A340" s="1">
-        <v>94356</v>
+        <v>96480</v>
       </c>
       <c r="B340" s="2">
-        <v>2246</v>
+        <v>1728</v>
       </c>
     </row>
     <row r="341" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A341" s="1">
-        <v>94357</v>
+        <v>96519</v>
       </c>
       <c r="B341" s="2">
-        <v>2612</v>
+        <v>304</v>
       </c>
     </row>
     <row r="342" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A342" s="1">
-        <v>94358</v>
+        <v>97127</v>
       </c>
       <c r="B342" s="2">
-        <v>2552</v>
+        <v>41</v>
       </c>
     </row>
     <row r="343" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A343" s="1">
-        <v>94394</v>
+        <v>97129</v>
       </c>
       <c r="B343" s="2">
-        <v>1800</v>
+        <v>44</v>
       </c>
     </row>
     <row r="344" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A344" s="1">
-        <v>94400</v>
+        <v>97131</v>
       </c>
       <c r="B344" s="2">
-        <v>2520</v>
+        <v>64</v>
       </c>
     </row>
     <row r="345" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A345" s="1">
-        <v>94402</v>
+        <v>97552</v>
       </c>
       <c r="B345" s="2">
-        <v>1024</v>
+        <v>14</v>
       </c>
     </row>
     <row r="346" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A346" s="1">
-        <v>94404</v>
+        <v>97554</v>
       </c>
       <c r="B346" s="2">
-        <v>508</v>
+        <v>168</v>
       </c>
     </row>
     <row r="347" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A347" s="1">
-        <v>95590</v>
+        <v>97561</v>
       </c>
       <c r="B347" s="2">
-        <v>1312</v>
+        <v>8</v>
       </c>
     </row>
     <row r="348" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A348" s="1">
-        <v>95591</v>
+        <v>97566</v>
       </c>
       <c r="B348" s="2">
-        <v>896</v>
+        <v>16</v>
       </c>
     </row>
     <row r="349" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A349" s="1">
-        <v>95592</v>
+        <v>97571</v>
       </c>
       <c r="B349" s="2">
-        <v>3600</v>
+        <v>4</v>
       </c>
     </row>
     <row r="350" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A350" s="1">
-        <v>95667</v>
+        <v>97573</v>
       </c>
       <c r="B350" s="2">
-        <v>12</v>
+        <v>32</v>
       </c>
     </row>
     <row r="351" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A351" s="1">
-        <v>96435</v>
+        <v>97581</v>
       </c>
       <c r="B351" s="2">
-        <v>588</v>
+        <v>20</v>
       </c>
     </row>
     <row r="352" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A352" s="1">
-        <v>96436</v>
+        <v>97582</v>
       </c>
       <c r="B352" s="2">
-        <v>624</v>
+        <v>52</v>
       </c>
     </row>
     <row r="353" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A353" s="1">
-        <v>96439</v>
+        <v>97583</v>
       </c>
       <c r="B353" s="2">
-        <v>240</v>
+        <v>116</v>
       </c>
     </row>
     <row r="354" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A354" s="1">
-        <v>96440</v>
+        <v>97584</v>
       </c>
       <c r="B354" s="2">
-        <v>240</v>
+        <v>16</v>
       </c>
     </row>
     <row r="355" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A355" s="1">
-        <v>96441</v>
+        <v>97585</v>
       </c>
       <c r="B355" s="2">
-        <v>192</v>
+        <v>84</v>
       </c>
     </row>
     <row r="356" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A356" s="1">
-        <v>96519</v>
+        <v>97596</v>
       </c>
       <c r="B356" s="2">
-        <v>360</v>
+        <v>12</v>
       </c>
     </row>
     <row r="357" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A357" s="1">
-        <v>97126</v>
+        <v>97598</v>
       </c>
       <c r="B357" s="2">
         <v>12</v>
@@ -3303,47 +3297,47 @@
     </row>
     <row r="358" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A358" s="1">
-        <v>97127</v>
+        <v>97600</v>
       </c>
       <c r="B358" s="2">
-        <v>49</v>
+        <v>69</v>
       </c>
     </row>
     <row r="359" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A359" s="1">
-        <v>97129</v>
+        <v>97624</v>
       </c>
       <c r="B359" s="2">
-        <v>56</v>
+        <v>51</v>
       </c>
     </row>
     <row r="360" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A360" s="1">
-        <v>97131</v>
+        <v>97626</v>
       </c>
       <c r="B360" s="2">
-        <v>84</v>
+        <v>5</v>
       </c>
     </row>
     <row r="361" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A361" s="1">
-        <v>97133</v>
+        <v>97627</v>
       </c>
       <c r="B361" s="2">
-        <v>4</v>
+        <v>30</v>
       </c>
     </row>
     <row r="362" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A362" s="1">
-        <v>97552</v>
+        <v>97653</v>
       </c>
       <c r="B362" s="2">
-        <v>20</v>
+        <v>64</v>
       </c>
     </row>
     <row r="363" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A363" s="1">
-        <v>97553</v>
+        <v>97654</v>
       </c>
       <c r="B363" s="2">
         <v>4</v>
@@ -3351,2026 +3345,1370 @@
     </row>
     <row r="364" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A364" s="1">
-        <v>97554</v>
+        <v>97881</v>
       </c>
       <c r="B364" s="2">
-        <v>180</v>
+        <v>300</v>
       </c>
     </row>
     <row r="365" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A365" s="1">
-        <v>97559</v>
+        <v>97882</v>
       </c>
       <c r="B365" s="2">
-        <v>12</v>
+        <v>264</v>
       </c>
     </row>
     <row r="366" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A366" s="1">
-        <v>97560</v>
+        <v>98227</v>
       </c>
       <c r="B366" s="2">
-        <v>24</v>
+        <v>16</v>
       </c>
     </row>
     <row r="367" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A367" s="1">
-        <v>97561</v>
+        <v>98587</v>
       </c>
       <c r="B367" s="2">
-        <v>44</v>
+        <v>4</v>
       </c>
     </row>
     <row r="368" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A368" s="1">
-        <v>97564</v>
+        <v>98629</v>
       </c>
       <c r="B368" s="2">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="369" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A369" s="1">
-        <v>97565</v>
+        <v>98633</v>
       </c>
       <c r="B369" s="2">
-        <v>12</v>
+        <v>28</v>
       </c>
     </row>
     <row r="370" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A370" s="1">
-        <v>97566</v>
+        <v>7722</v>
       </c>
       <c r="B370" s="2">
-        <v>40</v>
+        <v>744</v>
       </c>
     </row>
     <row r="371" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A371" s="1">
-        <v>97571</v>
+        <v>33427</v>
       </c>
       <c r="B371" s="2">
-        <v>14</v>
+        <v>4</v>
       </c>
     </row>
     <row r="372" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A372" s="1">
-        <v>97573</v>
+        <v>35060</v>
       </c>
       <c r="B372" s="2">
-        <v>68</v>
+        <v>1512</v>
       </c>
     </row>
     <row r="373" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A373" s="1">
-        <v>97580</v>
+        <v>78372</v>
       </c>
       <c r="B373" s="2">
-        <v>36</v>
+        <v>360</v>
       </c>
     </row>
     <row r="374" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A374" s="1">
-        <v>97581</v>
+        <v>78641</v>
       </c>
       <c r="B374" s="2">
-        <v>60</v>
+        <v>320</v>
       </c>
     </row>
     <row r="375" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A375" s="1">
-        <v>97582</v>
+        <v>84540</v>
       </c>
       <c r="B375" s="2">
-        <v>96</v>
+        <v>2659</v>
       </c>
     </row>
     <row r="376" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A376" s="1">
-        <v>97583</v>
+        <v>89097</v>
       </c>
       <c r="B376" s="2">
-        <v>140</v>
+        <v>351</v>
       </c>
     </row>
     <row r="377" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A377" s="1">
-        <v>97584</v>
+        <v>92811</v>
       </c>
       <c r="B377" s="2">
-        <v>76</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="378" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A378" s="1">
-        <v>97585</v>
+        <v>94746</v>
       </c>
       <c r="B378" s="2">
-        <v>116</v>
+        <v>6</v>
       </c>
     </row>
     <row r="379" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A379" s="1">
-        <v>97586</v>
+        <v>95346</v>
       </c>
       <c r="B379" s="2">
-        <v>84</v>
+        <v>42</v>
       </c>
     </row>
     <row r="380" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A380" s="1">
-        <v>97588</v>
+        <v>95588</v>
       </c>
       <c r="B380" s="2">
-        <v>14</v>
+        <v>2055</v>
       </c>
     </row>
     <row r="381" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A381" s="1">
-        <v>97596</v>
+        <v>95795</v>
       </c>
       <c r="B381" s="2">
-        <v>60</v>
+        <v>12</v>
       </c>
     </row>
     <row r="382" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A382" s="1">
-        <v>97598</v>
+        <v>96377</v>
       </c>
       <c r="B382" s="2">
-        <v>12</v>
+        <v>288</v>
       </c>
     </row>
     <row r="383" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A383" s="1">
-        <v>97600</v>
+        <v>96919</v>
       </c>
       <c r="B383" s="2">
-        <v>69</v>
+        <v>3616</v>
       </c>
     </row>
     <row r="384" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A384" s="1">
-        <v>97624</v>
+        <v>96984</v>
       </c>
       <c r="B384" s="2">
-        <v>131</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="385" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A385" s="1">
-        <v>97625</v>
+        <v>96985</v>
       </c>
       <c r="B385" s="2">
-        <v>39</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="386" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A386" s="1">
-        <v>97626</v>
+        <v>96986</v>
       </c>
       <c r="B386" s="2">
-        <v>9</v>
+        <v>600</v>
       </c>
     </row>
     <row r="387" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A387" s="1">
-        <v>97627</v>
+        <v>96989</v>
       </c>
       <c r="B387" s="2">
-        <v>40</v>
+        <v>536</v>
       </c>
     </row>
     <row r="388" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A388" s="1">
-        <v>97628</v>
+        <v>97662</v>
       </c>
       <c r="B388" s="2">
-        <v>6</v>
+        <v>130</v>
       </c>
     </row>
     <row r="389" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A389" s="1">
-        <v>97653</v>
+        <v>97663</v>
       </c>
       <c r="B389" s="2">
-        <v>78</v>
+        <v>330</v>
       </c>
     </row>
     <row r="390" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A390" s="1">
-        <v>97654</v>
+        <v>97664</v>
       </c>
       <c r="B390" s="2">
-        <v>4</v>
+        <v>310</v>
       </c>
     </row>
     <row r="391" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A391" s="1">
-        <v>97881</v>
+        <v>97665</v>
       </c>
       <c r="B391" s="2">
-        <v>340</v>
+        <v>2190</v>
       </c>
     </row>
     <row r="392" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A392" s="1">
-        <v>97882</v>
+        <v>99273</v>
       </c>
       <c r="B392" s="2">
-        <v>304</v>
+        <v>80</v>
       </c>
     </row>
     <row r="393" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A393" s="1">
-        <v>98217</v>
+        <v>99275</v>
       </c>
       <c r="B393" s="2">
-        <v>104</v>
+        <v>476</v>
       </c>
     </row>
     <row r="394" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A394" s="1">
-        <v>98218</v>
+        <v>9646</v>
       </c>
       <c r="B394" s="2">
-        <v>36</v>
+        <v>780</v>
       </c>
     </row>
     <row r="395" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A395" s="1">
-        <v>98219</v>
+        <v>24874</v>
       </c>
       <c r="B395" s="2">
-        <v>12</v>
+        <v>869</v>
       </c>
     </row>
     <row r="396" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A396" s="1">
-        <v>98222</v>
+        <v>34094</v>
       </c>
       <c r="B396" s="2">
-        <v>12</v>
+        <v>7658</v>
       </c>
     </row>
     <row r="397" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A397" s="1">
-        <v>98227</v>
+        <v>53546</v>
       </c>
       <c r="B397" s="2">
-        <v>52</v>
+        <v>620</v>
       </c>
     </row>
     <row r="398" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A398" s="1">
-        <v>98233</v>
+        <v>59014</v>
       </c>
       <c r="B398" s="2">
-        <v>24</v>
+        <v>946</v>
       </c>
     </row>
     <row r="399" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A399" s="1">
-        <v>98581</v>
+        <v>65948</v>
       </c>
       <c r="B399" s="2">
-        <v>20</v>
+        <v>1216</v>
       </c>
     </row>
     <row r="400" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A400" s="1">
-        <v>98582</v>
+        <v>66663</v>
       </c>
       <c r="B400" s="2">
-        <v>8</v>
+        <v>1764</v>
       </c>
     </row>
     <row r="401" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A401" s="1">
-        <v>98583</v>
+        <v>68463</v>
       </c>
       <c r="B401" s="2">
-        <v>20</v>
+        <v>368</v>
       </c>
     </row>
     <row r="402" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A402" s="1">
-        <v>98584</v>
+        <v>70620</v>
       </c>
       <c r="B402" s="2">
-        <v>12</v>
+        <v>96</v>
       </c>
     </row>
     <row r="403" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A403" s="1">
-        <v>98585</v>
+        <v>70653</v>
       </c>
       <c r="B403" s="2">
-        <v>24</v>
+        <v>1936</v>
       </c>
     </row>
     <row r="404" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A404" s="1">
-        <v>98587</v>
+        <v>74779</v>
       </c>
       <c r="B404" s="2">
-        <v>28</v>
+        <v>310</v>
       </c>
     </row>
     <row r="405" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A405" s="1">
-        <v>98626</v>
+        <v>75922</v>
       </c>
       <c r="B405" s="2">
-        <v>33</v>
+        <v>396</v>
       </c>
     </row>
     <row r="406" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A406" s="1">
-        <v>98627</v>
+        <v>75923</v>
       </c>
       <c r="B406" s="2">
-        <v>27</v>
+        <v>16</v>
       </c>
     </row>
     <row r="407" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A407" s="1">
-        <v>98628</v>
+        <v>75924</v>
       </c>
       <c r="B407" s="2">
-        <v>18</v>
+        <v>50</v>
       </c>
     </row>
     <row r="408" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A408" s="1">
-        <v>98629</v>
+        <v>76065</v>
       </c>
       <c r="B408" s="2">
-        <v>81</v>
+        <v>26</v>
       </c>
     </row>
     <row r="409" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A409" s="1">
-        <v>98631</v>
+        <v>76066</v>
       </c>
       <c r="B409" s="2">
-        <v>51</v>
+        <v>128</v>
       </c>
     </row>
     <row r="410" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A410" s="1">
-        <v>98632</v>
+        <v>76067</v>
       </c>
       <c r="B410" s="2">
-        <v>28</v>
+        <v>38</v>
       </c>
     </row>
     <row r="411" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A411" s="1">
-        <v>98634</v>
+        <v>78624</v>
       </c>
       <c r="B411" s="2">
-        <v>28</v>
+        <v>286</v>
       </c>
     </row>
     <row r="412" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A412" s="1">
-        <v>7722</v>
+        <v>78625</v>
       </c>
       <c r="B412" s="2">
-        <v>780</v>
+        <v>438</v>
       </c>
     </row>
     <row r="413" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A413" s="1">
-        <v>33427</v>
+        <v>78626</v>
       </c>
       <c r="B413" s="2">
-        <v>148</v>
+        <v>228</v>
       </c>
     </row>
     <row r="414" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A414" s="1">
-        <v>59285</v>
+        <v>78627</v>
       </c>
       <c r="B414" s="2">
-        <v>20</v>
+        <v>364</v>
       </c>
     </row>
     <row r="415" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A415" s="1">
-        <v>78372</v>
+        <v>78628</v>
       </c>
       <c r="B415" s="2">
-        <v>580</v>
+        <v>206</v>
       </c>
     </row>
     <row r="416" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A416" s="1">
-        <v>78641</v>
+        <v>78629</v>
       </c>
       <c r="B416" s="2">
-        <v>888</v>
+        <v>344</v>
       </c>
     </row>
     <row r="417" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A417" s="1">
-        <v>84540</v>
+        <v>78630</v>
       </c>
       <c r="B417" s="2">
-        <v>3459</v>
+        <v>280</v>
       </c>
     </row>
     <row r="418" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A418" s="1">
-        <v>89097</v>
+        <v>78631</v>
       </c>
       <c r="B418" s="2">
-        <v>431</v>
+        <v>16</v>
       </c>
     </row>
     <row r="419" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A419" s="1">
-        <v>92811</v>
+        <v>78632</v>
       </c>
       <c r="B419" s="2">
-        <v>1480</v>
+        <v>588</v>
       </c>
     </row>
     <row r="420" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A420" s="1">
-        <v>94746</v>
+        <v>78633</v>
       </c>
       <c r="B420" s="2">
-        <v>162</v>
+        <v>300</v>
       </c>
     </row>
     <row r="421" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A421" s="1">
-        <v>95346</v>
+        <v>78634</v>
       </c>
       <c r="B421" s="2">
-        <v>492</v>
+        <v>216</v>
       </c>
     </row>
     <row r="422" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A422" s="1">
-        <v>95588</v>
+        <v>78635</v>
       </c>
       <c r="B422" s="2">
-        <v>2730</v>
+        <v>312</v>
       </c>
     </row>
     <row r="423" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A423" s="1">
-        <v>95795</v>
+        <v>81763</v>
       </c>
       <c r="B423" s="2">
-        <v>94</v>
+        <v>238</v>
       </c>
     </row>
     <row r="424" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A424" s="1">
-        <v>96377</v>
+        <v>81764</v>
       </c>
       <c r="B424" s="2">
-        <v>308</v>
+        <v>130</v>
       </c>
     </row>
     <row r="425" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A425" s="1">
-        <v>96984</v>
+        <v>81765</v>
       </c>
       <c r="B425" s="2">
-        <v>1596</v>
+        <v>656</v>
       </c>
     </row>
     <row r="426" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A426" s="1">
-        <v>96985</v>
+        <v>83163</v>
       </c>
       <c r="B426" s="2">
-        <v>1500</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="427" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A427" s="1">
-        <v>96986</v>
+        <v>83184</v>
       </c>
       <c r="B427" s="2">
-        <v>1084</v>
+        <v>302</v>
       </c>
     </row>
     <row r="428" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A428" s="1">
-        <v>96989</v>
+        <v>84802</v>
       </c>
       <c r="B428" s="2">
-        <v>720</v>
+        <v>574</v>
       </c>
     </row>
     <row r="429" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A429" s="1">
-        <v>97662</v>
+        <v>84803</v>
       </c>
       <c r="B429" s="2">
-        <v>130</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="430" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A430" s="1">
-        <v>97663</v>
+        <v>84804</v>
       </c>
       <c r="B430" s="2">
-        <v>330</v>
+        <v>656</v>
       </c>
     </row>
     <row r="431" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A431" s="1">
-        <v>97664</v>
+        <v>84807</v>
       </c>
       <c r="B431" s="2">
-        <v>310</v>
+        <v>540</v>
       </c>
     </row>
     <row r="432" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A432" s="1">
-        <v>97665</v>
+        <v>87263</v>
       </c>
       <c r="B432" s="2">
-        <v>3050</v>
+        <v>792</v>
       </c>
     </row>
     <row r="433" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A433" s="1">
-        <v>98437</v>
+        <v>87325</v>
       </c>
       <c r="B433" s="2">
-        <v>28</v>
+        <v>22</v>
       </c>
     </row>
     <row r="434" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A434" s="1">
-        <v>98445</v>
+        <v>87326</v>
       </c>
       <c r="B434" s="2">
-        <v>4</v>
+        <v>14</v>
       </c>
     </row>
     <row r="435" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A435" s="1">
-        <v>98540</v>
+        <v>87635</v>
       </c>
       <c r="B435" s="2">
-        <v>30</v>
+        <v>1448</v>
       </c>
     </row>
     <row r="436" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A436" s="1">
-        <v>98541</v>
+        <v>87901</v>
       </c>
       <c r="B436" s="2">
-        <v>20</v>
+        <v>812</v>
       </c>
     </row>
     <row r="437" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A437" s="1">
-        <v>99273</v>
+        <v>87903</v>
       </c>
       <c r="B437" s="2">
-        <v>424</v>
+        <v>124</v>
       </c>
     </row>
     <row r="438" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A438" s="1">
-        <v>99275</v>
+        <v>88350</v>
       </c>
       <c r="B438" s="2">
-        <v>1036</v>
+        <v>340</v>
       </c>
     </row>
     <row r="439" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A439" s="1">
-        <v>9646</v>
+        <v>88360</v>
       </c>
       <c r="B439" s="2">
-        <v>2448</v>
+        <v>922</v>
       </c>
     </row>
     <row r="440" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A440" s="1">
-        <v>24874</v>
+        <v>88400</v>
       </c>
       <c r="B440" s="2">
-        <v>1413</v>
+        <v>510</v>
       </c>
     </row>
     <row r="441" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A441" s="1">
-        <v>34094</v>
+        <v>90109</v>
       </c>
       <c r="B441" s="2">
-        <v>3558</v>
+        <v>351</v>
       </c>
     </row>
     <row r="442" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A442" s="1">
-        <v>53546</v>
+        <v>90497</v>
       </c>
       <c r="B442" s="2">
-        <v>1002</v>
+        <v>6</v>
       </c>
     </row>
     <row r="443" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A443" s="1">
-        <v>59014</v>
+        <v>91653</v>
       </c>
       <c r="B443" s="2">
-        <v>334</v>
+        <v>160</v>
       </c>
     </row>
     <row r="444" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A444" s="1">
-        <v>66663</v>
+        <v>91665</v>
       </c>
       <c r="B444" s="2">
-        <v>344</v>
+        <v>744</v>
       </c>
     </row>
     <row r="445" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A445" s="1">
-        <v>68463</v>
+        <v>92172</v>
       </c>
       <c r="B445" s="2">
-        <v>928</v>
+        <v>416</v>
       </c>
     </row>
     <row r="446" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A446" s="1">
-        <v>70620</v>
+        <v>92176</v>
       </c>
       <c r="B446" s="2">
-        <v>380</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="447" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A447" s="1">
-        <v>70653</v>
+        <v>92463</v>
       </c>
       <c r="B447" s="2">
-        <v>2234</v>
+        <v>1692</v>
       </c>
     </row>
     <row r="448" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A448" s="1">
-        <v>74779</v>
+        <v>92636</v>
       </c>
       <c r="B448" s="2">
-        <v>594</v>
+        <v>378</v>
       </c>
     </row>
     <row r="449" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A449" s="1">
-        <v>75922</v>
+        <v>92822</v>
       </c>
       <c r="B449" s="2">
-        <v>544</v>
+        <v>144</v>
       </c>
     </row>
     <row r="450" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A450" s="1">
-        <v>75923</v>
+        <v>92823</v>
       </c>
       <c r="B450" s="2">
-        <v>168</v>
+        <v>94</v>
       </c>
     </row>
     <row r="451" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A451" s="1">
-        <v>75924</v>
+        <v>92999</v>
       </c>
       <c r="B451" s="2">
-        <v>230</v>
+        <v>890</v>
       </c>
     </row>
     <row r="452" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A452" s="1">
-        <v>76063</v>
+        <v>93016</v>
       </c>
       <c r="B452" s="2">
-        <v>12</v>
+        <v>1780</v>
       </c>
     </row>
     <row r="453" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A453" s="1">
-        <v>76064</v>
+        <v>93067</v>
       </c>
       <c r="B453" s="2">
-        <v>16</v>
+        <v>426</v>
       </c>
     </row>
     <row r="454" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A454" s="1">
-        <v>76065</v>
+        <v>93073</v>
       </c>
       <c r="B454" s="2">
-        <v>430</v>
+        <v>424</v>
       </c>
     </row>
     <row r="455" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A455" s="1">
-        <v>76066</v>
+        <v>94233</v>
       </c>
       <c r="B455" s="2">
-        <v>460</v>
+        <v>380</v>
       </c>
     </row>
     <row r="456" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A456" s="1">
-        <v>76067</v>
+        <v>94314</v>
       </c>
       <c r="B456" s="2">
-        <v>300</v>
+        <v>186</v>
       </c>
     </row>
     <row r="457" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A457" s="1">
-        <v>77697</v>
+        <v>94317</v>
       </c>
       <c r="B457" s="2">
-        <v>86</v>
+        <v>2980</v>
       </c>
     </row>
     <row r="458" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A458" s="1">
-        <v>78624</v>
+        <v>94821</v>
       </c>
       <c r="B458" s="2">
-        <v>552</v>
+        <v>544</v>
       </c>
     </row>
     <row r="459" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A459" s="1">
-        <v>78625</v>
+        <v>94830</v>
       </c>
       <c r="B459" s="2">
-        <v>558</v>
+        <v>2</v>
       </c>
     </row>
     <row r="460" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A460" s="1">
-        <v>78626</v>
+        <v>94835</v>
       </c>
       <c r="B460" s="2">
-        <v>552</v>
+        <v>1268</v>
       </c>
     </row>
     <row r="461" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A461" s="1">
-        <v>78627</v>
+        <v>95020</v>
       </c>
       <c r="B461" s="2">
-        <v>596</v>
+        <v>552</v>
       </c>
     </row>
     <row r="462" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A462" s="1">
-        <v>78628</v>
+        <v>95021</v>
       </c>
       <c r="B462" s="2">
-        <v>552</v>
+        <v>148</v>
       </c>
     </row>
     <row r="463" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A463" s="1">
-        <v>78629</v>
+        <v>95202</v>
       </c>
       <c r="B463" s="2">
-        <v>552</v>
+        <v>18</v>
       </c>
     </row>
     <row r="464" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A464" s="1">
-        <v>78630</v>
+        <v>95211</v>
       </c>
       <c r="B464" s="2">
-        <v>552</v>
+        <v>932</v>
       </c>
     </row>
     <row r="465" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A465" s="1">
-        <v>78631</v>
+        <v>95536</v>
       </c>
       <c r="B465" s="2">
-        <v>552</v>
+        <v>516</v>
       </c>
     </row>
     <row r="466" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A466" s="1">
-        <v>78633</v>
+        <v>95538</v>
       </c>
       <c r="B466" s="2">
-        <v>564</v>
+        <v>736</v>
       </c>
     </row>
     <row r="467" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A467" s="1">
-        <v>78634</v>
+        <v>95715</v>
       </c>
       <c r="B467" s="2">
-        <v>552</v>
+        <v>688</v>
       </c>
     </row>
     <row r="468" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A468" s="1">
-        <v>78635</v>
+        <v>95731</v>
       </c>
       <c r="B468" s="2">
-        <v>552</v>
+        <v>4</v>
       </c>
     </row>
     <row r="469" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A469" s="1">
-        <v>81763</v>
+        <v>95732</v>
       </c>
       <c r="B469" s="2">
-        <v>482</v>
+        <v>1912</v>
       </c>
     </row>
     <row r="470" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A470" s="1">
-        <v>81764</v>
+        <v>95735</v>
       </c>
       <c r="B470" s="2">
-        <v>370</v>
+        <v>774</v>
       </c>
     </row>
     <row r="471" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A471" s="1">
-        <v>81765</v>
+        <v>95765</v>
       </c>
       <c r="B471" s="2">
-        <v>976</v>
+        <v>156</v>
       </c>
     </row>
     <row r="472" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A472" s="1">
-        <v>83163</v>
+        <v>95768</v>
       </c>
       <c r="B472" s="2">
-        <v>1338</v>
+        <v>884</v>
       </c>
     </row>
     <row r="473" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A473" s="1">
-        <v>83184</v>
+        <v>95769</v>
       </c>
       <c r="B473" s="2">
-        <v>1140</v>
+        <v>2410</v>
       </c>
     </row>
     <row r="474" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A474" s="1">
-        <v>84801</v>
+        <v>95770</v>
       </c>
       <c r="B474" s="2">
-        <v>10</v>
+        <v>862</v>
       </c>
     </row>
     <row r="475" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A475" s="1">
-        <v>84802</v>
+        <v>95772</v>
       </c>
       <c r="B475" s="2">
-        <v>772</v>
+        <v>1456</v>
       </c>
     </row>
     <row r="476" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A476" s="1">
-        <v>87263</v>
+        <v>95774</v>
       </c>
       <c r="B476" s="2">
-        <v>92</v>
+        <v>1330</v>
       </c>
     </row>
     <row r="477" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A477" s="1">
-        <v>87325</v>
+        <v>95781</v>
       </c>
       <c r="B477" s="2">
-        <v>318</v>
+        <v>1654</v>
       </c>
     </row>
     <row r="478" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A478" s="1">
-        <v>87326</v>
+        <v>95907</v>
       </c>
       <c r="B478" s="2">
-        <v>292</v>
+        <v>904</v>
       </c>
     </row>
     <row r="479" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A479" s="1">
-        <v>87635</v>
+        <v>96507</v>
       </c>
       <c r="B479" s="2">
-        <v>468</v>
+        <v>2</v>
       </c>
     </row>
     <row r="480" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A480" s="1">
-        <v>87901</v>
+        <v>96508</v>
       </c>
       <c r="B480" s="2">
-        <v>1175</v>
+        <v>118</v>
       </c>
     </row>
     <row r="481" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A481" s="1">
-        <v>87903</v>
+        <v>96509</v>
       </c>
       <c r="B481" s="2">
-        <v>124</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="482" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A482" s="1">
-        <v>88350</v>
+        <v>96510</v>
       </c>
       <c r="B482" s="2">
-        <v>528</v>
+        <v>2</v>
       </c>
     </row>
     <row r="483" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A483" s="1">
-        <v>88360</v>
+        <v>96588</v>
       </c>
       <c r="B483" s="2">
-        <v>430</v>
+        <v>2180</v>
       </c>
     </row>
     <row r="484" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A484" s="1">
-        <v>88400</v>
+        <v>97066</v>
       </c>
       <c r="B484" s="2">
-        <v>840</v>
+        <v>30</v>
       </c>
     </row>
     <row r="485" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A485" s="1">
-        <v>90109</v>
+        <v>97067</v>
       </c>
       <c r="B485" s="2">
-        <v>599</v>
+        <v>38</v>
       </c>
     </row>
     <row r="486" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A486" s="1">
-        <v>90497</v>
+        <v>97111</v>
       </c>
       <c r="B486" s="2">
-        <v>60</v>
+        <v>1844</v>
       </c>
     </row>
     <row r="487" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A487" s="1">
-        <v>91653</v>
+        <v>97116</v>
       </c>
       <c r="B487" s="2">
-        <v>406</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="488" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A488" s="1">
-        <v>91665</v>
+        <v>97118</v>
       </c>
       <c r="B488" s="2">
-        <v>1100</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="489" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A489" s="1">
-        <v>91678</v>
+        <v>97186</v>
       </c>
       <c r="B489" s="2">
-        <v>144</v>
+        <v>800</v>
       </c>
     </row>
     <row r="490" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A490" s="1">
-        <v>92172</v>
+        <v>97245</v>
       </c>
       <c r="B490" s="2">
-        <v>724</v>
+        <v>912</v>
       </c>
     </row>
     <row r="491" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A491" s="1">
-        <v>92176</v>
+        <v>97703</v>
       </c>
       <c r="B491" s="2">
-        <v>1156</v>
+        <v>30</v>
       </c>
     </row>
     <row r="492" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A492" s="1">
-        <v>92636</v>
+        <v>97717</v>
       </c>
       <c r="B492" s="2">
-        <v>914</v>
+        <v>58</v>
       </c>
     </row>
     <row r="493" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A493" s="1">
-        <v>92815</v>
+        <v>97720</v>
       </c>
       <c r="B493" s="2">
-        <v>64</v>
+        <v>16</v>
       </c>
     </row>
     <row r="494" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A494" s="1">
-        <v>92822</v>
+        <v>97744</v>
       </c>
       <c r="B494" s="2">
-        <v>190</v>
+        <v>8</v>
       </c>
     </row>
     <row r="495" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A495" s="1">
-        <v>92823</v>
+        <v>97756</v>
       </c>
       <c r="B495" s="2">
-        <v>148</v>
+        <v>70</v>
       </c>
     </row>
     <row r="496" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A496" s="1">
-        <v>92836</v>
+        <v>97785</v>
       </c>
       <c r="B496" s="2">
-        <v>24</v>
+        <v>16</v>
       </c>
     </row>
     <row r="497" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A497" s="1">
-        <v>92999</v>
+        <v>97788</v>
       </c>
       <c r="B497" s="2">
-        <v>1818</v>
+        <v>40</v>
       </c>
     </row>
     <row r="498" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A498" s="1">
-        <v>93067</v>
+        <v>97791</v>
       </c>
       <c r="B498" s="2">
-        <v>664</v>
+        <v>2</v>
       </c>
     </row>
     <row r="499" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A499" s="1">
-        <v>93073</v>
+        <v>97793</v>
       </c>
       <c r="B499" s="2">
-        <v>762</v>
+        <v>30</v>
       </c>
     </row>
     <row r="500" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A500" s="1">
-        <v>94233</v>
+        <v>98132</v>
       </c>
       <c r="B500" s="2">
-        <v>498</v>
+        <v>2</v>
       </c>
     </row>
     <row r="501" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A501" s="1">
-        <v>94314</v>
+        <v>98140</v>
       </c>
       <c r="B501" s="2">
-        <v>466</v>
+        <v>16</v>
       </c>
     </row>
     <row r="502" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A502" s="1">
-        <v>94317</v>
+        <v>98141</v>
       </c>
       <c r="B502" s="2">
-        <v>1034</v>
+        <v>4</v>
       </c>
     </row>
     <row r="503" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A503" s="1">
-        <v>94821</v>
+        <v>98142</v>
       </c>
       <c r="B503" s="2">
-        <v>712</v>
+        <v>6</v>
       </c>
     </row>
     <row r="504" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A504" s="1">
-        <v>94830</v>
+        <v>98144</v>
       </c>
       <c r="B504" s="2">
-        <v>182</v>
+        <v>16</v>
       </c>
     </row>
     <row r="505" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A505" s="1">
-        <v>95020</v>
+        <v>98147</v>
       </c>
       <c r="B505" s="2">
-        <v>762</v>
+        <v>26</v>
       </c>
     </row>
     <row r="506" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A506" s="1">
-        <v>95021</v>
+        <v>98148</v>
       </c>
       <c r="B506" s="2">
-        <v>458</v>
+        <v>2</v>
       </c>
     </row>
     <row r="507" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A507" s="1">
-        <v>95202</v>
+        <v>98162</v>
       </c>
       <c r="B507" s="2">
-        <v>94</v>
+        <v>2</v>
       </c>
     </row>
     <row r="508" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A508" s="1">
-        <v>95211</v>
+        <v>98166</v>
       </c>
       <c r="B508" s="2">
-        <v>1052</v>
+        <v>36</v>
       </c>
     </row>
     <row r="509" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A509" s="1">
-        <v>95536</v>
+        <v>98171</v>
       </c>
       <c r="B509" s="2">
-        <v>754</v>
+        <v>8</v>
       </c>
     </row>
     <row r="510" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A510" s="1">
-        <v>95538</v>
+        <v>98172</v>
       </c>
       <c r="B510" s="2">
-        <v>938</v>
+        <v>4</v>
       </c>
     </row>
     <row r="511" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A511" s="1">
-        <v>95715</v>
+        <v>98173</v>
       </c>
       <c r="B511" s="2">
-        <v>894</v>
+        <v>22</v>
       </c>
     </row>
     <row r="512" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A512" s="1">
-        <v>95731</v>
+        <v>98264</v>
       </c>
       <c r="B512" s="2">
-        <v>148</v>
+        <v>6</v>
       </c>
     </row>
     <row r="513" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A513" s="1">
-        <v>95732</v>
+        <v>98269</v>
       </c>
       <c r="B513" s="2">
-        <v>132</v>
+        <v>2</v>
       </c>
     </row>
     <row r="514" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A514" s="1">
-        <v>95735</v>
+        <v>98270</v>
       </c>
       <c r="B514" s="2">
-        <v>1594</v>
+        <v>8</v>
       </c>
     </row>
     <row r="515" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A515" s="1">
-        <v>95765</v>
+        <v>98545</v>
       </c>
       <c r="B515" s="2">
-        <v>366</v>
+        <v>8</v>
       </c>
     </row>
     <row r="516" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A516" s="1">
-        <v>95768</v>
+        <v>98546</v>
       </c>
       <c r="B516" s="2">
-        <v>142</v>
+        <v>39</v>
       </c>
     </row>
     <row r="517" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A517" s="1">
-        <v>95769</v>
+        <v>98548</v>
       </c>
       <c r="B517" s="2">
-        <v>610</v>
+        <v>23</v>
       </c>
     </row>
     <row r="518" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A518" s="1">
-        <v>95770</v>
+        <v>98549</v>
       </c>
       <c r="B518" s="2">
-        <v>184</v>
+        <v>4</v>
       </c>
     </row>
     <row r="519" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A519" s="1">
-        <v>95772</v>
+        <v>98553</v>
       </c>
       <c r="B519" s="2">
-        <v>246</v>
+        <v>58</v>
       </c>
     </row>
     <row r="520" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A520" s="1">
-        <v>95774</v>
+        <v>98556</v>
       </c>
       <c r="B520" s="2">
-        <v>240</v>
+        <v>54</v>
       </c>
     </row>
     <row r="521" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A521" s="1">
-        <v>95781</v>
+        <v>98559</v>
       </c>
       <c r="B521" s="2">
-        <v>266</v>
+        <v>2</v>
       </c>
     </row>
     <row r="522" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A522" s="1">
-        <v>95907</v>
+        <v>98560</v>
       </c>
       <c r="B522" s="2">
-        <v>1746</v>
+        <v>4</v>
       </c>
     </row>
     <row r="523" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A523" s="1">
-        <v>95911</v>
+        <v>98561</v>
       </c>
       <c r="B523" s="2">
-        <v>24</v>
+        <v>14</v>
       </c>
     </row>
     <row r="524" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A524" s="1">
-        <v>96507</v>
+        <v>98562</v>
       </c>
       <c r="B524" s="2">
-        <v>40</v>
+        <v>52</v>
       </c>
     </row>
     <row r="525" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A525" s="1">
-        <v>96508</v>
+        <v>98568</v>
       </c>
       <c r="B525" s="2">
-        <v>394</v>
+        <v>12</v>
       </c>
     </row>
     <row r="526" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A526" s="1">
-        <v>96509</v>
+        <v>98569</v>
       </c>
       <c r="B526" s="2">
-        <v>1874</v>
+        <v>28</v>
       </c>
     </row>
     <row r="527" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A527" s="1">
-        <v>96510</v>
+        <v>98571</v>
       </c>
       <c r="B527" s="2">
-        <v>86</v>
+        <v>14</v>
       </c>
     </row>
     <row r="528" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A528" s="1">
-        <v>96517</v>
+        <v>98572</v>
       </c>
       <c r="B528" s="2">
-        <v>22</v>
+        <v>2</v>
       </c>
     </row>
     <row r="529" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A529" s="1">
-        <v>96539</v>
+        <v>98573</v>
       </c>
       <c r="B529" s="2">
-        <v>92</v>
+        <v>4</v>
       </c>
     </row>
     <row r="530" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A530" s="1">
-        <v>96588</v>
+        <v>98575</v>
       </c>
       <c r="B530" s="2">
-        <v>1496</v>
+        <v>56</v>
       </c>
     </row>
     <row r="531" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A531" s="1">
-        <v>97066</v>
+        <v>98579</v>
       </c>
       <c r="B531" s="2">
-        <v>222</v>
+        <v>8</v>
       </c>
     </row>
     <row r="532" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A532" s="1">
-        <v>97067</v>
+        <v>98597</v>
       </c>
       <c r="B532" s="2">
-        <v>302</v>
+        <v>6</v>
       </c>
     </row>
     <row r="533" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A533" s="1">
-        <v>97116</v>
+        <v>98598</v>
       </c>
       <c r="B533" s="2">
-        <v>2104</v>
+        <v>22</v>
       </c>
     </row>
     <row r="534" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A534" s="1">
-        <v>97118</v>
+        <v>98599</v>
       </c>
       <c r="B534" s="2">
-        <v>2104</v>
-      </c>
-    </row>
-    <row r="535" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A535" s="1">
-        <v>97186</v>
-      </c>
-      <c r="B535" s="2">
-        <v>1422</v>
-      </c>
-    </row>
-    <row r="536" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A536" s="1">
-        <v>97245</v>
-      </c>
-      <c r="B536" s="2">
-        <v>1354</v>
-      </c>
-    </row>
-    <row r="537" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A537" s="1">
-        <v>97703</v>
-      </c>
-      <c r="B537" s="2">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="538" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A538" s="1">
-        <v>97717</v>
-      </c>
-      <c r="B538" s="2">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="539" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A539" s="1">
-        <v>97720</v>
-      </c>
-      <c r="B539" s="2">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="540" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A540" s="1">
-        <v>97723</v>
-      </c>
-      <c r="B540" s="2">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="541" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A541" s="1">
-        <v>97725</v>
-      </c>
-      <c r="B541" s="2">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="542" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A542" s="1">
-        <v>97744</v>
-      </c>
-      <c r="B542" s="2">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="543" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A543" s="1">
-        <v>97756</v>
-      </c>
-      <c r="B543" s="2">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="544" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A544" s="1">
-        <v>97768</v>
-      </c>
-      <c r="B544" s="2">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="545" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A545" s="1">
-        <v>97784</v>
-      </c>
-      <c r="B545" s="2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="546" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A546" s="1">
-        <v>97785</v>
-      </c>
-      <c r="B546" s="2">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="547" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A547" s="1">
-        <v>97788</v>
-      </c>
-      <c r="B547" s="2">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="548" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A548" s="1">
-        <v>97790</v>
-      </c>
-      <c r="B548" s="2">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="549" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A549" s="1">
-        <v>97791</v>
-      </c>
-      <c r="B549" s="2">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="550" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A550" s="1">
-        <v>97792</v>
-      </c>
-      <c r="B550" s="2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="551" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A551" s="1">
-        <v>97793</v>
-      </c>
-      <c r="B551" s="2">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="552" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A552" s="1">
-        <v>98131</v>
-      </c>
-      <c r="B552" s="2">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="553" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A553" s="1">
-        <v>98132</v>
-      </c>
-      <c r="B553" s="2">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="554" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A554" s="1">
-        <v>98133</v>
-      </c>
-      <c r="B554" s="2">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="555" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A555" s="1">
-        <v>98134</v>
-      </c>
-      <c r="B555" s="2">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="556" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A556" s="1">
-        <v>98135</v>
-      </c>
-      <c r="B556" s="2">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="557" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A557" s="1">
-        <v>98136</v>
-      </c>
-      <c r="B557" s="2">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="558" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A558" s="1">
-        <v>98138</v>
-      </c>
-      <c r="B558" s="2">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="559" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A559" s="1">
-        <v>98140</v>
-      </c>
-      <c r="B559" s="2">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="560" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A560" s="1">
-        <v>98141</v>
-      </c>
-      <c r="B560" s="2">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="561" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A561" s="1">
-        <v>98142</v>
-      </c>
-      <c r="B561" s="2">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="562" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A562" s="1">
-        <v>98143</v>
-      </c>
-      <c r="B562" s="2">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="563" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A563" s="1">
-        <v>98144</v>
-      </c>
-      <c r="B563" s="2">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="564" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A564" s="1">
-        <v>98147</v>
-      </c>
-      <c r="B564" s="2">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="565" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A565" s="1">
-        <v>98148</v>
-      </c>
-      <c r="B565" s="2">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="566" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A566" s="1">
-        <v>98149</v>
-      </c>
-      <c r="B566" s="2">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="567" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A567" s="1">
-        <v>98150</v>
-      </c>
-      <c r="B567" s="2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="568" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A568" s="1">
-        <v>98151</v>
-      </c>
-      <c r="B568" s="2">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="569" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A569" s="1">
-        <v>98154</v>
-      </c>
-      <c r="B569" s="2">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="570" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A570" s="1">
-        <v>98159</v>
-      </c>
-      <c r="B570" s="2">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="571" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A571" s="1">
-        <v>98162</v>
-      </c>
-      <c r="B571" s="2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="572" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A572" s="1">
-        <v>98166</v>
-      </c>
-      <c r="B572" s="2">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="573" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A573" s="1">
-        <v>98171</v>
-      </c>
-      <c r="B573" s="2">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="574" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A574" s="1">
-        <v>98172</v>
-      </c>
-      <c r="B574" s="2">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="575" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A575" s="1">
-        <v>98173</v>
-      </c>
-      <c r="B575" s="2">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="576" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A576" s="1">
-        <v>98178</v>
-      </c>
-      <c r="B576" s="2">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="577" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A577" s="1">
-        <v>98263</v>
-      </c>
-      <c r="B577" s="2">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="578" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A578" s="1">
-        <v>98264</v>
-      </c>
-      <c r="B578" s="2">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="579" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A579" s="1">
-        <v>98268</v>
-      </c>
-      <c r="B579" s="2">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="580" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A580" s="1">
-        <v>98269</v>
-      </c>
-      <c r="B580" s="2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="581" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A581" s="1">
-        <v>98270</v>
-      </c>
-      <c r="B581" s="2">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="582" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A582" s="1">
-        <v>98545</v>
-      </c>
-      <c r="B582" s="2">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="583" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A583" s="1">
-        <v>98546</v>
-      </c>
-      <c r="B583" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="584" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A584" s="1">
-        <v>98547</v>
-      </c>
-      <c r="B584" s="2">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="585" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A585" s="1">
-        <v>98548</v>
-      </c>
-      <c r="B585" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="586" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A586" s="1">
-        <v>98549</v>
-      </c>
-      <c r="B586" s="2">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="587" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A587" s="1">
-        <v>98550</v>
-      </c>
-      <c r="B587" s="2">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="588" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A588" s="7">
-        <v>98551</v>
-      </c>
-      <c r="B588" s="8">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="589" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A589" s="7">
-        <v>98552</v>
-      </c>
-      <c r="B589" s="8">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="590" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A590" s="7">
-        <v>98553</v>
-      </c>
-      <c r="B590" s="8">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="591" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A591" s="7">
-        <v>98555</v>
-      </c>
-      <c r="B591" s="8">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="592" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A592" s="7">
-        <v>98556</v>
-      </c>
-      <c r="B592" s="8">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="593" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A593" s="7">
-        <v>98557</v>
-      </c>
-      <c r="B593" s="8">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="594" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A594" s="7">
-        <v>98559</v>
-      </c>
-      <c r="B594" s="8">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="595" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A595" s="7">
-        <v>98560</v>
-      </c>
-      <c r="B595" s="8">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="596" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A596" s="7">
-        <v>98561</v>
-      </c>
-      <c r="B596" s="8">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="597" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A597" s="7">
-        <v>98562</v>
-      </c>
-      <c r="B597" s="8">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="598" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A598" s="7">
-        <v>98563</v>
-      </c>
-      <c r="B598" s="8">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="599" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A599" s="7">
-        <v>98564</v>
-      </c>
-      <c r="B599" s="8">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="600" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A600" s="7">
-        <v>98566</v>
-      </c>
-      <c r="B600" s="8">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="601" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A601" s="7">
-        <v>98567</v>
-      </c>
-      <c r="B601" s="8">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="602" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A602" s="7">
-        <v>98568</v>
-      </c>
-      <c r="B602" s="8">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="603" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A603" s="7">
-        <v>98569</v>
-      </c>
-      <c r="B603" s="8">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="604" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A604" s="7">
-        <v>98571</v>
-      </c>
-      <c r="B604" s="8">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="605" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A605" s="7">
-        <v>98572</v>
-      </c>
-      <c r="B605" s="8">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="606" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A606" s="7">
-        <v>98573</v>
-      </c>
-      <c r="B606" s="8">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="607" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A607" s="7">
-        <v>98575</v>
-      </c>
-      <c r="B607" s="8">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="608" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A608" s="7">
-        <v>98579</v>
-      </c>
-      <c r="B608" s="8">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="609" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A609" s="7">
-        <v>98580</v>
-      </c>
-      <c r="B609" s="8">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="610" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A610" s="7">
-        <v>98593</v>
-      </c>
-      <c r="B610" s="8">
         <v>20</v>
-      </c>
-    </row>
-    <row r="611" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A611" s="7">
-        <v>98594</v>
-      </c>
-      <c r="B611" s="8">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="612" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A612" s="7">
-        <v>98595</v>
-      </c>
-      <c r="B612" s="8">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="613" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A613" s="7">
-        <v>98596</v>
-      </c>
-      <c r="B613" s="8">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="614" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A614" s="7">
-        <v>98597</v>
-      </c>
-      <c r="B614" s="8">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="615" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A615" s="7">
-        <v>98598</v>
-      </c>
-      <c r="B615" s="8">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="616" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A616" s="7">
-        <v>98599</v>
-      </c>
-      <c r="B616" s="8">
-        <v>86</v>
       </c>
     </row>
   </sheetData>
